--- a/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AA48F42-432B-4F9C-AEF7-78D34EFCD4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B20BB7C2-248D-491A-85C1-0F96DE2B1C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6703E927-87A0-4A6C-AA0A-067731434C25}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1A1DFE92-1F1D-4D7D-BDC3-8AE978F7FAEF}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3935,7 +3935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D0C4515-EAA3-4F2D-A33A-F7113B36EC55}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06E4933B-3CB3-4C8B-AA1E-2FC3FA4F869F}">
   <dimension ref="B9:T393"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22034,7 +22034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4B3092-42CD-45F6-AE47-6EEEBEC64A17}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{703B9626-79C3-4635-83DA-A37C86C84150}">
   <dimension ref="B9:T713"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -52100,7 +52100,7 @@
         <v>33</v>
       </c>
       <c r="L660">
-        <v>0.18879062275497618</v>
+        <v>0.18879062275497624</v>
       </c>
     </row>
     <row r="661" spans="2:12" x14ac:dyDescent="0.45">
@@ -52753,7 +52753,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L679">
-        <v>0.34091535770192305</v>
+        <v>0.34091535770192311</v>
       </c>
     </row>
     <row r="680" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B20BB7C2-248D-491A-85C1-0F96DE2B1C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BE03017-3D67-45CD-8893-854C5637B9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1A1DFE92-1F1D-4D7D-BDC3-8AE978F7FAEF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E0DC1649-77C9-4787-B467-1E4A272AEEF7}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3935,7 +3935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06E4933B-3CB3-4C8B-AA1E-2FC3FA4F869F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AABDAAA-DBCA-4267-A0EB-2D56669A08A5}">
   <dimension ref="B9:T393"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22034,7 +22034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{703B9626-79C3-4635-83DA-A37C86C84150}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF6B41F-6F33-49BB-A235-4A3A3633D1B0}">
   <dimension ref="B9:T713"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -52100,7 +52100,7 @@
         <v>33</v>
       </c>
       <c r="L660">
-        <v>0.18879062275497624</v>
+        <v>0.18879062275497618</v>
       </c>
     </row>
     <row r="661" spans="2:12" x14ac:dyDescent="0.45">
@@ -52753,7 +52753,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L679">
-        <v>0.34091535770192311</v>
+        <v>0.34091535770192305</v>
       </c>
     </row>
     <row r="680" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BE03017-3D67-45CD-8893-854C5637B9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D560F092-FAFB-4D28-B121-639FFCFE708C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E0DC1649-77C9-4787-B467-1E4A272AEEF7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4D932EB6-C615-4E8C-B01B-8DADEEC71FA2}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3935,7 +3935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AABDAAA-DBCA-4267-A0EB-2D56669A08A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABE08EB-0B9E-405D-9A1C-D9454E2BBA9E}">
   <dimension ref="B9:T393"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22034,7 +22034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF6B41F-6F33-49BB-A235-4A3A3633D1B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734F6D83-179B-4626-8298-1D60FC52E7D1}">
   <dimension ref="B9:T713"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -52100,7 +52100,7 @@
         <v>33</v>
       </c>
       <c r="L660">
-        <v>0.18879062275497618</v>
+        <v>0.18879062275497624</v>
       </c>
     </row>
     <row r="661" spans="2:12" x14ac:dyDescent="0.45">
@@ -52753,7 +52753,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L679">
-        <v>0.34091535770192305</v>
+        <v>0.34091535770192311</v>
       </c>
     </row>
     <row r="680" spans="2:12" x14ac:dyDescent="0.45">
@@ -52960,7 +52960,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L688">
-        <v>0.31350265799072619</v>
+        <v>0.31350265799072624</v>
       </c>
     </row>
     <row r="689" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D560F092-FAFB-4D28-B121-639FFCFE708C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51F76C6E-27DB-4B90-8F87-EDEB13EEBA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4D932EB6-C615-4E8C-B01B-8DADEEC71FA2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D3C59EAB-8C33-44A9-BADF-11F515188EA9}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1401,7 +1401,7 @@
     <t>ep_solar_pv_JPN</t>
   </si>
   <si>
-    <t>ep_windoff_c_wof-JPN</t>
+    <t>ep_windoff_JPN</t>
   </si>
   <si>
     <t>windoff</t>
@@ -1416,7 +1416,7 @@
     <t>ep_windoff_wind_G100000901431</t>
   </si>
   <si>
-    <t>ep_windoff_wind_c_wof-JPN</t>
+    <t>ep_windoff_wind_JPN</t>
   </si>
   <si>
     <t>ep_windon_wind_</t>
@@ -1428,7 +1428,7 @@
     <t>elc_won-JPN</t>
   </si>
   <si>
-    <t>ep_windon_wind_c_won-JPN</t>
+    <t>ep_windon_wind_JPN</t>
   </si>
   <si>
     <t>~fi_process</t>
@@ -3935,7 +3935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABE08EB-0B9E-405D-9A1C-D9454E2BBA9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F342E020-9B8E-46E4-85BA-7412D67F314C}">
   <dimension ref="B9:T393"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22034,7 +22034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734F6D83-179B-4626-8298-1D60FC52E7D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0337EF5-B1EF-46D3-B30C-738A7BE24418}">
   <dimension ref="B9:T713"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -52100,7 +52100,7 @@
         <v>33</v>
       </c>
       <c r="L660">
-        <v>0.18879062275497624</v>
+        <v>0.1919475549077887</v>
       </c>
     </row>
     <row r="661" spans="2:12" x14ac:dyDescent="0.45">
@@ -52135,7 +52135,7 @@
         <v>36</v>
       </c>
       <c r="L661">
-        <v>0.19553372699999999</v>
+        <v>0.19553372675776159</v>
       </c>
     </row>
     <row r="662" spans="2:12" x14ac:dyDescent="0.45">
@@ -52170,7 +52170,7 @@
         <v>37</v>
       </c>
       <c r="L662">
-        <v>0.19553372699999999</v>
+        <v>0.198412953192453</v>
       </c>
     </row>
     <row r="663" spans="2:12" x14ac:dyDescent="0.45">
@@ -52205,7 +52205,7 @@
         <v>30</v>
       </c>
       <c r="L663">
-        <v>0.205057828</v>
+        <v>0.2050578284580391</v>
       </c>
     </row>
     <row r="664" spans="2:12" x14ac:dyDescent="0.45">
@@ -52240,7 +52240,7 @@
         <v>44</v>
       </c>
       <c r="L664">
-        <v>0.193356948</v>
+        <v>0.1976534539076038</v>
       </c>
     </row>
     <row r="665" spans="2:12" x14ac:dyDescent="0.45">
@@ -52275,7 +52275,7 @@
         <v>42</v>
       </c>
       <c r="L665">
-        <v>0.18849895338857273</v>
+        <v>0.19155670571835337</v>
       </c>
     </row>
     <row r="666" spans="2:12" x14ac:dyDescent="0.45">
@@ -52310,7 +52310,7 @@
         <v>41</v>
       </c>
       <c r="L666">
-        <v>0.18790953052947762</v>
+        <v>0.19088160172929067</v>
       </c>
     </row>
     <row r="667" spans="2:12" x14ac:dyDescent="0.45">
@@ -52345,7 +52345,7 @@
         <v>40</v>
       </c>
       <c r="L667">
-        <v>0.18726172839115712</v>
+        <v>0.19059813905937753</v>
       </c>
     </row>
     <row r="668" spans="2:12" x14ac:dyDescent="0.45">
@@ -52380,7 +52380,7 @@
         <v>39</v>
       </c>
       <c r="L668">
-        <v>0.18705396679974498</v>
+        <v>0.19043532750319075</v>
       </c>
     </row>
     <row r="669" spans="2:12" x14ac:dyDescent="0.45">
@@ -52415,7 +52415,7 @@
         <v>38</v>
       </c>
       <c r="L669">
-        <v>0.18748195403549314</v>
+        <v>0.19076336576430539</v>
       </c>
     </row>
     <row r="670" spans="2:12" x14ac:dyDescent="0.45">
@@ -52450,7 +52450,7 @@
         <v>37</v>
       </c>
       <c r="L670">
-        <v>0.18703372391235171</v>
+        <v>0.19068540380811375</v>
       </c>
     </row>
     <row r="671" spans="2:12" x14ac:dyDescent="0.45">
@@ -52485,7 +52485,7 @@
         <v>36</v>
       </c>
       <c r="L671">
-        <v>0.18795525163079438</v>
+        <v>0.19161554674965406</v>
       </c>
     </row>
     <row r="672" spans="2:12" x14ac:dyDescent="0.45">
@@ -52520,7 +52520,7 @@
         <v>35</v>
       </c>
       <c r="L672">
-        <v>0.18705946836904874</v>
+        <v>0.19001875470431187</v>
       </c>
     </row>
     <row r="673" spans="2:12" x14ac:dyDescent="0.45">
@@ -52555,7 +52555,7 @@
         <v>34</v>
       </c>
       <c r="L673">
-        <v>0.18694612450712855</v>
+        <v>0.1907060284877726</v>
       </c>
     </row>
     <row r="674" spans="2:12" x14ac:dyDescent="0.45">
@@ -52590,7 +52590,7 @@
         <v>33</v>
       </c>
       <c r="L674">
-        <v>0.187178550855988</v>
+        <v>0.19103173414634983</v>
       </c>
     </row>
     <row r="675" spans="2:12" x14ac:dyDescent="0.45">
@@ -52625,7 +52625,7 @@
         <v>32</v>
       </c>
       <c r="L675">
-        <v>0.18771506610645669</v>
+        <v>0.19168997659731082</v>
       </c>
     </row>
     <row r="676" spans="2:12" x14ac:dyDescent="0.45">
@@ -52660,7 +52660,7 @@
         <v>31</v>
       </c>
       <c r="L676">
-        <v>0.18444010673291925</v>
+        <v>0.18683468866044445</v>
       </c>
     </row>
     <row r="677" spans="2:12" x14ac:dyDescent="0.45">
@@ -52695,7 +52695,7 @@
         <v>30</v>
       </c>
       <c r="L677">
-        <v>0.17961901499999999</v>
+        <v>0.18407784183612519</v>
       </c>
     </row>
     <row r="678" spans="2:12" x14ac:dyDescent="0.45">
@@ -52730,7 +52730,7 @@
         <v>30</v>
       </c>
       <c r="L678">
-        <v>0.18259553933043896</v>
+        <v>0.18750291125973922</v>
       </c>
     </row>
     <row r="679" spans="2:12" x14ac:dyDescent="0.45">
@@ -52753,7 +52753,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L679">
-        <v>0.34091535770192311</v>
+        <v>0.38298883693604863</v>
       </c>
     </row>
     <row r="680" spans="2:12" x14ac:dyDescent="0.45">
@@ -52776,7 +52776,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L680">
-        <v>0.28714474000000001</v>
+        <v>0.31800025417465738</v>
       </c>
     </row>
     <row r="681" spans="2:12" x14ac:dyDescent="0.45">
@@ -52799,7 +52799,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L681">
-        <v>0.344045237</v>
+        <v>0.41128422985257651</v>
       </c>
     </row>
     <row r="682" spans="2:12" x14ac:dyDescent="0.45">
@@ -52822,7 +52822,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L682">
-        <v>0.32345436399999999</v>
+        <v>0.40524317504741381</v>
       </c>
     </row>
     <row r="683" spans="2:12" x14ac:dyDescent="0.45">
@@ -52845,7 +52845,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L683">
-        <v>0.32345436399999999</v>
+        <v>0.40524317504741381</v>
       </c>
     </row>
     <row r="684" spans="2:12" x14ac:dyDescent="0.45">
@@ -52868,7 +52868,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L684">
-        <v>0.35796238699999999</v>
+        <v>0.34422113783574432</v>
       </c>
     </row>
     <row r="685" spans="2:12" x14ac:dyDescent="0.45">
@@ -52891,7 +52891,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L685">
-        <v>0.3219499236153846</v>
+        <v>0.34489092368481222</v>
       </c>
     </row>
     <row r="686" spans="2:12" x14ac:dyDescent="0.45">
@@ -52914,7 +52914,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L686">
-        <v>0.344045237</v>
+        <v>0.41128422985257657</v>
       </c>
     </row>
     <row r="687" spans="2:12" x14ac:dyDescent="0.45">
@@ -52937,7 +52937,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L687">
-        <v>0.42526660900000002</v>
+        <v>0.4237435699931944</v>
       </c>
     </row>
     <row r="688" spans="2:12" x14ac:dyDescent="0.45">
@@ -52960,7 +52960,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L688">
-        <v>0.31350265799072624</v>
+        <v>0.39895126255821034</v>
       </c>
     </row>
     <row r="689" spans="2:12" x14ac:dyDescent="0.45">
@@ -52983,7 +52983,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L689">
-        <v>0.36007824399999999</v>
+        <v>0.49340939513895699</v>
       </c>
     </row>
     <row r="690" spans="2:12" x14ac:dyDescent="0.45">
@@ -53006,7 +53006,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L690">
-        <v>0.55103598612500004</v>
+        <v>0.57549982888876816</v>
       </c>
     </row>
     <row r="691" spans="2:12" x14ac:dyDescent="0.45">
@@ -53029,7 +53029,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L691">
-        <v>0.35084091620444441</v>
+        <v>0.43979409562387495</v>
       </c>
     </row>
     <row r="692" spans="2:12" x14ac:dyDescent="0.45">
@@ -53052,7 +53052,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L692">
-        <v>0.30801275291596641</v>
+        <v>0.4251981211154951</v>
       </c>
     </row>
     <row r="693" spans="2:12" x14ac:dyDescent="0.45">
@@ -53075,7 +53075,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L693">
-        <v>0.34001820614207645</v>
+        <v>0.38932397286890646</v>
       </c>
     </row>
     <row r="694" spans="2:12" x14ac:dyDescent="0.45">
@@ -53098,7 +53098,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L694">
-        <v>0.2646504956625767</v>
+        <v>0.3229495208212585</v>
       </c>
     </row>
     <row r="695" spans="2:12" x14ac:dyDescent="0.45">
@@ -53121,7 +53121,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L695">
-        <v>0.3705975751554404</v>
+        <v>0.3980569352137322</v>
       </c>
     </row>
     <row r="696" spans="2:12" x14ac:dyDescent="0.45">
@@ -53144,7 +53144,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L696">
-        <v>0.3246005834163822</v>
+        <v>0.41682406819041018</v>
       </c>
     </row>
     <row r="697" spans="2:12" x14ac:dyDescent="0.45">
@@ -53167,7 +53167,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L697">
-        <v>0.35354767291743117</v>
+        <v>0.38497163061619466</v>
       </c>
     </row>
     <row r="698" spans="2:12" x14ac:dyDescent="0.45">
@@ -53190,7 +53190,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L698">
-        <v>0.27916896495604393</v>
+        <v>0.37369627749851897</v>
       </c>
     </row>
     <row r="699" spans="2:12" x14ac:dyDescent="0.45">
@@ -53213,7 +53213,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L699">
-        <v>0.29881577683333332</v>
+        <v>0.38427214669715015</v>
       </c>
     </row>
     <row r="700" spans="2:12" x14ac:dyDescent="0.45">
@@ -53236,7 +53236,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L700">
-        <v>0.29847689699999996</v>
+        <v>0.4056180724722328</v>
       </c>
     </row>
     <row r="701" spans="2:12" x14ac:dyDescent="0.45">
@@ -53259,7 +53259,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L701">
-        <v>0.32696561652830192</v>
+        <v>0.47572034020201476</v>
       </c>
     </row>
     <row r="702" spans="2:12" x14ac:dyDescent="0.45">
@@ -53282,7 +53282,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L702">
-        <v>0.31946744537547894</v>
+        <v>0.37908336668958792</v>
       </c>
     </row>
     <row r="703" spans="2:12" x14ac:dyDescent="0.45">
@@ -53305,7 +53305,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L703">
-        <v>0.25041226076666667</v>
+        <v>0.32172299865550041</v>
       </c>
     </row>
     <row r="704" spans="2:12" x14ac:dyDescent="0.45">
@@ -53328,7 +53328,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L704">
-        <v>0.30815091692307695</v>
+        <v>0.33935842070656402</v>
       </c>
     </row>
     <row r="705" spans="2:12" x14ac:dyDescent="0.45">
@@ -53351,7 +53351,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L705">
-        <v>0.28344232793534485</v>
+        <v>0.40866058546662265</v>
       </c>
     </row>
     <row r="706" spans="2:12" x14ac:dyDescent="0.45">
@@ -53374,7 +53374,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L706">
-        <v>0.28744242105347595</v>
+        <v>0.37189157031534964</v>
       </c>
     </row>
     <row r="707" spans="2:12" x14ac:dyDescent="0.45">
@@ -53397,7 +53397,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L707">
-        <v>0.33237277964503048</v>
+        <v>0.42528165630884407</v>
       </c>
     </row>
     <row r="708" spans="2:12" x14ac:dyDescent="0.45">
@@ -53420,7 +53420,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L708">
-        <v>0.29212029054414784</v>
+        <v>0.42416344567966718</v>
       </c>
     </row>
     <row r="709" spans="2:12" x14ac:dyDescent="0.45">
@@ -53443,7 +53443,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L709">
-        <v>0.20019164012612611</v>
+        <v>0.33785880235147708</v>
       </c>
     </row>
     <row r="710" spans="2:12" x14ac:dyDescent="0.45">
@@ -53466,7 +53466,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L710">
-        <v>0.30765301984620597</v>
+        <v>0.40474460167340448</v>
       </c>
     </row>
     <row r="711" spans="2:12" x14ac:dyDescent="0.45">
@@ -53489,7 +53489,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L711">
-        <v>0.32577484710911481</v>
+        <v>0.41960808141112532</v>
       </c>
     </row>
     <row r="712" spans="2:12" x14ac:dyDescent="0.45">
@@ -53512,7 +53512,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L712">
-        <v>0.23609252546148948</v>
+        <v>0.33263381680570242</v>
       </c>
     </row>
     <row r="713" spans="2:12" x14ac:dyDescent="0.45">
@@ -53535,7 +53535,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L713">
-        <v>0.26763628712499998</v>
+        <v>0.32343981254389931</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51F76C6E-27DB-4B90-8F87-EDEB13EEBA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0A71042-511D-4C59-A7D6-899211F623A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D3C59EAB-8C33-44A9-BADF-11F515188EA9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A7423318-47EE-4FCE-9A38-D7629F1A90A1}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3935,7 +3935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F342E020-9B8E-46E4-85BA-7412D67F314C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA5BDDEA-B31F-4F90-91C0-5B8E8D66520E}">
   <dimension ref="B9:T393"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22034,7 +22034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0337EF5-B1EF-46D3-B30C-738A7BE24418}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9580E4D5-7E24-46BC-A683-E3F808281251}">
   <dimension ref="B9:T713"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -52100,7 +52100,7 @@
         <v>33</v>
       </c>
       <c r="L660">
-        <v>0.1919475549077887</v>
+        <v>0.19194755490778873</v>
       </c>
     </row>
     <row r="661" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DADD377F-205C-4F55-897A-67F6E365D8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B44E3ED-0E43-42E1-9484-0D59DA1DB222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2DF109F0-88A5-40C0-AE64-34517201A74E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6282AA69-7E7C-4B4A-9C6B-EC583AF05505}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3479,7 +3479,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC8717C8-4D9A-4410-B40E-11C3D4A215B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70264E9-9893-4EBF-A4A6-EF22A8DC6D5C}">
   <dimension ref="B9:T266"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15537,7 +15537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DCB4876-D09B-4EC1-B4DB-6FFCBE703C56}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569296A4-5F6B-4F77-A269-C4C1F2CAAEE1}">
   <dimension ref="B9:T586"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40803,7 +40803,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L561">
-        <v>0.39895126255821028</v>
+        <v>0.3989512625582104</v>
       </c>
     </row>
     <row r="562" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B44E3ED-0E43-42E1-9484-0D59DA1DB222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBD954AE-CB56-4566-A2C4-E7B934830694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6282AA69-7E7C-4B4A-9C6B-EC583AF05505}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{01DD8B29-20EB-4D46-881E-0E6C7655B509}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3479,7 +3479,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70264E9-9893-4EBF-A4A6-EF22A8DC6D5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8AE9531-8CFD-40D5-930F-FACCF631D437}">
   <dimension ref="B9:T266"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3558,7 +3558,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.10697760000000002</v>
+        <v>9.0930960000000005E-2</v>
       </c>
       <c r="F11">
         <v>3583</v>
@@ -3614,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.10697760000000002</v>
+        <v>9.0930960000000005E-2</v>
       </c>
       <c r="F12">
         <v>3583</v>
@@ -3670,7 +3670,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.10697760000000002</v>
+        <v>9.0930960000000005E-2</v>
       </c>
       <c r="F13">
         <v>3583</v>
@@ -3726,7 +3726,7 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.33854309999999999</v>
+        <v>0.28776163499999996</v>
       </c>
       <c r="F14">
         <v>1967</v>
@@ -3782,7 +3782,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.33854309999999999</v>
+        <v>0.28776163499999996</v>
       </c>
       <c r="F15">
         <v>1967</v>
@@ -3838,7 +3838,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.12403200000000003</v>
+        <v>0.10542720000000003</v>
       </c>
       <c r="F16">
         <v>3583</v>
@@ -3894,7 +3894,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.11162880000000001</v>
+        <v>9.4884479999999993E-2</v>
       </c>
       <c r="F17">
         <v>3583</v>
@@ -3950,7 +3950,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.10542720000000003</v>
+        <v>8.9613120000000032E-2</v>
       </c>
       <c r="F18">
         <v>3583</v>
@@ -4006,7 +4006,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.10542720000000003</v>
+        <v>8.9613120000000032E-2</v>
       </c>
       <c r="F19">
         <v>3583</v>
@@ -4062,7 +4062,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.10542720000000003</v>
+        <v>8.9613120000000032E-2</v>
       </c>
       <c r="F20">
         <v>3583</v>
@@ -4118,7 +4118,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.10542720000000003</v>
+        <v>8.9613120000000032E-2</v>
       </c>
       <c r="F21">
         <v>3583</v>
@@ -4174,7 +4174,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F22">
         <v>3583</v>
@@ -4230,7 +4230,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F23">
         <v>3583</v>
@@ -4286,7 +4286,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F24">
         <v>3583</v>
@@ -4342,7 +4342,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F25">
         <v>3583</v>
@@ -4398,7 +4398,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F26">
         <v>3583</v>
@@ -4454,7 +4454,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F27">
         <v>3583</v>
@@ -4510,7 +4510,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F28">
         <v>3583</v>
@@ -4566,7 +4566,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F29">
         <v>3583</v>
@@ -4622,7 +4622,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F30">
         <v>3583</v>
@@ -4678,7 +4678,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F31">
         <v>3583</v>
@@ -4734,7 +4734,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F32">
         <v>3583</v>
@@ -4790,7 +4790,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F33">
         <v>3583</v>
@@ -4846,7 +4846,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F34">
         <v>3583</v>
@@ -4902,7 +4902,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F35">
         <v>3583</v>
@@ -4958,7 +4958,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F36">
         <v>3583</v>
@@ -5014,7 +5014,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F37">
         <v>3583</v>
@@ -5070,7 +5070,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F38">
         <v>3583</v>
@@ -5126,7 +5126,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F39">
         <v>3583</v>
@@ -5182,7 +5182,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F40">
         <v>3583</v>
@@ -5238,7 +5238,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F41">
         <v>3583</v>
@@ -5294,7 +5294,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F42">
         <v>3583</v>
@@ -5350,7 +5350,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F43">
         <v>3583</v>
@@ -5406,7 +5406,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F44">
         <v>3583</v>
@@ -5462,7 +5462,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F45">
         <v>3583</v>
@@ -5518,7 +5518,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F46">
         <v>3583</v>
@@ -5574,7 +5574,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F47">
         <v>3583</v>
@@ -5630,7 +5630,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F48">
         <v>3583</v>
@@ -5686,7 +5686,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F49">
         <v>3583</v>
@@ -5742,7 +5742,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F50">
         <v>3583</v>
@@ -5798,7 +5798,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F51">
         <v>3583</v>
@@ -5854,7 +5854,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F52">
         <v>3583</v>
@@ -5910,7 +5910,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F53">
         <v>3583</v>
@@ -5966,7 +5966,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F54">
         <v>3583</v>
@@ -6022,7 +6022,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F55">
         <v>3583</v>
@@ -6078,7 +6078,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F56">
         <v>3583</v>
@@ -6134,7 +6134,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F57">
         <v>3583</v>
@@ -6190,7 +6190,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F58">
         <v>3583</v>
@@ -6246,7 +6246,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F59">
         <v>3583</v>
@@ -6302,7 +6302,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F60">
         <v>3583</v>
@@ -6358,7 +6358,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F61">
         <v>3583</v>
@@ -6414,7 +6414,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F62">
         <v>3583</v>
@@ -6470,7 +6470,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F63">
         <v>3583</v>
@@ -6526,7 +6526,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F64">
         <v>3583</v>
@@ -6582,7 +6582,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F65">
         <v>3583</v>
@@ -6638,7 +6638,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F66">
         <v>3583</v>
@@ -6694,7 +6694,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F67">
         <v>3583</v>
@@ -6750,7 +6750,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>0.10914816000000002</v>
+        <v>9.2775936000000017E-2</v>
       </c>
       <c r="F68">
         <v>3583</v>
@@ -6806,19 +6806,19 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>0.33614100000000002</v>
+        <v>0.27895725000000005</v>
       </c>
       <c r="F69">
-        <v>1726</v>
+        <v>1923</v>
       </c>
       <c r="G69">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="H69">
-        <v>2.5499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="I69">
-        <v>0.82269999999999999</v>
+        <v>0.80844999999999989</v>
       </c>
       <c r="J69" t="s">
         <v>81</v>
@@ -6862,19 +6862,19 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>0.33614100000000002</v>
+        <v>0.27895725000000005</v>
       </c>
       <c r="F70">
-        <v>1726</v>
+        <v>1923</v>
       </c>
       <c r="G70">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="H70">
-        <v>2.5499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="I70">
-        <v>0.82269999999999999</v>
+        <v>0.80844999999999989</v>
       </c>
       <c r="J70" t="s">
         <v>82</v>
@@ -6918,19 +6918,19 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>0.2879562</v>
+        <v>0.23417670000000002</v>
       </c>
       <c r="F71">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G71">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H71">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I71">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J71" t="s">
         <v>83</v>
@@ -6974,19 +6974,19 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.2879562</v>
+        <v>0.23417670000000002</v>
       </c>
       <c r="F72">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G72">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H72">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I72">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J72" t="s">
         <v>84</v>
@@ -7030,19 +7030,19 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>0.31890299999999999</v>
+        <v>0.26465175000000002</v>
       </c>
       <c r="F73">
-        <v>1726</v>
+        <v>1923</v>
       </c>
       <c r="G73">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="H73">
-        <v>2.5499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="I73">
-        <v>0.82269999999999999</v>
+        <v>0.80844999999999989</v>
       </c>
       <c r="J73" t="s">
         <v>85</v>
@@ -7086,19 +7086,19 @@
         <v>14</v>
       </c>
       <c r="E74">
-        <v>0.31890299999999999</v>
+        <v>0.26465175000000002</v>
       </c>
       <c r="F74">
-        <v>1726</v>
+        <v>1923</v>
       </c>
       <c r="G74">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="H74">
-        <v>2.5499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="I74">
-        <v>0.82269999999999999</v>
+        <v>0.80844999999999989</v>
       </c>
       <c r="J74" t="s">
         <v>86</v>
@@ -7142,19 +7142,19 @@
         <v>14</v>
       </c>
       <c r="E75">
-        <v>0.2879562</v>
+        <v>0.23417670000000002</v>
       </c>
       <c r="F75">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G75">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H75">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I75">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J75" t="s">
         <v>87</v>
@@ -7198,19 +7198,19 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>0.2879562</v>
+        <v>0.23417670000000002</v>
       </c>
       <c r="F76">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G76">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H76">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I76">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J76" t="s">
         <v>88</v>
@@ -7254,19 +7254,19 @@
         <v>14</v>
       </c>
       <c r="E77">
-        <v>0.3035214</v>
+        <v>0.24683490000000002</v>
       </c>
       <c r="F77">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G77">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H77">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I77">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J77" t="s">
         <v>89</v>
@@ -7310,19 +7310,19 @@
         <v>14</v>
       </c>
       <c r="E78">
-        <v>0.33614100000000002</v>
+        <v>0.27895725000000005</v>
       </c>
       <c r="F78">
-        <v>1726</v>
+        <v>1923</v>
       </c>
       <c r="G78">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="H78">
-        <v>2.5499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="I78">
-        <v>0.82269999999999999</v>
+        <v>0.80844999999999989</v>
       </c>
       <c r="J78" t="s">
         <v>90</v>
@@ -7366,19 +7366,19 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>0.2879562</v>
+        <v>0.23417670000000002</v>
       </c>
       <c r="F79">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G79">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H79">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I79">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J79" t="s">
         <v>91</v>
@@ -7422,19 +7422,19 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>0.2879562</v>
+        <v>0.23417670000000002</v>
       </c>
       <c r="F80">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G80">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H80">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I80">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J80" t="s">
         <v>92</v>
@@ -7478,19 +7478,19 @@
         <v>14</v>
       </c>
       <c r="E81">
-        <v>0.33614100000000002</v>
+        <v>0.27895725000000005</v>
       </c>
       <c r="F81">
-        <v>1726</v>
+        <v>1923</v>
       </c>
       <c r="G81">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="H81">
-        <v>2.5499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="I81">
-        <v>0.82269999999999999</v>
+        <v>0.80844999999999989</v>
       </c>
       <c r="J81" t="s">
         <v>93</v>
@@ -7534,19 +7534,19 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>0.33614100000000002</v>
+        <v>0.27895725000000005</v>
       </c>
       <c r="F82">
-        <v>1726</v>
+        <v>1923</v>
       </c>
       <c r="G82">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="H82">
-        <v>2.5499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="I82">
-        <v>0.82269999999999999</v>
+        <v>0.80844999999999989</v>
       </c>
       <c r="J82" t="s">
         <v>94</v>
@@ -7590,7 +7590,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0.34045050000000004</v>
+        <v>0.28938292500000001</v>
       </c>
       <c r="F83">
         <v>1726</v>
@@ -7646,7 +7646,7 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <v>0.34045050000000004</v>
+        <v>0.28938292500000001</v>
       </c>
       <c r="F84">
         <v>1726</v>
@@ -7702,7 +7702,7 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>0.30741269999999998</v>
+        <v>0.26130079500000003</v>
       </c>
       <c r="F85">
         <v>1967</v>
@@ -7758,19 +7758,19 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>0.31890299999999999</v>
+        <v>0.26465175000000002</v>
       </c>
       <c r="F86">
-        <v>1726</v>
+        <v>1923</v>
       </c>
       <c r="G86">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="H86">
-        <v>2.5499999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="I86">
-        <v>0.82269999999999999</v>
+        <v>0.80844999999999989</v>
       </c>
       <c r="J86" t="s">
         <v>98</v>
@@ -7814,19 +7814,19 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <v>0.2879562</v>
+        <v>0.23417670000000002</v>
       </c>
       <c r="F87">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G87">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H87">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I87">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J87" t="s">
         <v>99</v>
@@ -7870,19 +7870,19 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.3035214</v>
+        <v>0.24683490000000002</v>
       </c>
       <c r="F88">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G88">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H88">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I88">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J88" t="s">
         <v>100</v>
@@ -7926,7 +7926,7 @@
         <v>14</v>
       </c>
       <c r="E89">
-        <v>0.12248160000000004</v>
+        <v>0.10410936000000003</v>
       </c>
       <c r="F89">
         <v>3583</v>
@@ -7982,7 +7982,7 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.35337900000000005</v>
+        <v>0.30037214999999995</v>
       </c>
       <c r="F90">
         <v>1726</v>
@@ -8038,7 +8038,7 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.35337900000000005</v>
+        <v>0.30037214999999995</v>
       </c>
       <c r="F91">
         <v>1726</v>
@@ -8094,7 +8094,7 @@
         <v>14</v>
       </c>
       <c r="E92">
-        <v>0.35337899999999989</v>
+        <v>0.30037214999999995</v>
       </c>
       <c r="F92">
         <v>1726</v>
@@ -8150,7 +8150,7 @@
         <v>14</v>
       </c>
       <c r="E93">
-        <v>0.36199800000000004</v>
+        <v>0.30769830000000004</v>
       </c>
       <c r="F93">
         <v>1726</v>
@@ -8206,7 +8206,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.36199800000000004</v>
+        <v>0.30769830000000004</v>
       </c>
       <c r="F94">
         <v>1726</v>
@@ -8262,7 +8262,7 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.32686920000000003</v>
+        <v>0.27783882000000004</v>
       </c>
       <c r="F95">
         <v>1967</v>
@@ -8318,7 +8318,7 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.33854309999999993</v>
+        <v>0.28776163499999996</v>
       </c>
       <c r="F96">
         <v>1967</v>
@@ -8374,7 +8374,7 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0.34632570000000001</v>
+        <v>0.294376845</v>
       </c>
       <c r="F97">
         <v>1967</v>
@@ -8430,7 +8430,7 @@
         <v>14</v>
       </c>
       <c r="E98">
-        <v>0.36199800000000004</v>
+        <v>0.30769830000000004</v>
       </c>
       <c r="F98">
         <v>1726</v>
@@ -8486,7 +8486,7 @@
         <v>14</v>
       </c>
       <c r="E99">
-        <v>0.3749265</v>
+        <v>0.31868752499999997</v>
       </c>
       <c r="F99">
         <v>1726</v>
@@ -8542,7 +8542,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.32686920000000003</v>
+        <v>0.27783882000000004</v>
       </c>
       <c r="F100">
         <v>1967</v>
@@ -8598,7 +8598,7 @@
         <v>14</v>
       </c>
       <c r="E101">
-        <v>0.32686920000000003</v>
+        <v>0.27783882000000004</v>
       </c>
       <c r="F101">
         <v>1967</v>
@@ -8654,7 +8654,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.353379</v>
+        <v>0.30037214999999995</v>
       </c>
       <c r="F102">
         <v>1726</v>
@@ -8710,7 +8710,7 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.353379</v>
+        <v>0.30037214999999995</v>
       </c>
       <c r="F103">
         <v>1726</v>
@@ -8766,7 +8766,7 @@
         <v>14</v>
       </c>
       <c r="E104">
-        <v>0.34632570000000001</v>
+        <v>0.294376845</v>
       </c>
       <c r="F104">
         <v>1967</v>
@@ -8822,7 +8822,7 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.34632570000000001</v>
+        <v>0.294376845</v>
       </c>
       <c r="F105">
         <v>1967</v>
@@ -8878,7 +8878,7 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>0.36199800000000004</v>
+        <v>0.30769830000000004</v>
       </c>
       <c r="F106">
         <v>1726</v>
@@ -8934,7 +8934,7 @@
         <v>14</v>
       </c>
       <c r="E107">
-        <v>0.36199800000000004</v>
+        <v>0.30769830000000004</v>
       </c>
       <c r="F107">
         <v>1726</v>
@@ -8990,7 +8990,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.3749265</v>
+        <v>0.31868752499999997</v>
       </c>
       <c r="F108">
         <v>1726</v>
@@ -9046,7 +9046,7 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>0.35337900000000005</v>
+        <v>0.30037214999999995</v>
       </c>
       <c r="F109">
         <v>1726</v>
@@ -9102,7 +9102,7 @@
         <v>14</v>
       </c>
       <c r="E110">
-        <v>0.35337900000000005</v>
+        <v>0.30037214999999995</v>
       </c>
       <c r="F110">
         <v>1726</v>
@@ -9158,7 +9158,7 @@
         <v>14</v>
       </c>
       <c r="E111">
-        <v>0.38354550000000004</v>
+        <v>0.326013675</v>
       </c>
       <c r="F111">
         <v>1726</v>
@@ -9214,7 +9214,7 @@
         <v>14</v>
       </c>
       <c r="E112">
-        <v>0.3190866</v>
+        <v>0.27122360999999995</v>
       </c>
       <c r="F112">
         <v>1967</v>
@@ -9270,7 +9270,7 @@
         <v>14</v>
       </c>
       <c r="E113">
-        <v>0.35337899999999989</v>
+        <v>0.30037214999999995</v>
       </c>
       <c r="F113">
         <v>1726</v>
@@ -9326,7 +9326,7 @@
         <v>14</v>
       </c>
       <c r="E114">
-        <v>0.3190866</v>
+        <v>0.27122360999999995</v>
       </c>
       <c r="F114">
         <v>1967</v>
@@ -9382,7 +9382,7 @@
         <v>14</v>
       </c>
       <c r="E115">
-        <v>0.33854309999999993</v>
+        <v>0.28776163499999996</v>
       </c>
       <c r="F115">
         <v>1967</v>
@@ -9438,7 +9438,7 @@
         <v>14</v>
       </c>
       <c r="E116">
-        <v>0.36199800000000004</v>
+        <v>0.30769830000000004</v>
       </c>
       <c r="F116">
         <v>1726</v>
@@ -9494,7 +9494,7 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>0.34632570000000001</v>
+        <v>0.294376845</v>
       </c>
       <c r="F117">
         <v>1967</v>
@@ -9550,7 +9550,7 @@
         <v>14</v>
       </c>
       <c r="E118">
-        <v>0.35337899999999989</v>
+        <v>0.30037214999999995</v>
       </c>
       <c r="F118">
         <v>1726</v>
@@ -9606,7 +9606,7 @@
         <v>14</v>
       </c>
       <c r="E119">
-        <v>0.33854309999999993</v>
+        <v>0.28776163499999996</v>
       </c>
       <c r="F119">
         <v>1967</v>
@@ -9662,7 +9662,7 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>0.33854309999999993</v>
+        <v>0.28776163499999996</v>
       </c>
       <c r="F120">
         <v>1967</v>
@@ -9718,7 +9718,7 @@
         <v>14</v>
       </c>
       <c r="E121">
-        <v>0.38354550000000004</v>
+        <v>0.326013675</v>
       </c>
       <c r="F121">
         <v>1726</v>
@@ -9774,7 +9774,7 @@
         <v>14</v>
       </c>
       <c r="E122">
-        <v>0.36199800000000004</v>
+        <v>0.30769830000000004</v>
       </c>
       <c r="F122">
         <v>1726</v>
@@ -9830,7 +9830,7 @@
         <v>14</v>
       </c>
       <c r="E123">
-        <v>0.35337899999999989</v>
+        <v>0.30037214999999995</v>
       </c>
       <c r="F123">
         <v>1726</v>
@@ -9886,7 +9886,7 @@
         <v>14</v>
       </c>
       <c r="E124">
-        <v>0.34632570000000001</v>
+        <v>0.294376845</v>
       </c>
       <c r="F124">
         <v>1967</v>
@@ -9942,7 +9942,7 @@
         <v>14</v>
       </c>
       <c r="E125">
-        <v>0.34632570000000001</v>
+        <v>0.294376845</v>
       </c>
       <c r="F125">
         <v>1967</v>
@@ -9998,7 +9998,7 @@
         <v>14</v>
       </c>
       <c r="E126">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F126">
         <v>1365</v>
@@ -10054,7 +10054,7 @@
         <v>14</v>
       </c>
       <c r="E127">
-        <v>0.53549999999999998</v>
+        <v>0.455175</v>
       </c>
       <c r="F127">
         <v>1365</v>
@@ -10110,7 +10110,7 @@
         <v>14</v>
       </c>
       <c r="E128">
-        <v>0.53549999999999998</v>
+        <v>0.455175</v>
       </c>
       <c r="F128">
         <v>1365</v>
@@ -10166,7 +10166,7 @@
         <v>14</v>
       </c>
       <c r="E129">
-        <v>0.53549999999999998</v>
+        <v>0.455175</v>
       </c>
       <c r="F129">
         <v>1365</v>
@@ -10222,7 +10222,7 @@
         <v>14</v>
       </c>
       <c r="E130">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F130">
         <v>1365</v>
@@ -10278,7 +10278,7 @@
         <v>14</v>
       </c>
       <c r="E131">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F131">
         <v>1365</v>
@@ -10334,7 +10334,7 @@
         <v>14</v>
       </c>
       <c r="E132">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F132">
         <v>1365</v>
@@ -10390,7 +10390,7 @@
         <v>14</v>
       </c>
       <c r="E133">
-        <v>0.4685625000000001</v>
+        <v>0.39827812500000009</v>
       </c>
       <c r="F133">
         <v>1365</v>
@@ -10446,7 +10446,7 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>0.4685625000000001</v>
+        <v>0.39827812500000009</v>
       </c>
       <c r="F134">
         <v>1365</v>
@@ -10502,7 +10502,7 @@
         <v>14</v>
       </c>
       <c r="E135">
-        <v>0.4685625000000001</v>
+        <v>0.39827812500000009</v>
       </c>
       <c r="F135">
         <v>1365</v>
@@ -10558,7 +10558,7 @@
         <v>14</v>
       </c>
       <c r="E136">
-        <v>0.4685625000000001</v>
+        <v>0.39827812500000009</v>
       </c>
       <c r="F136">
         <v>1365</v>
@@ -10614,7 +10614,7 @@
         <v>14</v>
       </c>
       <c r="E137">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F137">
         <v>1365</v>
@@ -10670,7 +10670,7 @@
         <v>14</v>
       </c>
       <c r="E138">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F138">
         <v>1365</v>
@@ -10726,7 +10726,7 @@
         <v>14</v>
       </c>
       <c r="E139">
-        <v>0.48641250000000008</v>
+        <v>0.41345062500000007</v>
       </c>
       <c r="F139">
         <v>1365</v>
@@ -10782,7 +10782,7 @@
         <v>14</v>
       </c>
       <c r="E140">
-        <v>0.48641250000000008</v>
+        <v>0.41345062500000007</v>
       </c>
       <c r="F140">
         <v>1365</v>
@@ -10838,7 +10838,7 @@
         <v>14</v>
       </c>
       <c r="E141">
-        <v>0.48641250000000008</v>
+        <v>0.41345062500000007</v>
       </c>
       <c r="F141">
         <v>1365</v>
@@ -10894,7 +10894,7 @@
         <v>14</v>
       </c>
       <c r="E142">
-        <v>0.53549999999999998</v>
+        <v>0.455175</v>
       </c>
       <c r="F142">
         <v>1365</v>
@@ -10950,7 +10950,7 @@
         <v>14</v>
       </c>
       <c r="E143">
-        <v>0.53549999999999998</v>
+        <v>0.455175</v>
       </c>
       <c r="F143">
         <v>1365</v>
@@ -11006,7 +11006,7 @@
         <v>14</v>
       </c>
       <c r="E144">
-        <v>0.53549999999999998</v>
+        <v>0.455175</v>
       </c>
       <c r="F144">
         <v>1365</v>
@@ -11062,7 +11062,7 @@
         <v>14</v>
       </c>
       <c r="E145">
-        <v>0.40162499999999995</v>
+        <v>0.34138125000000002</v>
       </c>
       <c r="F145">
         <v>1365</v>
@@ -11118,7 +11118,7 @@
         <v>14</v>
       </c>
       <c r="E146">
-        <v>0.40162499999999995</v>
+        <v>0.34138125000000002</v>
       </c>
       <c r="F146">
         <v>1365</v>
@@ -11174,7 +11174,7 @@
         <v>14</v>
       </c>
       <c r="E147">
-        <v>0.4685625000000001</v>
+        <v>0.39827812500000009</v>
       </c>
       <c r="F147">
         <v>1365</v>
@@ -11230,7 +11230,7 @@
         <v>14</v>
       </c>
       <c r="E148">
-        <v>0.48641250000000008</v>
+        <v>0.41345062500000007</v>
       </c>
       <c r="F148">
         <v>1365</v>
@@ -11286,7 +11286,7 @@
         <v>14</v>
       </c>
       <c r="E149">
-        <v>0.4685625000000001</v>
+        <v>0.39827812500000009</v>
       </c>
       <c r="F149">
         <v>1365</v>
@@ -11342,7 +11342,7 @@
         <v>14</v>
       </c>
       <c r="E150">
-        <v>0.4685625000000001</v>
+        <v>0.39827812500000009</v>
       </c>
       <c r="F150">
         <v>1365</v>
@@ -11398,7 +11398,7 @@
         <v>14</v>
       </c>
       <c r="E151">
-        <v>0.53549999999999998</v>
+        <v>0.455175</v>
       </c>
       <c r="F151">
         <v>1365</v>
@@ -11454,7 +11454,7 @@
         <v>14</v>
       </c>
       <c r="E152">
-        <v>0.53549999999999998</v>
+        <v>0.455175</v>
       </c>
       <c r="F152">
         <v>1365</v>
@@ -11510,7 +11510,7 @@
         <v>14</v>
       </c>
       <c r="E153">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F153">
         <v>1365</v>
@@ -11566,7 +11566,7 @@
         <v>14</v>
       </c>
       <c r="E154">
-        <v>0.53549999999999998</v>
+        <v>0.455175</v>
       </c>
       <c r="F154">
         <v>1365</v>
@@ -11622,7 +11622,7 @@
         <v>14</v>
       </c>
       <c r="E155">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F155">
         <v>1365</v>
@@ -11657,7 +11657,7 @@
         <v>14</v>
       </c>
       <c r="E156">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F156">
         <v>1365</v>
@@ -11692,7 +11692,7 @@
         <v>14</v>
       </c>
       <c r="E157">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F157">
         <v>1365</v>
@@ -11727,7 +11727,7 @@
         <v>14</v>
       </c>
       <c r="E158">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F158">
         <v>1365</v>
@@ -11762,7 +11762,7 @@
         <v>14</v>
       </c>
       <c r="E159">
-        <v>0.48641250000000008</v>
+        <v>0.41345062500000007</v>
       </c>
       <c r="F159">
         <v>1365</v>
@@ -11797,7 +11797,7 @@
         <v>14</v>
       </c>
       <c r="E160">
-        <v>0.48641250000000008</v>
+        <v>0.41345062500000007</v>
       </c>
       <c r="F160">
         <v>1365</v>
@@ -11832,7 +11832,7 @@
         <v>14</v>
       </c>
       <c r="E161">
-        <v>0.48641250000000008</v>
+        <v>0.41345062500000007</v>
       </c>
       <c r="F161">
         <v>1365</v>
@@ -11867,7 +11867,7 @@
         <v>14</v>
       </c>
       <c r="E162">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F162">
         <v>1365</v>
@@ -11902,7 +11902,7 @@
         <v>14</v>
       </c>
       <c r="E163">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F163">
         <v>1365</v>
@@ -11937,7 +11937,7 @@
         <v>14</v>
       </c>
       <c r="E164">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F164">
         <v>1365</v>
@@ -11972,7 +11972,7 @@
         <v>14</v>
       </c>
       <c r="E165">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F165">
         <v>1365</v>
@@ -12007,7 +12007,7 @@
         <v>14</v>
       </c>
       <c r="E166">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F166">
         <v>1365</v>
@@ -12042,7 +12042,7 @@
         <v>14</v>
       </c>
       <c r="E167">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F167">
         <v>1365</v>
@@ -12077,7 +12077,7 @@
         <v>14</v>
       </c>
       <c r="E168">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F168">
         <v>1365</v>
@@ -12112,7 +12112,7 @@
         <v>14</v>
       </c>
       <c r="E169">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F169">
         <v>1365</v>
@@ -12147,7 +12147,7 @@
         <v>14</v>
       </c>
       <c r="E170">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F170">
         <v>1365</v>
@@ -12182,7 +12182,7 @@
         <v>14</v>
       </c>
       <c r="E171">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F171">
         <v>1365</v>
@@ -12217,7 +12217,7 @@
         <v>14</v>
       </c>
       <c r="E172">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F172">
         <v>1365</v>
@@ -12252,7 +12252,7 @@
         <v>14</v>
       </c>
       <c r="E173">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F173">
         <v>1365</v>
@@ -12287,7 +12287,7 @@
         <v>14</v>
       </c>
       <c r="E174">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F174">
         <v>1365</v>
@@ -12322,7 +12322,7 @@
         <v>14</v>
       </c>
       <c r="E175">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F175">
         <v>1365</v>
@@ -12357,7 +12357,7 @@
         <v>14</v>
       </c>
       <c r="E176">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F176">
         <v>1365</v>
@@ -12392,7 +12392,7 @@
         <v>14</v>
       </c>
       <c r="E177">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F177">
         <v>1365</v>
@@ -12427,7 +12427,7 @@
         <v>14</v>
       </c>
       <c r="E178">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F178">
         <v>1365</v>
@@ -12462,7 +12462,7 @@
         <v>14</v>
       </c>
       <c r="E179">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F179">
         <v>1365</v>
@@ -12497,7 +12497,7 @@
         <v>14</v>
       </c>
       <c r="E180">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F180">
         <v>1365</v>
@@ -12532,7 +12532,7 @@
         <v>14</v>
       </c>
       <c r="E181">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F181">
         <v>1365</v>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="E182">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F182">
         <v>1365</v>
@@ -12602,7 +12602,7 @@
         <v>14</v>
       </c>
       <c r="E183">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F183">
         <v>1365</v>
@@ -12637,7 +12637,7 @@
         <v>14</v>
       </c>
       <c r="E184">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F184">
         <v>1365</v>
@@ -12672,7 +12672,7 @@
         <v>14</v>
       </c>
       <c r="E185">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F185">
         <v>1365</v>
@@ -12707,7 +12707,7 @@
         <v>14</v>
       </c>
       <c r="E186">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F186">
         <v>1365</v>
@@ -12742,7 +12742,7 @@
         <v>14</v>
       </c>
       <c r="E187">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F187">
         <v>1365</v>
@@ -12777,7 +12777,7 @@
         <v>14</v>
       </c>
       <c r="E188">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F188">
         <v>1365</v>
@@ -12812,7 +12812,7 @@
         <v>14</v>
       </c>
       <c r="E189">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F189">
         <v>1365</v>
@@ -12847,7 +12847,7 @@
         <v>14</v>
       </c>
       <c r="E190">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F190">
         <v>1365</v>
@@ -12882,7 +12882,7 @@
         <v>14</v>
       </c>
       <c r="E191">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F191">
         <v>1365</v>
@@ -12917,7 +12917,7 @@
         <v>14</v>
       </c>
       <c r="E192">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F192">
         <v>1365</v>
@@ -12952,7 +12952,7 @@
         <v>14</v>
       </c>
       <c r="E193">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F193">
         <v>1365</v>
@@ -12987,7 +12987,7 @@
         <v>14</v>
       </c>
       <c r="E194">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F194">
         <v>1365</v>
@@ -13022,7 +13022,7 @@
         <v>14</v>
       </c>
       <c r="E195">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F195">
         <v>1365</v>
@@ -13057,7 +13057,7 @@
         <v>14</v>
       </c>
       <c r="E196">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F196">
         <v>1365</v>
@@ -13092,7 +13092,7 @@
         <v>14</v>
       </c>
       <c r="E197">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F197">
         <v>1365</v>
@@ -13127,7 +13127,7 @@
         <v>14</v>
       </c>
       <c r="E198">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F198">
         <v>1365</v>
@@ -13162,7 +13162,7 @@
         <v>14</v>
       </c>
       <c r="E199">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F199">
         <v>1365</v>
@@ -13197,7 +13197,7 @@
         <v>14</v>
       </c>
       <c r="E200">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F200">
         <v>1365</v>
@@ -13232,7 +13232,7 @@
         <v>14</v>
       </c>
       <c r="E201">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F201">
         <v>1365</v>
@@ -13267,7 +13267,7 @@
         <v>14</v>
       </c>
       <c r="E202">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F202">
         <v>1365</v>
@@ -13302,7 +13302,7 @@
         <v>14</v>
       </c>
       <c r="E203">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F203">
         <v>1365</v>
@@ -13337,7 +13337,7 @@
         <v>14</v>
       </c>
       <c r="E204">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F204">
         <v>1365</v>
@@ -13372,7 +13372,7 @@
         <v>14</v>
       </c>
       <c r="E205">
-        <v>0.51765000000000005</v>
+        <v>0.44000250000000002</v>
       </c>
       <c r="F205">
         <v>1365</v>
@@ -13407,7 +13407,7 @@
         <v>14</v>
       </c>
       <c r="E206">
-        <v>0.28560000000000002</v>
+        <v>0.24276000000000003</v>
       </c>
       <c r="F206">
         <v>1365</v>
@@ -13442,7 +13442,7 @@
         <v>14</v>
       </c>
       <c r="E207">
-        <v>0.28560000000000002</v>
+        <v>0.24276000000000003</v>
       </c>
       <c r="F207">
         <v>1365</v>
@@ -13477,7 +13477,7 @@
         <v>14</v>
       </c>
       <c r="E208">
-        <v>0.32129999999999997</v>
+        <v>0.27310499999999999</v>
       </c>
       <c r="F208">
         <v>1365</v>
@@ -13512,7 +13512,7 @@
         <v>14</v>
       </c>
       <c r="E209">
-        <v>0.32129999999999997</v>
+        <v>0.27310499999999999</v>
       </c>
       <c r="F209">
         <v>1365</v>
@@ -13547,7 +13547,7 @@
         <v>14</v>
       </c>
       <c r="E210">
-        <v>0.32129999999999997</v>
+        <v>0.27310499999999999</v>
       </c>
       <c r="F210">
         <v>1365</v>
@@ -13582,7 +13582,7 @@
         <v>14</v>
       </c>
       <c r="E211">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F211">
         <v>1365</v>
@@ -13617,7 +13617,7 @@
         <v>14</v>
       </c>
       <c r="E212">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F212">
         <v>1365</v>
@@ -13652,7 +13652,7 @@
         <v>14</v>
       </c>
       <c r="E213">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F213">
         <v>1365</v>
@@ -13687,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="E214">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F214">
         <v>1365</v>
@@ -13722,7 +13722,7 @@
         <v>14</v>
       </c>
       <c r="E215">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F215">
         <v>1365</v>
@@ -13757,7 +13757,7 @@
         <v>14</v>
       </c>
       <c r="E216">
-        <v>0.31237499999999996</v>
+        <v>0.26551874999999997</v>
       </c>
       <c r="F216">
         <v>1365</v>
@@ -13792,7 +13792,7 @@
         <v>14</v>
       </c>
       <c r="E217">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F217">
         <v>1365</v>
@@ -13827,7 +13827,7 @@
         <v>14</v>
       </c>
       <c r="E218">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F218">
         <v>1365</v>
@@ -13862,7 +13862,7 @@
         <v>14</v>
       </c>
       <c r="E219">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F219">
         <v>1365</v>
@@ -13897,7 +13897,7 @@
         <v>14</v>
       </c>
       <c r="E220">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F220">
         <v>1365</v>
@@ -13932,7 +13932,7 @@
         <v>14</v>
       </c>
       <c r="E221">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F221">
         <v>1365</v>
@@ -13967,7 +13967,7 @@
         <v>14</v>
       </c>
       <c r="E222">
-        <v>0.31237499999999996</v>
+        <v>0.26551874999999997</v>
       </c>
       <c r="F222">
         <v>1365</v>
@@ -14002,7 +14002,7 @@
         <v>14</v>
       </c>
       <c r="E223">
-        <v>0.31237499999999996</v>
+        <v>0.26551874999999997</v>
       </c>
       <c r="F223">
         <v>1365</v>
@@ -14037,7 +14037,7 @@
         <v>14</v>
       </c>
       <c r="E224">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F224">
         <v>1365</v>
@@ -14072,7 +14072,7 @@
         <v>14</v>
       </c>
       <c r="E225">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F225">
         <v>1365</v>
@@ -14107,7 +14107,7 @@
         <v>14</v>
       </c>
       <c r="E226">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F226">
         <v>1365</v>
@@ -14142,7 +14142,7 @@
         <v>14</v>
       </c>
       <c r="E227">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F227">
         <v>1365</v>
@@ -14177,7 +14177,7 @@
         <v>14</v>
       </c>
       <c r="E228">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F228">
         <v>1365</v>
@@ -14212,7 +14212,7 @@
         <v>14</v>
       </c>
       <c r="E229">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F229">
         <v>1365</v>
@@ -14247,7 +14247,7 @@
         <v>14</v>
       </c>
       <c r="E230">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F230">
         <v>1365</v>
@@ -14282,7 +14282,7 @@
         <v>14</v>
       </c>
       <c r="E231">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F231">
         <v>1365</v>
@@ -14317,7 +14317,7 @@
         <v>14</v>
       </c>
       <c r="E232">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F232">
         <v>1365</v>
@@ -14352,7 +14352,7 @@
         <v>14</v>
       </c>
       <c r="E233">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F233">
         <v>1365</v>
@@ -14387,7 +14387,7 @@
         <v>14</v>
       </c>
       <c r="E234">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F234">
         <v>1365</v>
@@ -14422,7 +14422,7 @@
         <v>14</v>
       </c>
       <c r="E235">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F235">
         <v>1365</v>
@@ -14457,7 +14457,7 @@
         <v>14</v>
       </c>
       <c r="E236">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F236">
         <v>1365</v>
@@ -14492,7 +14492,7 @@
         <v>14</v>
       </c>
       <c r="E237">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F237">
         <v>1365</v>
@@ -14527,7 +14527,7 @@
         <v>14</v>
       </c>
       <c r="E238">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F238">
         <v>1365</v>
@@ -14562,7 +14562,7 @@
         <v>14</v>
       </c>
       <c r="E239">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F239">
         <v>1365</v>
@@ -14597,7 +14597,7 @@
         <v>14</v>
       </c>
       <c r="E240">
-        <v>0.32576250000000001</v>
+        <v>0.27689812499999999</v>
       </c>
       <c r="F240">
         <v>1365</v>
@@ -14632,7 +14632,7 @@
         <v>14</v>
       </c>
       <c r="E241">
-        <v>0.26774999999999999</v>
+        <v>0.2275875</v>
       </c>
       <c r="F241">
         <v>1365</v>
@@ -14667,7 +14667,7 @@
         <v>14</v>
       </c>
       <c r="E242">
-        <v>0.26774999999999999</v>
+        <v>0.2275875</v>
       </c>
       <c r="F242">
         <v>1365</v>
@@ -14702,7 +14702,7 @@
         <v>14</v>
       </c>
       <c r="E243">
-        <v>0.26774999999999999</v>
+        <v>0.2275875</v>
       </c>
       <c r="F243">
         <v>1365</v>
@@ -14737,7 +14737,7 @@
         <v>14</v>
       </c>
       <c r="E244">
-        <v>0.28560000000000002</v>
+        <v>0.24276000000000003</v>
       </c>
       <c r="F244">
         <v>1365</v>
@@ -14772,7 +14772,7 @@
         <v>14</v>
       </c>
       <c r="E245">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F245">
         <v>1365</v>
@@ -14807,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="E246">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F246">
         <v>1365</v>
@@ -14842,7 +14842,7 @@
         <v>14</v>
       </c>
       <c r="E247">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F247">
         <v>1365</v>
@@ -14877,7 +14877,7 @@
         <v>14</v>
       </c>
       <c r="E248">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F248">
         <v>1365</v>
@@ -14912,7 +14912,7 @@
         <v>14</v>
       </c>
       <c r="E249">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F249">
         <v>1365</v>
@@ -14947,7 +14947,7 @@
         <v>14</v>
       </c>
       <c r="E250">
-        <v>0.28560000000000002</v>
+        <v>0.24276000000000003</v>
       </c>
       <c r="F250">
         <v>1365</v>
@@ -14982,7 +14982,7 @@
         <v>14</v>
       </c>
       <c r="E251">
-        <v>0.28560000000000002</v>
+        <v>0.24276000000000003</v>
       </c>
       <c r="F251">
         <v>1365</v>
@@ -15017,7 +15017,7 @@
         <v>14</v>
       </c>
       <c r="E252">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F252">
         <v>1365</v>
@@ -15052,7 +15052,7 @@
         <v>14</v>
       </c>
       <c r="E253">
-        <v>0.29452499999999998</v>
+        <v>0.25034624999999999</v>
       </c>
       <c r="F253">
         <v>1365</v>
@@ -15087,7 +15087,7 @@
         <v>14</v>
       </c>
       <c r="E254">
-        <v>0.28560000000000008</v>
+        <v>0.24276000000000003</v>
       </c>
       <c r="F254">
         <v>1365</v>
@@ -15122,7 +15122,7 @@
         <v>14</v>
       </c>
       <c r="E255">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F255">
         <v>1365</v>
@@ -15157,7 +15157,7 @@
         <v>14</v>
       </c>
       <c r="E256">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F256">
         <v>1365</v>
@@ -15192,7 +15192,7 @@
         <v>14</v>
       </c>
       <c r="E257">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F257">
         <v>1365</v>
@@ -15227,7 +15227,7 @@
         <v>14</v>
       </c>
       <c r="E258">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F258">
         <v>1365</v>
@@ -15262,7 +15262,7 @@
         <v>14</v>
       </c>
       <c r="E259">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F259">
         <v>1365</v>
@@ -15297,7 +15297,7 @@
         <v>14</v>
       </c>
       <c r="E260">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F260">
         <v>1365</v>
@@ -15332,7 +15332,7 @@
         <v>14</v>
       </c>
       <c r="E261">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F261">
         <v>1365</v>
@@ -15367,7 +15367,7 @@
         <v>14</v>
       </c>
       <c r="E262">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F262">
         <v>1365</v>
@@ -15402,7 +15402,7 @@
         <v>14</v>
       </c>
       <c r="E263">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F263">
         <v>1365</v>
@@ -15437,7 +15437,7 @@
         <v>14</v>
       </c>
       <c r="E264">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F264">
         <v>1365</v>
@@ -15472,7 +15472,7 @@
         <v>14</v>
       </c>
       <c r="E265">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F265">
         <v>1365</v>
@@ -15507,7 +15507,7 @@
         <v>14</v>
       </c>
       <c r="E266">
-        <v>0.30345000000000005</v>
+        <v>0.25793250000000006</v>
       </c>
       <c r="F266">
         <v>1365</v>
@@ -15537,7 +15537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569296A4-5F6B-4F77-A269-C4C1F2CAAEE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C63898D-D74E-4D56-A3CD-CD0457031BB7}">
   <dimension ref="B9:T586"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15622,7 +15622,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G11">
-        <v>0.2346</v>
+        <v>0.19941000000000003</v>
       </c>
       <c r="H11">
         <v>5670</v>
@@ -15675,7 +15675,7 @@
         <v>0.04</v>
       </c>
       <c r="G12">
-        <v>0.2601</v>
+        <v>0.22108500000000003</v>
       </c>
       <c r="H12">
         <v>5670</v>
@@ -15728,7 +15728,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="G13">
-        <v>0.28560000000000002</v>
+        <v>0.24276</v>
       </c>
       <c r="H13">
         <v>5670</v>
@@ -15781,7 +15781,7 @@
         <v>0.1663</v>
       </c>
       <c r="G14">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H14">
         <v>5670</v>
@@ -15834,7 +15834,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G15">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H15">
         <v>5670</v>
@@ -15887,7 +15887,7 @@
         <v>0.11652999999999999</v>
       </c>
       <c r="G16">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H16">
         <v>5670</v>
@@ -15940,7 +15940,7 @@
         <v>0.04</v>
       </c>
       <c r="G17">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H17">
         <v>5670</v>
@@ -15993,7 +15993,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G18">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H18">
         <v>5670</v>
@@ -16046,7 +16046,7 @@
         <v>0.09</v>
       </c>
       <c r="G19">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H19">
         <v>5670</v>
@@ -16099,7 +16099,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
       <c r="G20">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H20">
         <v>5670</v>
@@ -16152,7 +16152,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G21">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H21">
         <v>5670</v>
@@ -16205,7 +16205,7 @@
         <v>1.5011700000000001</v>
       </c>
       <c r="G22">
-        <v>0.35699999999999998</v>
+        <v>0.30345</v>
       </c>
       <c r="H22">
         <v>4200</v>
@@ -16258,7 +16258,7 @@
         <v>0.112</v>
       </c>
       <c r="G23">
-        <v>0.33660000000000007</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H23">
         <v>4829.9999999999991</v>
@@ -16311,7 +16311,7 @@
         <v>0.05</v>
       </c>
       <c r="G24">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H24">
         <v>5670</v>
@@ -16364,7 +16364,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G25">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H25">
         <v>4829.9999999999991</v>
@@ -16417,7 +16417,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G26">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H26">
         <v>4829.9999999999991</v>
@@ -16470,7 +16470,7 @@
         <v>0.05</v>
       </c>
       <c r="G27">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H27">
         <v>5670</v>
@@ -16523,7 +16523,7 @@
         <v>0.05</v>
       </c>
       <c r="G28">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H28">
         <v>5670</v>
@@ -16576,7 +16576,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="G29">
-        <v>0.33659999999999995</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H29">
         <v>4829.9999999999991</v>
@@ -16629,7 +16629,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G30">
-        <v>0.31619999999999998</v>
+        <v>0.26876999999999995</v>
       </c>
       <c r="H30">
         <v>4829.9999999999991</v>
@@ -16682,7 +16682,7 @@
         <v>0.05</v>
       </c>
       <c r="G31">
-        <v>0.2601</v>
+        <v>0.221085</v>
       </c>
       <c r="H31">
         <v>5670</v>
@@ -16735,7 +16735,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G32">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H32">
         <v>4829.9999999999991</v>
@@ -16788,7 +16788,7 @@
         <v>0.05</v>
       </c>
       <c r="G33">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H33">
         <v>5670</v>
@@ -16841,7 +16841,7 @@
         <v>0.05</v>
       </c>
       <c r="G34">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H34">
         <v>5670</v>
@@ -16894,7 +16894,7 @@
         <v>0.05</v>
       </c>
       <c r="G35">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H35">
         <v>5670</v>
@@ -16947,7 +16947,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G36">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H36">
         <v>4829.9999999999991</v>
@@ -17000,7 +17000,7 @@
         <v>0.112</v>
       </c>
       <c r="G37">
-        <v>0.33660000000000007</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H37">
         <v>4829.9999999999991</v>
@@ -17053,7 +17053,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G38">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H38">
         <v>4829.9999999999991</v>
@@ -17106,7 +17106,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G39">
-        <v>0.31619999999999998</v>
+        <v>0.26876999999999995</v>
       </c>
       <c r="H39">
         <v>4829.9999999999991</v>
@@ -17159,7 +17159,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G40">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H40">
         <v>4829.9999999999991</v>
@@ -17212,7 +17212,7 @@
         <v>0.05</v>
       </c>
       <c r="G41">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H41">
         <v>5670</v>
@@ -17265,7 +17265,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G42">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H42">
         <v>4829.9999999999991</v>
@@ -17318,7 +17318,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G43">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H43">
         <v>4829.9999999999991</v>
@@ -17371,7 +17371,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G44">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H44">
         <v>4829.9999999999991</v>
@@ -17424,7 +17424,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G45">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H45">
         <v>4829.9999999999991</v>
@@ -17477,7 +17477,7 @@
         <v>0.05</v>
       </c>
       <c r="G46">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H46">
         <v>5670</v>
@@ -17530,7 +17530,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G47">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H47">
         <v>4829.9999999999991</v>
@@ -17583,7 +17583,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G48">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H48">
         <v>4829.9999999999991</v>
@@ -17636,7 +17636,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G49">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H49">
         <v>4829.9999999999991</v>
@@ -17689,7 +17689,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G50">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H50">
         <v>4829.9999999999991</v>
@@ -17742,7 +17742,7 @@
         <v>0.2</v>
       </c>
       <c r="G51">
-        <v>0.2601</v>
+        <v>0.221085</v>
       </c>
       <c r="H51">
         <v>4829.9999999999991</v>
@@ -17795,7 +17795,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="G52">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H52">
         <v>4829.9999999999991</v>
@@ -17848,7 +17848,7 @@
         <v>0.112</v>
       </c>
       <c r="G53">
-        <v>0.33660000000000007</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H53">
         <v>4829.9999999999991</v>
@@ -17901,7 +17901,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="G54">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H54">
         <v>4829.9999999999991</v>
@@ -17954,7 +17954,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G55">
-        <v>0.31619999999999998</v>
+        <v>0.26876999999999995</v>
       </c>
       <c r="H55">
         <v>4829.9999999999991</v>
@@ -18007,7 +18007,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G56">
-        <v>0.31619999999999998</v>
+        <v>0.26876999999999995</v>
       </c>
       <c r="H56">
         <v>4829.9999999999991</v>
@@ -18060,7 +18060,7 @@
         <v>0.05</v>
       </c>
       <c r="G57">
-        <v>0.2346</v>
+        <v>0.19940999999999998</v>
       </c>
       <c r="H57">
         <v>5670</v>
@@ -18113,7 +18113,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G58">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H58">
         <v>4829.9999999999991</v>
@@ -18166,7 +18166,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G59">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H59">
         <v>4829.9999999999991</v>
@@ -18219,7 +18219,7 @@
         <v>0.05</v>
       </c>
       <c r="G60">
-        <v>0.28560000000000002</v>
+        <v>0.24276</v>
       </c>
       <c r="H60">
         <v>5670</v>
@@ -18272,7 +18272,7 @@
         <v>0.05</v>
       </c>
       <c r="G61">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H61">
         <v>5670</v>
@@ -18325,7 +18325,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G62">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H62">
         <v>4829.9999999999991</v>
@@ -18378,7 +18378,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="G63">
-        <v>0.31619999999999998</v>
+        <v>0.26876999999999995</v>
       </c>
       <c r="H63">
         <v>4829.9999999999991</v>
@@ -18431,7 +18431,7 @@
         <v>0.05</v>
       </c>
       <c r="G64">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H64">
         <v>5670</v>
@@ -18484,7 +18484,7 @@
         <v>0.05</v>
       </c>
       <c r="G65">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H65">
         <v>5670</v>
@@ -18537,7 +18537,7 @@
         <v>0.08</v>
       </c>
       <c r="G66">
-        <v>0.31619999999999998</v>
+        <v>0.26876999999999995</v>
       </c>
       <c r="H66">
         <v>4829.9999999999991</v>
@@ -18590,7 +18590,7 @@
         <v>0.05</v>
       </c>
       <c r="G67">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H67">
         <v>5670</v>
@@ -18643,7 +18643,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G68">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H68">
         <v>4829.9999999999991</v>
@@ -18696,7 +18696,7 @@
         <v>0.05</v>
       </c>
       <c r="G69">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H69">
         <v>5670</v>
@@ -18749,7 +18749,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="G70">
-        <v>0.31619999999999998</v>
+        <v>0.26876999999999995</v>
       </c>
       <c r="H70">
         <v>4829.9999999999991</v>
@@ -18802,7 +18802,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G71">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H71">
         <v>4829.9999999999991</v>
@@ -18855,7 +18855,7 @@
         <v>0.05</v>
       </c>
       <c r="G72">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H72">
         <v>5670</v>
@@ -18908,7 +18908,7 @@
         <v>0.05</v>
       </c>
       <c r="G73">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H73">
         <v>5670</v>
@@ -18961,7 +18961,7 @@
         <v>0.05</v>
       </c>
       <c r="G74">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H74">
         <v>5670</v>
@@ -19014,7 +19014,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G75">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H75">
         <v>4829.9999999999991</v>
@@ -19067,7 +19067,7 @@
         <v>0.112</v>
       </c>
       <c r="G76">
-        <v>0.33660000000000007</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H76">
         <v>4829.9999999999991</v>
@@ -19120,7 +19120,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G77">
-        <v>0.31619999999999998</v>
+        <v>0.26876999999999995</v>
       </c>
       <c r="H77">
         <v>4829.9999999999991</v>
@@ -19173,7 +19173,7 @@
         <v>0.05</v>
       </c>
       <c r="G78">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H78">
         <v>5670</v>
@@ -19226,7 +19226,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="G79">
-        <v>0.31619999999999998</v>
+        <v>0.26876999999999995</v>
       </c>
       <c r="H79">
         <v>4829.9999999999991</v>
@@ -19279,7 +19279,7 @@
         <v>0.14899999999999999</v>
       </c>
       <c r="G80">
-        <v>0.35189999999999999</v>
+        <v>0.29911499999999996</v>
       </c>
       <c r="H80">
         <v>3174</v>
@@ -19332,7 +19332,7 @@
         <v>0.05</v>
       </c>
       <c r="G81">
-        <v>0.3417</v>
+        <v>0.29044500000000001</v>
       </c>
       <c r="H81">
         <v>3726</v>
@@ -19385,7 +19385,7 @@
         <v>3.85E-2</v>
       </c>
       <c r="G82">
-        <v>0.35189999999999999</v>
+        <v>0.29911499999999996</v>
       </c>
       <c r="H82">
         <v>3726</v>
@@ -19438,7 +19438,7 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="G83">
-        <v>0.40800000000000003</v>
+        <v>0.3468</v>
       </c>
       <c r="H83">
         <v>5796</v>
@@ -19491,7 +19491,7 @@
         <v>0.54300000000000004</v>
       </c>
       <c r="G84">
-        <v>0.44369999999999998</v>
+        <v>0.37714499999999995</v>
       </c>
       <c r="H84">
         <v>5040</v>
@@ -19544,7 +19544,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G85">
-        <v>0.44369999999999998</v>
+        <v>0.37714499999999995</v>
       </c>
       <c r="H85">
         <v>5040</v>
@@ -19597,7 +19597,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G86">
-        <v>0.28560000000000002</v>
+        <v>0.24276</v>
       </c>
       <c r="H86">
         <v>2760</v>
@@ -19650,7 +19650,7 @@
         <v>0.03</v>
       </c>
       <c r="G87">
-        <v>0.27540000000000003</v>
+        <v>0.23409000000000002</v>
       </c>
       <c r="H87">
         <v>3240</v>
@@ -19703,7 +19703,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G88">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H88">
         <v>2760</v>
@@ -19756,7 +19756,7 @@
         <v>0.25</v>
       </c>
       <c r="G89">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H89">
         <v>2760</v>
@@ -19809,7 +19809,7 @@
         <v>0.25</v>
       </c>
       <c r="G90">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H90">
         <v>2760</v>
@@ -19862,7 +19862,7 @@
         <v>0.5</v>
       </c>
       <c r="G91">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H91">
         <v>2760</v>
@@ -19915,7 +19915,7 @@
         <v>0.25</v>
       </c>
       <c r="G92">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H92">
         <v>2760</v>
@@ -19968,7 +19968,7 @@
         <v>0.25</v>
       </c>
       <c r="G93">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H93">
         <v>2760</v>
@@ -20021,7 +20021,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="G94">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H94">
         <v>2760</v>
@@ -20074,7 +20074,7 @@
         <v>0.189</v>
       </c>
       <c r="G95">
-        <v>0.32639999999999997</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H95">
         <v>2760</v>
@@ -20127,7 +20127,7 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="G96">
-        <v>0.32640000000000008</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H96">
         <v>2760</v>
@@ -20180,7 +20180,7 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="G97">
-        <v>0.34143157894736847</v>
+        <v>0.29021684210526316</v>
       </c>
       <c r="H97">
         <v>2494.7368421052633</v>
@@ -20233,7 +20233,7 @@
         <v>0.35</v>
       </c>
       <c r="G98">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H98">
         <v>2400</v>
@@ -20286,7 +20286,7 @@
         <v>0.35</v>
       </c>
       <c r="G99">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H99">
         <v>2400</v>
@@ -20339,7 +20339,7 @@
         <v>0.27</v>
       </c>
       <c r="G100">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H100">
         <v>2760</v>
@@ -20392,7 +20392,7 @@
         <v>0.21299999999999999</v>
       </c>
       <c r="G101">
-        <v>0.33659999999999995</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H101">
         <v>2760</v>
@@ -20445,7 +20445,7 @@
         <v>0.44600000000000001</v>
       </c>
       <c r="G102">
-        <v>0.33561659192825111</v>
+        <v>0.28527410313901341</v>
       </c>
       <c r="H102">
         <v>2806.2780269058294</v>
@@ -20498,7 +20498,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G103">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H103">
         <v>3240</v>
@@ -20551,7 +20551,7 @@
         <v>0.28699999999999998</v>
       </c>
       <c r="G104">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H104">
         <v>2760</v>
@@ -20604,7 +20604,7 @@
         <v>0.14899999999999999</v>
       </c>
       <c r="G105">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H105">
         <v>2760</v>
@@ -20657,7 +20657,7 @@
         <v>0.10579999999999999</v>
       </c>
       <c r="G106">
-        <v>0.34294366729678644</v>
+        <v>0.29150211720226843</v>
       </c>
       <c r="H106">
         <v>2941.4744801512288</v>
@@ -20710,7 +20710,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="G107">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H107">
         <v>2760</v>
@@ -20763,7 +20763,7 @@
         <v>0.1226</v>
       </c>
       <c r="G108">
-        <v>0.34283980424143562</v>
+        <v>0.29141383360522027</v>
       </c>
       <c r="H108">
         <v>2946.3621533442088</v>
@@ -20816,7 +20816,7 @@
         <v>0.156</v>
       </c>
       <c r="G109">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H109">
         <v>2760</v>
@@ -20869,7 +20869,7 @@
         <v>0.156</v>
       </c>
       <c r="G110">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H110">
         <v>2760</v>
@@ -20922,7 +20922,7 @@
         <v>0.19850000000000001</v>
       </c>
       <c r="G111">
-        <v>0.34425642317380356</v>
+        <v>0.29261795969773302</v>
       </c>
       <c r="H111">
         <v>2879.6977329974811</v>
@@ -20975,7 +20975,7 @@
         <v>0.10249999999999999</v>
       </c>
       <c r="G112">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H112">
         <v>2760</v>
@@ -21028,7 +21028,7 @@
         <v>0.11</v>
       </c>
       <c r="G113">
-        <v>0.34680000000000005</v>
+        <v>0.2947800000000001</v>
       </c>
       <c r="H113">
         <v>2760</v>
@@ -21081,7 +21081,7 @@
         <v>0.65300000000000002</v>
       </c>
       <c r="G114">
-        <v>0.34680000000000005</v>
+        <v>0.29477999999999999</v>
       </c>
       <c r="H114">
         <v>2760</v>
@@ -21134,7 +21134,7 @@
         <v>0.29799999999999999</v>
       </c>
       <c r="G115">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H115">
         <v>2760</v>
@@ -21187,7 +21187,7 @@
         <v>0.14499999999999999</v>
       </c>
       <c r="G116">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H116">
         <v>2760</v>
@@ -21240,7 +21240,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G117">
-        <v>0.35903999999999997</v>
+        <v>0.30518400000000001</v>
       </c>
       <c r="H117">
         <v>2544</v>
@@ -21293,7 +21293,7 @@
         <v>0.438</v>
       </c>
       <c r="G118">
-        <v>0.3468</v>
+        <v>0.29477999999999999</v>
       </c>
       <c r="H118">
         <v>2760</v>
@@ -21346,7 +21346,7 @@
         <v>0.46029999999999999</v>
       </c>
       <c r="G119">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H119">
         <v>2760</v>
@@ -21399,7 +21399,7 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="G120">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H120">
         <v>2760</v>
@@ -21452,7 +21452,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G121">
-        <v>0.33660000000000007</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H121">
         <v>3240</v>
@@ -21505,7 +21505,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="G122">
-        <v>0.34329785407725327</v>
+        <v>0.29180317596566524</v>
       </c>
       <c r="H122">
         <v>2924.8068669527897</v>
@@ -21558,7 +21558,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="G123">
-        <v>0.34594158415841592</v>
+        <v>0.29405034653465345</v>
       </c>
       <c r="H123">
         <v>2800.3960396039606</v>
@@ -21611,7 +21611,7 @@
         <v>0.11</v>
       </c>
       <c r="G124">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H124">
         <v>2760</v>
@@ -21664,7 +21664,7 @@
         <v>7.3799999999999991E-2</v>
       </c>
       <c r="G125">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H125">
         <v>3240</v>
@@ -21717,7 +21717,7 @@
         <v>0.03</v>
       </c>
       <c r="G126">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H126">
         <v>3240</v>
@@ -21770,7 +21770,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="G127">
-        <v>0.34680000000000005</v>
+        <v>0.29477999999999999</v>
       </c>
       <c r="H127">
         <v>2760</v>
@@ -21823,7 +21823,7 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="G128">
-        <v>0.34605948477751763</v>
+        <v>0.29415056206088996</v>
       </c>
       <c r="H128">
         <v>2794.8477751756441</v>
@@ -21876,7 +21876,7 @@
         <v>0.112</v>
       </c>
       <c r="G129">
-        <v>0.34680000000000005</v>
+        <v>0.29477999999999999</v>
       </c>
       <c r="H129">
         <v>2760</v>
@@ -21929,7 +21929,7 @@
         <v>0.112</v>
       </c>
       <c r="G130">
-        <v>0.34680000000000005</v>
+        <v>0.29477999999999999</v>
       </c>
       <c r="H130">
         <v>2760</v>
@@ -21982,7 +21982,7 @@
         <v>0.112</v>
       </c>
       <c r="G131">
-        <v>0.34680000000000005</v>
+        <v>0.29477999999999999</v>
       </c>
       <c r="H131">
         <v>2760</v>
@@ -22035,7 +22035,7 @@
         <v>0.3</v>
       </c>
       <c r="G132">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H132">
         <v>2760</v>
@@ -22088,7 +22088,7 @@
         <v>0.64199999999998891</v>
       </c>
       <c r="G133">
-        <v>0.36719999999999997</v>
+        <v>0.31211999999999995</v>
       </c>
       <c r="H133">
         <v>2400</v>
@@ -22141,7 +22141,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="G134">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H134">
         <v>2760</v>
@@ -22194,7 +22194,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="G135">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H135">
         <v>2760</v>
@@ -22247,7 +22247,7 @@
         <v>0.25900000000000001</v>
       </c>
       <c r="G136">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H136">
         <v>2760</v>
@@ -22300,7 +22300,7 @@
         <v>0.112</v>
       </c>
       <c r="G137">
-        <v>0.34680000000000005</v>
+        <v>0.29477999999999999</v>
       </c>
       <c r="H137">
         <v>2760</v>
@@ -22353,7 +22353,7 @@
         <v>0.7</v>
       </c>
       <c r="G138">
-        <v>0.39780000000000004</v>
+        <v>0.33813000000000004</v>
       </c>
       <c r="H138">
         <v>2640</v>
@@ -22406,7 +22406,7 @@
         <v>0.7</v>
       </c>
       <c r="G139">
-        <v>0.39780000000000004</v>
+        <v>0.33813000000000004</v>
       </c>
       <c r="H139">
         <v>2640</v>
@@ -22459,7 +22459,7 @@
         <v>0.5</v>
       </c>
       <c r="G140">
-        <v>0.37740000000000001</v>
+        <v>0.32079000000000002</v>
       </c>
       <c r="H140">
         <v>2640</v>
@@ -22512,7 +22512,7 @@
         <v>0.5</v>
       </c>
       <c r="G141">
-        <v>0.37740000000000001</v>
+        <v>0.32079000000000002</v>
       </c>
       <c r="H141">
         <v>2640</v>
@@ -22565,7 +22565,7 @@
         <v>0.7</v>
       </c>
       <c r="G142">
-        <v>0.37740000000000001</v>
+        <v>0.32079000000000002</v>
       </c>
       <c r="H142">
         <v>2640</v>
@@ -22618,7 +22618,7 @@
         <v>1</v>
       </c>
       <c r="G143">
-        <v>0.37740000000000001</v>
+        <v>0.32079000000000002</v>
       </c>
       <c r="H143">
         <v>2640</v>
@@ -22671,7 +22671,7 @@
         <v>0.6</v>
       </c>
       <c r="G144">
-        <v>0.37740000000000001</v>
+        <v>0.32079000000000002</v>
       </c>
       <c r="H144">
         <v>2640</v>
@@ -22724,7 +22724,7 @@
         <v>0.6</v>
       </c>
       <c r="G145">
-        <v>0.37740000000000001</v>
+        <v>0.32079000000000002</v>
       </c>
       <c r="H145">
         <v>2640</v>
@@ -22777,7 +22777,7 @@
         <v>0.6</v>
       </c>
       <c r="G146">
-        <v>0.39780000000000004</v>
+        <v>0.33813000000000004</v>
       </c>
       <c r="H146">
         <v>2640</v>
@@ -22830,7 +22830,7 @@
         <v>0.7</v>
       </c>
       <c r="G147">
-        <v>0.39780000000000004</v>
+        <v>0.33813000000000004</v>
       </c>
       <c r="H147">
         <v>2640</v>
@@ -22883,7 +22883,7 @@
         <v>0.5</v>
       </c>
       <c r="G148">
-        <v>0.37740000000000001</v>
+        <v>0.32079000000000002</v>
       </c>
       <c r="H148">
         <v>2640</v>
@@ -22936,7 +22936,7 @@
         <v>0.5</v>
       </c>
       <c r="G149">
-        <v>0.37740000000000001</v>
+        <v>0.32079000000000002</v>
       </c>
       <c r="H149">
         <v>2640</v>
@@ -22989,7 +22989,7 @@
         <v>1</v>
       </c>
       <c r="G150">
-        <v>0.39780000000000004</v>
+        <v>0.33813000000000004</v>
       </c>
       <c r="H150">
         <v>2640</v>
@@ -23042,7 +23042,7 @@
         <v>1</v>
       </c>
       <c r="G151">
-        <v>0.39780000000000004</v>
+        <v>0.33813000000000004</v>
       </c>
       <c r="H151">
         <v>2640</v>
@@ -23095,7 +23095,7 @@
         <v>0.7</v>
       </c>
       <c r="G152">
-        <v>0.40290000000000004</v>
+        <v>0.34246500000000002</v>
       </c>
       <c r="H152">
         <v>2640</v>
@@ -23148,7 +23148,7 @@
         <v>0.7</v>
       </c>
       <c r="G153">
-        <v>0.40290000000000004</v>
+        <v>0.34246500000000002</v>
       </c>
       <c r="H153">
         <v>2640</v>
@@ -23201,7 +23201,7 @@
         <v>0.52200000000000002</v>
       </c>
       <c r="G154">
-        <v>0.40290000000000004</v>
+        <v>0.34246500000000002</v>
       </c>
       <c r="H154">
         <v>2640</v>
@@ -23254,7 +23254,7 @@
         <v>0.7</v>
       </c>
       <c r="G155">
-        <v>0.37740000000000001</v>
+        <v>0.32079000000000002</v>
       </c>
       <c r="H155">
         <v>2640</v>
@@ -23307,7 +23307,7 @@
         <v>0.6</v>
       </c>
       <c r="G156">
-        <v>0.37740000000000001</v>
+        <v>0.32079000000000002</v>
       </c>
       <c r="H156">
         <v>2640</v>
@@ -23360,7 +23360,7 @@
         <v>0.5</v>
       </c>
       <c r="G157">
-        <v>0.39780000000000004</v>
+        <v>0.33813000000000004</v>
       </c>
       <c r="H157">
         <v>2640</v>
@@ -23413,7 +23413,7 @@
         <v>0.36</v>
       </c>
       <c r="G158">
-        <v>0.40290000000000004</v>
+        <v>0.34246500000000002</v>
       </c>
       <c r="H158">
         <v>2640</v>
@@ -23466,7 +23466,7 @@
         <v>1</v>
       </c>
       <c r="G159">
-        <v>0.41820000000000002</v>
+        <v>0.35546999999999995</v>
       </c>
       <c r="H159">
         <v>2880</v>
@@ -23519,7 +23519,7 @@
         <v>1</v>
       </c>
       <c r="G160">
-        <v>0.41820000000000002</v>
+        <v>0.35546999999999995</v>
       </c>
       <c r="H160">
         <v>2880</v>
@@ -23572,7 +23572,7 @@
         <v>0.7</v>
       </c>
       <c r="G161">
-        <v>0.41819999999999991</v>
+        <v>0.35546999999999995</v>
       </c>
       <c r="H161">
         <v>2880</v>
@@ -23625,7 +23625,7 @@
         <v>1</v>
       </c>
       <c r="G162">
-        <v>0.4284</v>
+        <v>0.36414000000000002</v>
       </c>
       <c r="H162">
         <v>2880</v>
@@ -23678,7 +23678,7 @@
         <v>1</v>
       </c>
       <c r="G163">
-        <v>0.4284</v>
+        <v>0.36414000000000002</v>
       </c>
       <c r="H163">
         <v>2880</v>
@@ -23731,7 +23731,7 @@
         <v>0.6</v>
       </c>
       <c r="G164">
-        <v>0.42840000000000006</v>
+        <v>0.36414000000000002</v>
       </c>
       <c r="H164">
         <v>2880</v>
@@ -23784,7 +23784,7 @@
         <v>0.6</v>
       </c>
       <c r="G165">
-        <v>0.44369999999999993</v>
+        <v>0.37714499999999995</v>
       </c>
       <c r="H165">
         <v>2880</v>
@@ -23837,7 +23837,7 @@
         <v>0.65</v>
       </c>
       <c r="G166">
-        <v>0.45390000000000003</v>
+        <v>0.38581500000000002</v>
       </c>
       <c r="H166">
         <v>2880</v>
@@ -23890,7 +23890,7 @@
         <v>1</v>
       </c>
       <c r="G167">
-        <v>0.4284</v>
+        <v>0.36414000000000002</v>
       </c>
       <c r="H167">
         <v>2880</v>
@@ -23943,7 +23943,7 @@
         <v>1</v>
       </c>
       <c r="G168">
-        <v>0.44369999999999998</v>
+        <v>0.37714499999999995</v>
       </c>
       <c r="H168">
         <v>2880</v>
@@ -23996,7 +23996,7 @@
         <v>0.6</v>
       </c>
       <c r="G169">
-        <v>0.42840000000000006</v>
+        <v>0.36414000000000002</v>
       </c>
       <c r="H169">
         <v>2880</v>
@@ -24049,7 +24049,7 @@
         <v>0.6</v>
       </c>
       <c r="G170">
-        <v>0.42840000000000006</v>
+        <v>0.36414000000000002</v>
       </c>
       <c r="H170">
         <v>2880</v>
@@ -24102,7 +24102,7 @@
         <v>1.05</v>
       </c>
       <c r="G171">
-        <v>0.41819999999999996</v>
+        <v>0.35546999999999995</v>
       </c>
       <c r="H171">
         <v>2880</v>
@@ -24155,7 +24155,7 @@
         <v>1.05</v>
       </c>
       <c r="G172">
-        <v>0.41819999999999996</v>
+        <v>0.35546999999999995</v>
       </c>
       <c r="H172">
         <v>2880</v>
@@ -24208,7 +24208,7 @@
         <v>0.65</v>
       </c>
       <c r="G173">
-        <v>0.45390000000000003</v>
+        <v>0.38581500000000002</v>
       </c>
       <c r="H173">
         <v>2880</v>
@@ -24261,7 +24261,7 @@
         <v>0.65</v>
       </c>
       <c r="G174">
-        <v>0.45390000000000003</v>
+        <v>0.38581500000000002</v>
       </c>
       <c r="H174">
         <v>2880</v>
@@ -24314,7 +24314,7 @@
         <v>0.9</v>
       </c>
       <c r="G175">
-        <v>0.4284</v>
+        <v>0.36414000000000002</v>
       </c>
       <c r="H175">
         <v>2880</v>
@@ -24367,7 +24367,7 @@
         <v>0.9</v>
       </c>
       <c r="G176">
-        <v>0.4284</v>
+        <v>0.36414000000000002</v>
       </c>
       <c r="H176">
         <v>2880</v>
@@ -24420,7 +24420,7 @@
         <v>1</v>
       </c>
       <c r="G177">
-        <v>0.44369999999999998</v>
+        <v>0.37714499999999995</v>
       </c>
       <c r="H177">
         <v>2880</v>
@@ -24473,7 +24473,7 @@
         <v>1</v>
       </c>
       <c r="G178">
-        <v>0.41820000000000002</v>
+        <v>0.35546999999999995</v>
       </c>
       <c r="H178">
         <v>2880</v>
@@ -24526,7 +24526,7 @@
         <v>1</v>
       </c>
       <c r="G179">
-        <v>0.41820000000000002</v>
+        <v>0.35546999999999995</v>
       </c>
       <c r="H179">
         <v>2880</v>
@@ -24579,7 +24579,7 @@
         <v>1</v>
       </c>
       <c r="G180">
-        <v>0.45390000000000003</v>
+        <v>0.38581500000000002</v>
       </c>
       <c r="H180">
         <v>2880</v>
@@ -24632,7 +24632,7 @@
         <v>0.5</v>
       </c>
       <c r="G181">
-        <v>0.41820000000000002</v>
+        <v>0.35546999999999995</v>
       </c>
       <c r="H181">
         <v>2880</v>
@@ -24685,7 +24685,7 @@
         <v>0.7</v>
       </c>
       <c r="G182">
-        <v>0.41819999999999991</v>
+        <v>0.35546999999999995</v>
       </c>
       <c r="H182">
         <v>2880</v>
@@ -24738,7 +24738,7 @@
         <v>0.6</v>
       </c>
       <c r="G183">
-        <v>0.41819999999999996</v>
+        <v>0.35546999999999995</v>
       </c>
       <c r="H183">
         <v>2880</v>
@@ -24791,7 +24791,7 @@
         <v>0.6</v>
       </c>
       <c r="G184">
-        <v>0.44369999999999993</v>
+        <v>0.37714499999999995</v>
       </c>
       <c r="H184">
         <v>2880</v>
@@ -24844,7 +24844,7 @@
         <v>0.7</v>
       </c>
       <c r="G185">
-        <v>0.4284</v>
+        <v>0.36414000000000002</v>
       </c>
       <c r="H185">
         <v>2880</v>
@@ -24897,7 +24897,7 @@
         <v>0.5</v>
       </c>
       <c r="G186">
-        <v>0.45390000000000003</v>
+        <v>0.38581500000000002</v>
       </c>
       <c r="H186">
         <v>2880</v>
@@ -24950,7 +24950,7 @@
         <v>0.7</v>
       </c>
       <c r="G187">
-        <v>0.41819999999999991</v>
+        <v>0.35546999999999995</v>
       </c>
       <c r="H187">
         <v>2880</v>
@@ -25003,7 +25003,7 @@
         <v>0.64500000000000002</v>
       </c>
       <c r="G188">
-        <v>0.44369999999999993</v>
+        <v>0.37714499999999995</v>
       </c>
       <c r="H188">
         <v>2880</v>
@@ -25056,7 +25056,7 @@
         <v>0.6</v>
       </c>
       <c r="G189">
-        <v>0.44369999999999993</v>
+        <v>0.37714499999999995</v>
       </c>
       <c r="H189">
         <v>2880</v>
@@ -25109,7 +25109,7 @@
         <v>1.07</v>
       </c>
       <c r="G190">
-        <v>0.45390000000000003</v>
+        <v>0.38581500000000002</v>
       </c>
       <c r="H190">
         <v>2880</v>
@@ -25162,7 +25162,7 @@
         <v>0.7</v>
       </c>
       <c r="G191">
-        <v>0.4284</v>
+        <v>0.36414000000000002</v>
       </c>
       <c r="H191">
         <v>2880</v>
@@ -25215,7 +25215,7 @@
         <v>0.7</v>
       </c>
       <c r="G192">
-        <v>0.41819999999999991</v>
+        <v>0.35546999999999995</v>
       </c>
       <c r="H192">
         <v>2880</v>
@@ -25268,7 +25268,7 @@
         <v>0.65</v>
       </c>
       <c r="G193">
-        <v>0.45390000000000003</v>
+        <v>0.38581500000000002</v>
       </c>
       <c r="H193">
         <v>2880</v>
@@ -25321,7 +25321,7 @@
         <v>0.65</v>
       </c>
       <c r="G194">
-        <v>0.45390000000000003</v>
+        <v>0.38581500000000002</v>
       </c>
       <c r="H194">
         <v>2880</v>
@@ -25374,7 +25374,7 @@
         <v>0.14799999999999999</v>
       </c>
       <c r="G195">
-        <v>0.36719999999999997</v>
+        <v>0.31211999999999995</v>
       </c>
       <c r="H195">
         <v>1380</v>
@@ -25427,7 +25427,7 @@
         <v>0.38580000000000003</v>
       </c>
       <c r="G196">
-        <v>0.43859999999999999</v>
+        <v>0.37280999999999997</v>
       </c>
       <c r="H196">
         <v>1380</v>
@@ -25480,7 +25480,7 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="G197">
-        <v>0.43859999999999999</v>
+        <v>0.37280999999999997</v>
       </c>
       <c r="H197">
         <v>1380</v>
@@ -25533,7 +25533,7 @@
         <v>1</v>
       </c>
       <c r="G198">
-        <v>0.43860000000000005</v>
+        <v>0.37280999999999992</v>
       </c>
       <c r="H198">
         <v>1380</v>
@@ -25586,7 +25586,7 @@
         <v>0.16200000000000001</v>
       </c>
       <c r="G199">
-        <v>0.43860000000000005</v>
+        <v>0.37280999999999997</v>
       </c>
       <c r="H199">
         <v>1380</v>
@@ -25639,7 +25639,7 @@
         <v>1.5489999999999999</v>
       </c>
       <c r="G200">
-        <v>0.43859999999999993</v>
+        <v>0.37280999999999997</v>
       </c>
       <c r="H200">
         <v>1380</v>
@@ -25692,7 +25692,7 @@
         <v>0.6</v>
       </c>
       <c r="G201">
-        <v>0.51</v>
+        <v>0.43349999999999994</v>
       </c>
       <c r="H201">
         <v>1380</v>
@@ -25745,7 +25745,7 @@
         <v>0.78600000000000003</v>
       </c>
       <c r="G202">
-        <v>0.51</v>
+        <v>0.4335</v>
       </c>
       <c r="H202">
         <v>1380</v>
@@ -25798,7 +25798,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="G203">
-        <v>0.51</v>
+        <v>0.43349999999999994</v>
       </c>
       <c r="H203">
         <v>1380</v>
@@ -25851,7 +25851,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="G204">
-        <v>0.51</v>
+        <v>0.43349999999999994</v>
       </c>
       <c r="H204">
         <v>1380</v>
@@ -25904,7 +25904,7 @@
         <v>3.2469999999999999</v>
       </c>
       <c r="G205">
-        <v>0.51592146596858646</v>
+        <v>0.43853324607329847</v>
       </c>
       <c r="H205">
         <v>1338.2014166923313</v>
@@ -25957,7 +25957,7 @@
         <v>3.2090000000000001</v>
       </c>
       <c r="G206">
-        <v>0.52198317232782798</v>
+        <v>0.44368569647865386</v>
       </c>
       <c r="H206">
         <v>1295.4129012153319</v>
@@ -26010,7 +26010,7 @@
         <v>3.3069999999999999</v>
       </c>
       <c r="G207">
-        <v>0.51858996068944674</v>
+        <v>0.4408014665860297</v>
       </c>
       <c r="H207">
         <v>1319.364983368612</v>
@@ -26063,7 +26063,7 @@
         <v>1.589</v>
       </c>
       <c r="G208">
-        <v>0.5331088735053493</v>
+        <v>0.45314254247954694</v>
       </c>
       <c r="H208">
         <v>1216.8785399622404</v>
@@ -26116,7 +26116,7 @@
         <v>1.08</v>
       </c>
       <c r="G209">
-        <v>0.53550000000000009</v>
+        <v>0.45517500000000005</v>
       </c>
       <c r="H209">
         <v>1200</v>
@@ -26169,7 +26169,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="G210">
-        <v>0.55590000000000006</v>
+        <v>0.47251500000000002</v>
       </c>
       <c r="H210">
         <v>1200</v>
@@ -26222,7 +26222,7 @@
         <v>0.91849999999999998</v>
       </c>
       <c r="G211">
-        <v>0.55199934676102347</v>
+        <v>0.46919944474686992</v>
       </c>
       <c r="H211">
         <v>1227.5340228633643</v>
@@ -26275,7 +26275,7 @@
         <v>1.8614000000000002</v>
       </c>
       <c r="G212">
-        <v>0.55070246051359184</v>
+        <v>0.46809709143655309</v>
       </c>
       <c r="H212">
         <v>1236.6885140217041</v>
@@ -26328,7 +26328,7 @@
         <v>0.46</v>
       </c>
       <c r="G213">
-        <v>0.52818260869565214</v>
+        <v>0.44895521739130434</v>
       </c>
       <c r="H213">
         <v>1406.0869565217392</v>
@@ -26381,7 +26381,7 @@
         <v>0.1047</v>
       </c>
       <c r="G214">
-        <v>0.53039999999999998</v>
+        <v>0.45083999999999996</v>
       </c>
       <c r="H214">
         <v>1380</v>
@@ -26434,7 +26434,7 @@
         <v>0.24</v>
       </c>
       <c r="G215">
-        <v>0.53039999999999998</v>
+        <v>0.45083999999999996</v>
       </c>
       <c r="H215">
         <v>1380</v>
@@ -26487,7 +26487,7 @@
         <v>2.5474000000000001</v>
       </c>
       <c r="G216">
-        <v>0.55489897935149568</v>
+        <v>0.47166413244877131</v>
       </c>
       <c r="H216">
         <v>1207.0660281070896</v>
@@ -26540,7 +26540,7 @@
         <v>2.5939999999999999</v>
       </c>
       <c r="G217">
-        <v>0.54219645335389355</v>
+        <v>0.46086698535080944</v>
       </c>
       <c r="H217">
         <v>1296.7309175019275</v>
@@ -26593,7 +26593,7 @@
         <v>2.4981999999999998</v>
       </c>
       <c r="G218">
-        <v>0.55165374269474021</v>
+        <v>0.46890568129052912</v>
       </c>
       <c r="H218">
         <v>1229.9735809783044</v>
@@ -26646,7 +26646,7 @@
         <v>0.26189999999999997</v>
       </c>
       <c r="G219">
-        <v>0.57120000000000004</v>
+        <v>0.48552000000000006</v>
       </c>
       <c r="H219">
         <v>1380.0000000000002</v>
@@ -26699,7 +26699,7 @@
         <v>0.36330000000000001</v>
       </c>
       <c r="G220">
-        <v>0.57120000000000004</v>
+        <v>0.48552000000000001</v>
       </c>
       <c r="H220">
         <v>1380</v>
@@ -26752,7 +26752,7 @@
         <v>1.224</v>
       </c>
       <c r="G221">
-        <v>0.5874166666666667</v>
+        <v>0.49930416666666672</v>
       </c>
       <c r="H221">
         <v>1236.9117647058824</v>
@@ -26805,7 +26805,7 @@
         <v>3.149</v>
       </c>
       <c r="G222">
-        <v>0.58881759288663071</v>
+        <v>0.50049495395363597</v>
       </c>
       <c r="H222">
         <v>1224.5506510003177</v>
@@ -26858,7 +26858,7 @@
         <v>1.0771999999999999</v>
       </c>
       <c r="G223">
-        <v>0.58041333085777946</v>
+        <v>0.49335133122911246</v>
       </c>
       <c r="H223">
         <v>1298.7059041960638</v>
@@ -26911,7 +26911,7 @@
         <v>0.69610000000000005</v>
       </c>
       <c r="G224">
-        <v>0.58313052722310021</v>
+        <v>0.49566094813963507</v>
       </c>
       <c r="H224">
         <v>1274.7306421491164</v>
@@ -26964,7 +26964,7 @@
         <v>0.42469999999999997</v>
       </c>
       <c r="G225">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H225">
         <v>1200</v>
@@ -27017,7 +27017,7 @@
         <v>0.33700000000000002</v>
       </c>
       <c r="G226">
-        <v>0.57120000000000004</v>
+        <v>0.48552000000000001</v>
       </c>
       <c r="H226">
         <v>1380</v>
@@ -27070,7 +27070,7 @@
         <v>0.2</v>
       </c>
       <c r="G227">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H227">
         <v>1380</v>
@@ -27123,7 +27123,7 @@
         <v>0.28560000000003072</v>
       </c>
       <c r="G228">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H228">
         <v>1380</v>
@@ -27176,7 +27176,7 @@
         <v>0.56599999999999995</v>
       </c>
       <c r="G229">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H229">
         <v>1200</v>
@@ -27229,7 +27229,7 @@
         <v>0.65</v>
       </c>
       <c r="G230">
-        <v>0.61199999999999999</v>
+        <v>0.5202</v>
       </c>
       <c r="H230">
         <v>1200</v>
@@ -27282,7 +27282,7 @@
         <v>0.65</v>
       </c>
       <c r="G231">
-        <v>0.61199999999999999</v>
+        <v>0.5202</v>
       </c>
       <c r="H231">
         <v>1200</v>
@@ -27335,7 +27335,7 @@
         <v>0.65</v>
       </c>
       <c r="G232">
-        <v>0.61199999999999999</v>
+        <v>0.5202</v>
       </c>
       <c r="H232">
         <v>1200</v>
@@ -27388,7 +27388,7 @@
         <v>0.5</v>
       </c>
       <c r="G233">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H233">
         <v>1200</v>
@@ -27441,7 +27441,7 @@
         <v>0.5</v>
       </c>
       <c r="G234">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H234">
         <v>1200</v>
@@ -27494,7 +27494,7 @@
         <v>0.5</v>
       </c>
       <c r="G235">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H235">
         <v>1200</v>
@@ -27547,7 +27547,7 @@
         <v>0.85399999999999998</v>
       </c>
       <c r="G236">
-        <v>0.53550000000000009</v>
+        <v>0.45517500000000005</v>
       </c>
       <c r="H236">
         <v>1200</v>
@@ -27600,7 +27600,7 @@
         <v>0.85399999999999998</v>
       </c>
       <c r="G237">
-        <v>0.53550000000000009</v>
+        <v>0.45517500000000005</v>
       </c>
       <c r="H237">
         <v>1200</v>
@@ -27653,7 +27653,7 @@
         <v>0.85399999999999998</v>
       </c>
       <c r="G238">
-        <v>0.53550000000000009</v>
+        <v>0.45517500000000005</v>
       </c>
       <c r="H238">
         <v>1200</v>
@@ -27706,7 +27706,7 @@
         <v>0.85399999999999998</v>
       </c>
       <c r="G239">
-        <v>0.53550000000000009</v>
+        <v>0.45517500000000005</v>
       </c>
       <c r="H239">
         <v>1200</v>
@@ -27759,7 +27759,7 @@
         <v>0.59</v>
       </c>
       <c r="G240">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H240">
         <v>1200</v>
@@ -27812,7 +27812,7 @@
         <v>0.59</v>
       </c>
       <c r="G241">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H241">
         <v>1200</v>
@@ -27865,7 +27865,7 @@
         <v>0.50700000000000001</v>
       </c>
       <c r="G242">
-        <v>0.55590000000000006</v>
+        <v>0.47251500000000002</v>
       </c>
       <c r="H242">
         <v>1200</v>
@@ -27918,7 +27918,7 @@
         <v>0.50700000000000001</v>
       </c>
       <c r="G243">
-        <v>0.55590000000000006</v>
+        <v>0.47251500000000002</v>
       </c>
       <c r="H243">
         <v>1200</v>
@@ -27971,7 +27971,7 @@
         <v>0.50700000000000001</v>
       </c>
       <c r="G244">
-        <v>0.55590000000000006</v>
+        <v>0.47251500000000002</v>
       </c>
       <c r="H244">
         <v>1200</v>
@@ -28024,7 +28024,7 @@
         <v>0.78</v>
       </c>
       <c r="G245">
-        <v>0.61199999999999999</v>
+        <v>0.5202</v>
       </c>
       <c r="H245">
         <v>1200</v>
@@ -28077,7 +28077,7 @@
         <v>0.78</v>
       </c>
       <c r="G246">
-        <v>0.61199999999999999</v>
+        <v>0.5202</v>
       </c>
       <c r="H246">
         <v>1200</v>
@@ -28130,7 +28130,7 @@
         <v>0.78</v>
       </c>
       <c r="G247">
-        <v>0.61199999999999999</v>
+        <v>0.5202</v>
       </c>
       <c r="H247">
         <v>1200</v>
@@ -28183,7 +28183,7 @@
         <v>0.60499999999999998</v>
       </c>
       <c r="G248">
-        <v>0.45899999999999996</v>
+        <v>0.39015</v>
       </c>
       <c r="H248">
         <v>1200</v>
@@ -28236,7 +28236,7 @@
         <v>0.60499999999999998</v>
       </c>
       <c r="G249">
-        <v>0.45899999999999996</v>
+        <v>0.39015</v>
       </c>
       <c r="H249">
         <v>1200</v>
@@ -28289,7 +28289,7 @@
         <v>0.85</v>
       </c>
       <c r="G250">
-        <v>0.53550000000000009</v>
+        <v>0.45517500000000005</v>
       </c>
       <c r="H250">
         <v>1200</v>
@@ -28342,7 +28342,7 @@
         <v>0.85</v>
       </c>
       <c r="G251">
-        <v>0.55590000000000006</v>
+        <v>0.47251500000000007</v>
       </c>
       <c r="H251">
         <v>1200</v>
@@ -28395,7 +28395,7 @@
         <v>0.72899999999999998</v>
       </c>
       <c r="G252">
-        <v>0.53550000000000009</v>
+        <v>0.45517500000000005</v>
       </c>
       <c r="H252">
         <v>1200</v>
@@ -28448,7 +28448,7 @@
         <v>0.71299999999999997</v>
       </c>
       <c r="G253">
-        <v>0.53550000000000009</v>
+        <v>0.45517500000000005</v>
       </c>
       <c r="H253">
         <v>1200</v>
@@ -28501,7 +28501,7 @@
         <v>0.62260000000000004</v>
       </c>
       <c r="G254">
-        <v>0.61199999999999999</v>
+        <v>0.5202</v>
       </c>
       <c r="H254">
         <v>1200</v>
@@ -28554,7 +28554,7 @@
         <v>0.62260000000000004</v>
       </c>
       <c r="G255">
-        <v>0.61199999999999999</v>
+        <v>0.5202</v>
       </c>
       <c r="H255">
         <v>1200</v>
@@ -28607,7 +28607,7 @@
         <v>0.56940000000000002</v>
       </c>
       <c r="G256">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H256">
         <v>1200</v>
@@ -28660,7 +28660,7 @@
         <v>0.57199999999999995</v>
       </c>
       <c r="G257">
-        <v>0.61199999999999999</v>
+        <v>0.5202</v>
       </c>
       <c r="H257">
         <v>1200</v>
@@ -28713,7 +28713,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="G258">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H258">
         <v>1200</v>
@@ -28766,7 +28766,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="G259">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H259">
         <v>1200</v>
@@ -28819,7 +28819,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="G260">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H260">
         <v>1200</v>
@@ -28872,7 +28872,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="G261">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H261">
         <v>1200</v>
@@ -28925,7 +28925,7 @@
         <v>0.5</v>
       </c>
       <c r="G262">
-        <v>0.55590000000000006</v>
+        <v>0.47251500000000002</v>
       </c>
       <c r="H262">
         <v>1200</v>
@@ -28978,7 +28978,7 @@
         <v>0.5</v>
       </c>
       <c r="G263">
-        <v>0.55590000000000006</v>
+        <v>0.47251500000000002</v>
       </c>
       <c r="H263">
         <v>1200</v>
@@ -29031,7 +29031,7 @@
         <v>0.5</v>
       </c>
       <c r="G264">
-        <v>0.55590000000000006</v>
+        <v>0.47251500000000002</v>
       </c>
       <c r="H264">
         <v>1200</v>
@@ -29084,7 +29084,7 @@
         <v>0.5</v>
       </c>
       <c r="G265">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H265">
         <v>1200</v>
@@ -29137,7 +29137,7 @@
         <v>0.71</v>
       </c>
       <c r="G266">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H266">
         <v>1200</v>
@@ -29190,7 +29190,7 @@
         <v>0.71</v>
       </c>
       <c r="G267">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H267">
         <v>1200</v>
@@ -29243,7 +29243,7 @@
         <v>0.62409999999999999</v>
       </c>
       <c r="G268">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H268">
         <v>1200</v>
@@ -29296,7 +29296,7 @@
         <v>0.62409999999999999</v>
       </c>
       <c r="G269">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H269">
         <v>1200</v>
@@ -29349,7 +29349,7 @@
         <v>1.1879999999999999</v>
       </c>
       <c r="G270">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H270">
         <v>1200</v>
@@ -29402,7 +29402,7 @@
         <v>1.1879999999999999</v>
       </c>
       <c r="G271">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H271">
         <v>1200</v>
@@ -29455,7 +29455,7 @@
         <v>0.5</v>
       </c>
       <c r="G272">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H272">
         <v>1200</v>
@@ -29508,7 +29508,7 @@
         <v>0.52300000000000002</v>
       </c>
       <c r="G273">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H273">
         <v>1200</v>
@@ -29561,7 +29561,7 @@
         <v>0.52300000000000002</v>
       </c>
       <c r="G274">
-        <v>0.59160000000000001</v>
+        <v>0.50285999999999997</v>
       </c>
       <c r="H274">
         <v>1200</v>
@@ -29614,7 +29614,7 @@
         <v>0.41599999999999998</v>
       </c>
       <c r="G275">
-        <v>0.32639999999999997</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H275">
         <v>960</v>
@@ -29667,7 +29667,7 @@
         <v>0.15</v>
       </c>
       <c r="G276">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H276">
         <v>1103.9999999999998</v>
@@ -29720,7 +29720,7 @@
         <v>0.10920000000000001</v>
       </c>
       <c r="G277">
-        <v>0.36209999999999998</v>
+        <v>0.30778499999999998</v>
       </c>
       <c r="H277">
         <v>1518</v>
@@ -29773,7 +29773,7 @@
         <v>0.10920000000000001</v>
       </c>
       <c r="G278">
-        <v>0.36209999999999998</v>
+        <v>0.30778499999999998</v>
       </c>
       <c r="H278">
         <v>1518</v>
@@ -29826,7 +29826,7 @@
         <v>0.10920000000000001</v>
       </c>
       <c r="G279">
-        <v>0.36719999999999997</v>
+        <v>0.31211999999999995</v>
       </c>
       <c r="H279">
         <v>1518</v>
@@ -29879,7 +29879,7 @@
         <v>1.7190000000000001</v>
       </c>
       <c r="G280">
-        <v>0.32261431064572432</v>
+        <v>0.27422216404886568</v>
       </c>
       <c r="H280">
         <v>1480.0837696335079</v>
@@ -29932,7 +29932,7 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="G281">
-        <v>0.31619999999999998</v>
+        <v>0.26876999999999995</v>
       </c>
       <c r="H281">
         <v>1656</v>
@@ -29985,7 +29985,7 @@
         <v>0.66800000000000004</v>
       </c>
       <c r="G282">
-        <v>0.31620000000000004</v>
+        <v>0.26876999999999995</v>
       </c>
       <c r="H282">
         <v>1656</v>
@@ -30038,7 +30038,7 @@
         <v>0.70499999999999996</v>
       </c>
       <c r="G283">
-        <v>0.32922127659574468</v>
+        <v>0.27983808510638297</v>
       </c>
       <c r="H283">
         <v>1518.127659574468</v>
@@ -30091,7 +30091,7 @@
         <v>0.375</v>
       </c>
       <c r="G284">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H284">
         <v>1440</v>
@@ -30144,7 +30144,7 @@
         <v>0.13800000000000001</v>
       </c>
       <c r="G285">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H285">
         <v>1656</v>
@@ -30197,7 +30197,7 @@
         <v>0.14899999999999999</v>
       </c>
       <c r="G286">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H286">
         <v>1656</v>
@@ -30250,7 +30250,7 @@
         <v>0.1</v>
       </c>
       <c r="G287">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H287">
         <v>1656</v>
@@ -30303,7 +30303,7 @@
         <v>0.34</v>
       </c>
       <c r="G288">
-        <v>0.36719999999999997</v>
+        <v>0.31211999999999995</v>
       </c>
       <c r="H288">
         <v>1440</v>
@@ -30356,7 +30356,7 @@
         <v>0.46</v>
       </c>
       <c r="G289">
-        <v>0.36232173913043475</v>
+        <v>0.30797347826086957</v>
       </c>
       <c r="H289">
         <v>1491.6521739130435</v>
@@ -30409,7 +30409,7 @@
         <v>0.35</v>
       </c>
       <c r="G290">
-        <v>0.37230000000000002</v>
+        <v>0.31645499999999999</v>
       </c>
       <c r="H290">
         <v>1440</v>
@@ -30462,7 +30462,7 @@
         <v>0.85599999999999998</v>
       </c>
       <c r="G291">
-        <v>0.36858224299065417</v>
+        <v>0.31329490654205605</v>
       </c>
       <c r="H291">
         <v>1479.3644859813085</v>
@@ -30515,7 +30515,7 @@
         <v>0.156</v>
       </c>
       <c r="G292">
-        <v>0.35189999999999999</v>
+        <v>0.29911499999999996</v>
       </c>
       <c r="H292">
         <v>1656</v>
@@ -30568,7 +30568,7 @@
         <v>0.6</v>
       </c>
       <c r="G293">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H293">
         <v>1440</v>
@@ -30621,7 +30621,7 @@
         <v>0.6</v>
       </c>
       <c r="G294">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H294">
         <v>1440</v>
@@ -30674,7 +30674,7 @@
         <v>0.6</v>
       </c>
       <c r="G295">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H295">
         <v>1440</v>
@@ -30727,7 +30727,7 @@
         <v>0.6</v>
       </c>
       <c r="G296">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H296">
         <v>1440</v>
@@ -30780,7 +30780,7 @@
         <v>1</v>
       </c>
       <c r="G297">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H297">
         <v>1440</v>
@@ -30833,7 +30833,7 @@
         <v>1</v>
       </c>
       <c r="G298">
-        <v>0.35699999999999998</v>
+        <v>0.30345</v>
       </c>
       <c r="H298">
         <v>1440</v>
@@ -30886,7 +30886,7 @@
         <v>0.7</v>
       </c>
       <c r="G299">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H299">
         <v>1440</v>
@@ -30939,7 +30939,7 @@
         <v>0.7</v>
       </c>
       <c r="G300">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H300">
         <v>1440</v>
@@ -30992,7 +30992,7 @@
         <v>0.6</v>
       </c>
       <c r="G301">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H301">
         <v>1440</v>
@@ -31045,7 +31045,7 @@
         <v>0.6</v>
       </c>
       <c r="G302">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H302">
         <v>1440</v>
@@ -31098,7 +31098,7 @@
         <v>0.6</v>
       </c>
       <c r="G303">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H303">
         <v>1440</v>
@@ -31151,7 +31151,7 @@
         <v>0.6</v>
       </c>
       <c r="G304">
-        <v>0.35699999999999998</v>
+        <v>0.30345</v>
       </c>
       <c r="H304">
         <v>1440</v>
@@ -31204,7 +31204,7 @@
         <v>0.6</v>
       </c>
       <c r="G305">
-        <v>0.35699999999999998</v>
+        <v>0.30345</v>
       </c>
       <c r="H305">
         <v>1440</v>
@@ -31257,7 +31257,7 @@
         <v>0.6</v>
       </c>
       <c r="G306">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H306">
         <v>1440</v>
@@ -31310,7 +31310,7 @@
         <v>1</v>
       </c>
       <c r="G307">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H307">
         <v>1440</v>
@@ -31363,7 +31363,7 @@
         <v>1</v>
       </c>
       <c r="G308">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H308">
         <v>1440</v>
@@ -31416,7 +31416,7 @@
         <v>1</v>
       </c>
       <c r="G309">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H309">
         <v>1440</v>
@@ -39096,7 +39096,7 @@
         <v>0.14799999999999999</v>
       </c>
       <c r="G507">
-        <v>0.22440000000000004</v>
+        <v>0.19074000000000002</v>
       </c>
       <c r="H507">
         <v>1242</v>
@@ -39128,7 +39128,7 @@
         <v>0.106</v>
       </c>
       <c r="G508">
-        <v>0.28560000000000002</v>
+        <v>0.24276</v>
       </c>
       <c r="H508">
         <v>1242</v>
@@ -39160,7 +39160,7 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="G509">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H509">
         <v>1242</v>
@@ -39192,7 +39192,7 @@
         <v>0.45</v>
       </c>
       <c r="G510">
-        <v>0.31619999999999998</v>
+        <v>0.26876999999999995</v>
       </c>
       <c r="H510">
         <v>1560</v>
@@ -39224,7 +39224,7 @@
         <v>0.25</v>
       </c>
       <c r="G511">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H511">
         <v>1793.9999999999998</v>
@@ -39256,7 +39256,7 @@
         <v>0.35</v>
       </c>
       <c r="G512">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H512">
         <v>1560</v>
@@ -39288,7 +39288,7 @@
         <v>0.25</v>
       </c>
       <c r="G513">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H513">
         <v>1793.9999999999998</v>
@@ -39320,7 +39320,7 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="G514">
-        <v>0.30599999999999999</v>
+        <v>0.2601</v>
       </c>
       <c r="H514">
         <v>1793.9999999999998</v>
@@ -39352,7 +39352,7 @@
         <v>0.45</v>
       </c>
       <c r="G515">
-        <v>0.32640000000000008</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H515">
         <v>1560</v>
@@ -39384,7 +39384,7 @@
         <v>0.72499999999999998</v>
       </c>
       <c r="G516">
-        <v>0.31584827586206898</v>
+        <v>0.26847103448275861</v>
       </c>
       <c r="H516">
         <v>1681.0344827586207</v>
@@ -39416,7 +39416,7 @@
         <v>0.35</v>
       </c>
       <c r="G517">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H517">
         <v>1560</v>
@@ -39448,7 +39448,7 @@
         <v>0.125</v>
       </c>
       <c r="G518">
-        <v>0.31619999999999998</v>
+        <v>0.26877000000000001</v>
       </c>
       <c r="H518">
         <v>1793.9999999999998</v>
@@ -39480,7 +39480,7 @@
         <v>0.35</v>
       </c>
       <c r="G519">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H519">
         <v>1560</v>
@@ -39512,7 +39512,7 @@
         <v>0.35</v>
       </c>
       <c r="G520">
-        <v>0.34680000000000005</v>
+        <v>0.29478000000000004</v>
       </c>
       <c r="H520">
         <v>1560</v>
@@ -39544,7 +39544,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="G521">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H521">
         <v>1793.9999999999998</v>
@@ -39576,7 +39576,7 @@
         <v>0.5</v>
       </c>
       <c r="G522">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H522">
         <v>1560</v>
@@ -39608,7 +39608,7 @@
         <v>0.7</v>
       </c>
       <c r="G523">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H523">
         <v>1560</v>
@@ -39640,7 +39640,7 @@
         <v>0.7</v>
       </c>
       <c r="G524">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H524">
         <v>1560</v>
@@ -39672,7 +39672,7 @@
         <v>0.6</v>
       </c>
       <c r="G525">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H525">
         <v>1560</v>
@@ -39704,7 +39704,7 @@
         <v>0.6</v>
       </c>
       <c r="G526">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H526">
         <v>1560</v>
@@ -39736,7 +39736,7 @@
         <v>0.5</v>
       </c>
       <c r="G527">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H527">
         <v>1560</v>
@@ -39768,7 +39768,7 @@
         <v>0.5</v>
       </c>
       <c r="G528">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H528">
         <v>1560</v>
@@ -39800,7 +39800,7 @@
         <v>0.6</v>
       </c>
       <c r="G529">
-        <v>0.32640000000000002</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H529">
         <v>1560</v>
@@ -39832,7 +39832,7 @@
         <v>0.6</v>
       </c>
       <c r="G530">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H530">
         <v>1560</v>
@@ -39864,7 +39864,7 @@
         <v>0.6</v>
       </c>
       <c r="G531">
-        <v>0.33660000000000001</v>
+        <v>0.28610999999999998</v>
       </c>
       <c r="H531">
         <v>1560</v>
@@ -39896,7 +39896,7 @@
         <v>0.45</v>
       </c>
       <c r="G532">
-        <v>0.32640000000000008</v>
+        <v>0.27744000000000002</v>
       </c>
       <c r="H532">
         <v>1560</v>
@@ -40803,7 +40803,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L561">
-        <v>0.3989512625582104</v>
+        <v>0.39895126255821034</v>
       </c>
     </row>
     <row r="562" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBD954AE-CB56-4566-A2C4-E7B934830694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{59E83A22-B569-4EB9-9698-1BDAF258DDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{01DD8B29-20EB-4D46-881E-0E6C7655B509}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{506E9D17-4763-471F-B781-A7200E9E9C64}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3479,7 +3479,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8AE9531-8CFD-40D5-930F-FACCF631D437}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A7EB98-106B-4F22-84F6-5C2894A214CE}">
   <dimension ref="B9:T266"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3558,7 +3558,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>9.0930960000000005E-2</v>
+        <v>9.4140288000000016E-2</v>
       </c>
       <c r="F11">
         <v>3583</v>
@@ -3614,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>9.0930960000000005E-2</v>
+        <v>9.4140288000000016E-2</v>
       </c>
       <c r="F12">
         <v>3583</v>
@@ -3670,7 +3670,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>9.0930960000000005E-2</v>
+        <v>9.4140288000000016E-2</v>
       </c>
       <c r="F13">
         <v>3583</v>
@@ -3726,7 +3726,7 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.28776163499999996</v>
+        <v>0.29791792799999994</v>
       </c>
       <c r="F14">
         <v>1967</v>
@@ -3782,7 +3782,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.28776163499999996</v>
+        <v>0.29791792799999994</v>
       </c>
       <c r="F15">
         <v>1967</v>
@@ -3838,7 +3838,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.10542720000000003</v>
+        <v>0.10914816000000004</v>
       </c>
       <c r="F16">
         <v>3583</v>
@@ -3894,7 +3894,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>9.4884479999999993E-2</v>
+        <v>9.8233344000000014E-2</v>
       </c>
       <c r="F17">
         <v>3583</v>
@@ -3950,7 +3950,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>8.9613120000000032E-2</v>
+        <v>9.2775936000000031E-2</v>
       </c>
       <c r="F18">
         <v>3583</v>
@@ -4006,7 +4006,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>8.9613120000000032E-2</v>
+        <v>9.2775936000000031E-2</v>
       </c>
       <c r="F19">
         <v>3583</v>
@@ -4062,7 +4062,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>8.9613120000000032E-2</v>
+        <v>9.2775936000000031E-2</v>
       </c>
       <c r="F20">
         <v>3583</v>
@@ -4118,7 +4118,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>8.9613120000000032E-2</v>
+        <v>9.2775936000000031E-2</v>
       </c>
       <c r="F21">
         <v>3583</v>
@@ -4174,7 +4174,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F22">
         <v>3583</v>
@@ -4230,7 +4230,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F23">
         <v>3583</v>
@@ -4286,7 +4286,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F24">
         <v>3583</v>
@@ -4342,7 +4342,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F25">
         <v>3583</v>
@@ -4398,7 +4398,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F26">
         <v>3583</v>
@@ -4454,7 +4454,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F27">
         <v>3583</v>
@@ -4510,7 +4510,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F28">
         <v>3583</v>
@@ -4566,7 +4566,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F29">
         <v>3583</v>
@@ -4622,7 +4622,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F30">
         <v>3583</v>
@@ -4678,7 +4678,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F31">
         <v>3583</v>
@@ -4734,7 +4734,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F32">
         <v>3583</v>
@@ -4790,7 +4790,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F33">
         <v>3583</v>
@@ -4846,7 +4846,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F34">
         <v>3583</v>
@@ -4902,7 +4902,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F35">
         <v>3583</v>
@@ -4958,7 +4958,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F36">
         <v>3583</v>
@@ -5014,7 +5014,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F37">
         <v>3583</v>
@@ -5070,7 +5070,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F38">
         <v>3583</v>
@@ -5126,7 +5126,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F39">
         <v>3583</v>
@@ -5182,7 +5182,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F40">
         <v>3583</v>
@@ -5238,7 +5238,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F41">
         <v>3583</v>
@@ -5294,7 +5294,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F42">
         <v>3583</v>
@@ -5350,7 +5350,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F43">
         <v>3583</v>
@@ -5406,7 +5406,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F44">
         <v>3583</v>
@@ -5462,7 +5462,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F45">
         <v>3583</v>
@@ -5518,7 +5518,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F46">
         <v>3583</v>
@@ -5574,7 +5574,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F47">
         <v>3583</v>
@@ -5630,7 +5630,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F48">
         <v>3583</v>
@@ -5686,7 +5686,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F49">
         <v>3583</v>
@@ -5742,7 +5742,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F50">
         <v>3583</v>
@@ -5798,7 +5798,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F51">
         <v>3583</v>
@@ -5854,7 +5854,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F52">
         <v>3583</v>
@@ -5910,7 +5910,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F53">
         <v>3583</v>
@@ -5966,7 +5966,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F54">
         <v>3583</v>
@@ -6022,7 +6022,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F55">
         <v>3583</v>
@@ -6078,7 +6078,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F56">
         <v>3583</v>
@@ -6134,7 +6134,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F57">
         <v>3583</v>
@@ -6190,7 +6190,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F58">
         <v>3583</v>
@@ -6246,7 +6246,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F59">
         <v>3583</v>
@@ -6302,7 +6302,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F60">
         <v>3583</v>
@@ -6358,7 +6358,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F61">
         <v>3583</v>
@@ -6414,7 +6414,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F62">
         <v>3583</v>
@@ -6470,7 +6470,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F63">
         <v>3583</v>
@@ -6526,7 +6526,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F64">
         <v>3583</v>
@@ -6582,7 +6582,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F65">
         <v>3583</v>
@@ -6638,7 +6638,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F66">
         <v>3583</v>
@@ -6694,7 +6694,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F67">
         <v>3583</v>
@@ -6750,7 +6750,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>9.2775936000000017E-2</v>
+        <v>9.6050380800000015E-2</v>
       </c>
       <c r="F68">
         <v>3583</v>
@@ -6806,19 +6806,19 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>0.27895725000000005</v>
+        <v>0.29580408000000002</v>
       </c>
       <c r="F69">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G69">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H69">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I69">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J69" t="s">
         <v>81</v>
@@ -6862,19 +6862,19 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>0.27895725000000005</v>
+        <v>0.29580408000000002</v>
       </c>
       <c r="F70">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G70">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H70">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I70">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J70" t="s">
         <v>82</v>
@@ -6918,7 +6918,7 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>0.23417670000000002</v>
+        <v>0.24244176000000003</v>
       </c>
       <c r="F71">
         <v>2200</v>
@@ -6974,7 +6974,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.23417670000000002</v>
+        <v>0.24244176000000003</v>
       </c>
       <c r="F72">
         <v>2200</v>
@@ -7030,7 +7030,7 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>0.26465175000000002</v>
+        <v>0.27399240000000002</v>
       </c>
       <c r="F73">
         <v>1923</v>
@@ -7086,7 +7086,7 @@
         <v>14</v>
       </c>
       <c r="E74">
-        <v>0.26465175000000002</v>
+        <v>0.27399240000000002</v>
       </c>
       <c r="F74">
         <v>1923</v>
@@ -7142,7 +7142,7 @@
         <v>14</v>
       </c>
       <c r="E75">
-        <v>0.23417670000000002</v>
+        <v>0.24244176000000003</v>
       </c>
       <c r="F75">
         <v>2200</v>
@@ -7198,7 +7198,7 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>0.23417670000000002</v>
+        <v>0.24244176000000003</v>
       </c>
       <c r="F76">
         <v>2200</v>
@@ -7254,19 +7254,19 @@
         <v>14</v>
       </c>
       <c r="E77">
-        <v>0.24683490000000002</v>
+        <v>0.26709883200000006</v>
       </c>
       <c r="F77">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G77">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H77">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I77">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J77" t="s">
         <v>89</v>
@@ -7310,19 +7310,19 @@
         <v>14</v>
       </c>
       <c r="E78">
-        <v>0.27895725000000005</v>
+        <v>0.29580408000000002</v>
       </c>
       <c r="F78">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G78">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H78">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I78">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J78" t="s">
         <v>90</v>
@@ -7366,7 +7366,7 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>0.23417670000000002</v>
+        <v>0.24244176000000003</v>
       </c>
       <c r="F79">
         <v>2200</v>
@@ -7422,7 +7422,7 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>0.23417670000000002</v>
+        <v>0.24244176000000003</v>
       </c>
       <c r="F80">
         <v>2200</v>
@@ -7478,19 +7478,19 @@
         <v>14</v>
       </c>
       <c r="E81">
-        <v>0.27895725000000005</v>
+        <v>0.29580408000000002</v>
       </c>
       <c r="F81">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G81">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H81">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I81">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J81" t="s">
         <v>93</v>
@@ -7534,19 +7534,19 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>0.27895725000000005</v>
+        <v>0.29580408000000002</v>
       </c>
       <c r="F82">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G82">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H82">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I82">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J82" t="s">
         <v>94</v>
@@ -7590,7 +7590,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0.28938292500000001</v>
+        <v>0.29959644000000002</v>
       </c>
       <c r="F83">
         <v>1726</v>
@@ -7646,7 +7646,7 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <v>0.28938292500000001</v>
+        <v>0.29959644000000002</v>
       </c>
       <c r="F84">
         <v>1726</v>
@@ -7702,7 +7702,7 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>0.26130079500000003</v>
+        <v>0.27052317600000003</v>
       </c>
       <c r="F85">
         <v>1967</v>
@@ -7758,7 +7758,7 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>0.26465175000000002</v>
+        <v>0.27399240000000002</v>
       </c>
       <c r="F86">
         <v>1923</v>
@@ -7814,7 +7814,7 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <v>0.23417670000000002</v>
+        <v>0.24244176000000003</v>
       </c>
       <c r="F87">
         <v>2200</v>
@@ -7870,19 +7870,19 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.24683490000000002</v>
+        <v>0.26709883200000006</v>
       </c>
       <c r="F88">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G88">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H88">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I88">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J88" t="s">
         <v>100</v>
@@ -7926,7 +7926,7 @@
         <v>14</v>
       </c>
       <c r="E89">
-        <v>0.10410936000000003</v>
+        <v>0.10778380800000002</v>
       </c>
       <c r="F89">
         <v>3583</v>
@@ -7982,7 +7982,7 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.30037214999999995</v>
+        <v>0.31097351999999995</v>
       </c>
       <c r="F90">
         <v>1726</v>
@@ -8038,7 +8038,7 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.30037214999999995</v>
+        <v>0.31097351999999995</v>
       </c>
       <c r="F91">
         <v>1726</v>
@@ -8094,7 +8094,7 @@
         <v>14</v>
       </c>
       <c r="E92">
-        <v>0.30037214999999995</v>
+        <v>0.31097351999999989</v>
       </c>
       <c r="F92">
         <v>1726</v>
@@ -8150,7 +8150,7 @@
         <v>14</v>
       </c>
       <c r="E93">
-        <v>0.30769830000000004</v>
+        <v>0.31855823999999999</v>
       </c>
       <c r="F93">
         <v>1726</v>
@@ -8206,7 +8206,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.30769830000000004</v>
+        <v>0.31855823999999999</v>
       </c>
       <c r="F94">
         <v>1726</v>
@@ -8262,7 +8262,7 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.27783882000000004</v>
+        <v>0.28764489599999998</v>
       </c>
       <c r="F95">
         <v>1967</v>
@@ -8318,7 +8318,7 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.28776163499999996</v>
+        <v>0.29791792799999994</v>
       </c>
       <c r="F96">
         <v>1967</v>
@@ -8374,7 +8374,7 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0.294376845</v>
+        <v>0.30476661599999999</v>
       </c>
       <c r="F97">
         <v>1967</v>
@@ -8430,7 +8430,7 @@
         <v>14</v>
       </c>
       <c r="E98">
-        <v>0.30769830000000004</v>
+        <v>0.31855823999999999</v>
       </c>
       <c r="F98">
         <v>1726</v>
@@ -8486,7 +8486,7 @@
         <v>14</v>
       </c>
       <c r="E99">
-        <v>0.31868752499999997</v>
+        <v>0.32993531999999992</v>
       </c>
       <c r="F99">
         <v>1726</v>
@@ -8542,7 +8542,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.27783882000000004</v>
+        <v>0.28764489599999998</v>
       </c>
       <c r="F100">
         <v>1967</v>
@@ -8598,7 +8598,7 @@
         <v>14</v>
       </c>
       <c r="E101">
-        <v>0.27783882000000004</v>
+        <v>0.28764489599999998</v>
       </c>
       <c r="F101">
         <v>1967</v>
@@ -8654,7 +8654,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.30037214999999995</v>
+        <v>0.31097351999999995</v>
       </c>
       <c r="F102">
         <v>1726</v>
@@ -8710,7 +8710,7 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.30037214999999995</v>
+        <v>0.31097351999999995</v>
       </c>
       <c r="F103">
         <v>1726</v>
@@ -8766,7 +8766,7 @@
         <v>14</v>
       </c>
       <c r="E104">
-        <v>0.294376845</v>
+        <v>0.30476661599999999</v>
       </c>
       <c r="F104">
         <v>1967</v>
@@ -8822,7 +8822,7 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.294376845</v>
+        <v>0.30476661599999999</v>
       </c>
       <c r="F105">
         <v>1967</v>
@@ -8878,7 +8878,7 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>0.30769830000000004</v>
+        <v>0.31855823999999999</v>
       </c>
       <c r="F106">
         <v>1726</v>
@@ -8934,7 +8934,7 @@
         <v>14</v>
       </c>
       <c r="E107">
-        <v>0.30769830000000004</v>
+        <v>0.31855823999999999</v>
       </c>
       <c r="F107">
         <v>1726</v>
@@ -8990,7 +8990,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.31868752499999997</v>
+        <v>0.32993531999999992</v>
       </c>
       <c r="F108">
         <v>1726</v>
@@ -9046,7 +9046,7 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>0.30037214999999995</v>
+        <v>0.31097351999999995</v>
       </c>
       <c r="F109">
         <v>1726</v>
@@ -9102,7 +9102,7 @@
         <v>14</v>
       </c>
       <c r="E110">
-        <v>0.30037214999999995</v>
+        <v>0.31097351999999995</v>
       </c>
       <c r="F110">
         <v>1726</v>
@@ -9158,7 +9158,7 @@
         <v>14</v>
       </c>
       <c r="E111">
-        <v>0.326013675</v>
+        <v>0.33752004000000002</v>
       </c>
       <c r="F111">
         <v>1726</v>
@@ -9214,7 +9214,7 @@
         <v>14</v>
       </c>
       <c r="E112">
-        <v>0.27122360999999995</v>
+        <v>0.28079620799999999</v>
       </c>
       <c r="F112">
         <v>1967</v>
@@ -9270,7 +9270,7 @@
         <v>14</v>
       </c>
       <c r="E113">
-        <v>0.30037214999999995</v>
+        <v>0.31097351999999989</v>
       </c>
       <c r="F113">
         <v>1726</v>
@@ -9326,7 +9326,7 @@
         <v>14</v>
       </c>
       <c r="E114">
-        <v>0.27122360999999995</v>
+        <v>0.28079620799999999</v>
       </c>
       <c r="F114">
         <v>1967</v>
@@ -9382,7 +9382,7 @@
         <v>14</v>
       </c>
       <c r="E115">
-        <v>0.28776163499999996</v>
+        <v>0.29791792799999994</v>
       </c>
       <c r="F115">
         <v>1967</v>
@@ -9438,7 +9438,7 @@
         <v>14</v>
       </c>
       <c r="E116">
-        <v>0.30769830000000004</v>
+        <v>0.31855824000000005</v>
       </c>
       <c r="F116">
         <v>1726</v>
@@ -9494,7 +9494,7 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>0.294376845</v>
+        <v>0.30476661599999999</v>
       </c>
       <c r="F117">
         <v>1967</v>
@@ -9550,7 +9550,7 @@
         <v>14</v>
       </c>
       <c r="E118">
-        <v>0.30037214999999995</v>
+        <v>0.31097351999999989</v>
       </c>
       <c r="F118">
         <v>1726</v>
@@ -9606,7 +9606,7 @@
         <v>14</v>
       </c>
       <c r="E119">
-        <v>0.28776163499999996</v>
+        <v>0.29791792799999994</v>
       </c>
       <c r="F119">
         <v>1967</v>
@@ -9662,7 +9662,7 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>0.28776163499999996</v>
+        <v>0.29791792799999994</v>
       </c>
       <c r="F120">
         <v>1967</v>
@@ -9718,7 +9718,7 @@
         <v>14</v>
       </c>
       <c r="E121">
-        <v>0.326013675</v>
+        <v>0.33752004000000002</v>
       </c>
       <c r="F121">
         <v>1726</v>
@@ -9774,7 +9774,7 @@
         <v>14</v>
       </c>
       <c r="E122">
-        <v>0.30769830000000004</v>
+        <v>0.31855824000000005</v>
       </c>
       <c r="F122">
         <v>1726</v>
@@ -9830,7 +9830,7 @@
         <v>14</v>
       </c>
       <c r="E123">
-        <v>0.30037214999999995</v>
+        <v>0.31097351999999989</v>
       </c>
       <c r="F123">
         <v>1726</v>
@@ -9886,7 +9886,7 @@
         <v>14</v>
       </c>
       <c r="E124">
-        <v>0.294376845</v>
+        <v>0.30476661599999999</v>
       </c>
       <c r="F124">
         <v>1967</v>
@@ -9942,7 +9942,7 @@
         <v>14</v>
       </c>
       <c r="E125">
-        <v>0.294376845</v>
+        <v>0.30476661599999999</v>
       </c>
       <c r="F125">
         <v>1967</v>
@@ -9998,7 +9998,7 @@
         <v>14</v>
       </c>
       <c r="E126">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F126">
         <v>1365</v>
@@ -10054,7 +10054,7 @@
         <v>14</v>
       </c>
       <c r="E127">
-        <v>0.455175</v>
+        <v>0.47124000000000005</v>
       </c>
       <c r="F127">
         <v>1365</v>
@@ -10110,7 +10110,7 @@
         <v>14</v>
       </c>
       <c r="E128">
-        <v>0.455175</v>
+        <v>0.47124000000000005</v>
       </c>
       <c r="F128">
         <v>1365</v>
@@ -10166,7 +10166,7 @@
         <v>14</v>
       </c>
       <c r="E129">
-        <v>0.455175</v>
+        <v>0.47124000000000005</v>
       </c>
       <c r="F129">
         <v>1365</v>
@@ -10222,7 +10222,7 @@
         <v>14</v>
       </c>
       <c r="E130">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F130">
         <v>1365</v>
@@ -10278,7 +10278,7 @@
         <v>14</v>
       </c>
       <c r="E131">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F131">
         <v>1365</v>
@@ -10334,7 +10334,7 @@
         <v>14</v>
       </c>
       <c r="E132">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F132">
         <v>1365</v>
@@ -10390,7 +10390,7 @@
         <v>14</v>
       </c>
       <c r="E133">
-        <v>0.39827812500000009</v>
+        <v>0.41233500000000006</v>
       </c>
       <c r="F133">
         <v>1365</v>
@@ -10446,7 +10446,7 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>0.39827812500000009</v>
+        <v>0.41233500000000006</v>
       </c>
       <c r="F134">
         <v>1365</v>
@@ -10502,7 +10502,7 @@
         <v>14</v>
       </c>
       <c r="E135">
-        <v>0.39827812500000009</v>
+        <v>0.41233500000000006</v>
       </c>
       <c r="F135">
         <v>1365</v>
@@ -10558,7 +10558,7 @@
         <v>14</v>
       </c>
       <c r="E136">
-        <v>0.39827812500000009</v>
+        <v>0.41233500000000006</v>
       </c>
       <c r="F136">
         <v>1365</v>
@@ -10614,7 +10614,7 @@
         <v>14</v>
       </c>
       <c r="E137">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F137">
         <v>1365</v>
@@ -10670,7 +10670,7 @@
         <v>14</v>
       </c>
       <c r="E138">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F138">
         <v>1365</v>
@@ -10726,7 +10726,7 @@
         <v>14</v>
       </c>
       <c r="E139">
-        <v>0.41345062500000007</v>
+        <v>0.42804300000000006</v>
       </c>
       <c r="F139">
         <v>1365</v>
@@ -10782,7 +10782,7 @@
         <v>14</v>
       </c>
       <c r="E140">
-        <v>0.41345062500000007</v>
+        <v>0.42804300000000006</v>
       </c>
       <c r="F140">
         <v>1365</v>
@@ -10838,7 +10838,7 @@
         <v>14</v>
       </c>
       <c r="E141">
-        <v>0.41345062500000007</v>
+        <v>0.42804300000000006</v>
       </c>
       <c r="F141">
         <v>1365</v>
@@ -10894,7 +10894,7 @@
         <v>14</v>
       </c>
       <c r="E142">
-        <v>0.455175</v>
+        <v>0.47124000000000005</v>
       </c>
       <c r="F142">
         <v>1365</v>
@@ -10950,7 +10950,7 @@
         <v>14</v>
       </c>
       <c r="E143">
-        <v>0.455175</v>
+        <v>0.47124000000000005</v>
       </c>
       <c r="F143">
         <v>1365</v>
@@ -11006,7 +11006,7 @@
         <v>14</v>
       </c>
       <c r="E144">
-        <v>0.455175</v>
+        <v>0.47124000000000005</v>
       </c>
       <c r="F144">
         <v>1365</v>
@@ -11062,7 +11062,7 @@
         <v>14</v>
       </c>
       <c r="E145">
-        <v>0.34138125000000002</v>
+        <v>0.35343000000000002</v>
       </c>
       <c r="F145">
         <v>1365</v>
@@ -11118,7 +11118,7 @@
         <v>14</v>
       </c>
       <c r="E146">
-        <v>0.34138125000000002</v>
+        <v>0.35343000000000002</v>
       </c>
       <c r="F146">
         <v>1365</v>
@@ -11174,7 +11174,7 @@
         <v>14</v>
       </c>
       <c r="E147">
-        <v>0.39827812500000009</v>
+        <v>0.41233500000000006</v>
       </c>
       <c r="F147">
         <v>1365</v>
@@ -11230,7 +11230,7 @@
         <v>14</v>
       </c>
       <c r="E148">
-        <v>0.41345062500000007</v>
+        <v>0.42804300000000006</v>
       </c>
       <c r="F148">
         <v>1365</v>
@@ -11286,7 +11286,7 @@
         <v>14</v>
       </c>
       <c r="E149">
-        <v>0.39827812500000009</v>
+        <v>0.41233500000000006</v>
       </c>
       <c r="F149">
         <v>1365</v>
@@ -11342,7 +11342,7 @@
         <v>14</v>
       </c>
       <c r="E150">
-        <v>0.39827812500000009</v>
+        <v>0.41233500000000006</v>
       </c>
       <c r="F150">
         <v>1365</v>
@@ -11398,7 +11398,7 @@
         <v>14</v>
       </c>
       <c r="E151">
-        <v>0.455175</v>
+        <v>0.47124000000000005</v>
       </c>
       <c r="F151">
         <v>1365</v>
@@ -11454,7 +11454,7 @@
         <v>14</v>
       </c>
       <c r="E152">
-        <v>0.455175</v>
+        <v>0.47124000000000005</v>
       </c>
       <c r="F152">
         <v>1365</v>
@@ -11510,7 +11510,7 @@
         <v>14</v>
       </c>
       <c r="E153">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F153">
         <v>1365</v>
@@ -11566,7 +11566,7 @@
         <v>14</v>
       </c>
       <c r="E154">
-        <v>0.455175</v>
+        <v>0.47124000000000005</v>
       </c>
       <c r="F154">
         <v>1365</v>
@@ -11622,7 +11622,7 @@
         <v>14</v>
       </c>
       <c r="E155">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F155">
         <v>1365</v>
@@ -11657,7 +11657,7 @@
         <v>14</v>
       </c>
       <c r="E156">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F156">
         <v>1365</v>
@@ -11692,7 +11692,7 @@
         <v>14</v>
       </c>
       <c r="E157">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F157">
         <v>1365</v>
@@ -11727,7 +11727,7 @@
         <v>14</v>
       </c>
       <c r="E158">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F158">
         <v>1365</v>
@@ -11762,7 +11762,7 @@
         <v>14</v>
       </c>
       <c r="E159">
-        <v>0.41345062500000007</v>
+        <v>0.42804300000000006</v>
       </c>
       <c r="F159">
         <v>1365</v>
@@ -11797,7 +11797,7 @@
         <v>14</v>
       </c>
       <c r="E160">
-        <v>0.41345062500000007</v>
+        <v>0.42804300000000006</v>
       </c>
       <c r="F160">
         <v>1365</v>
@@ -11832,7 +11832,7 @@
         <v>14</v>
       </c>
       <c r="E161">
-        <v>0.41345062500000007</v>
+        <v>0.42804300000000006</v>
       </c>
       <c r="F161">
         <v>1365</v>
@@ -11867,7 +11867,7 @@
         <v>14</v>
       </c>
       <c r="E162">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F162">
         <v>1365</v>
@@ -11902,7 +11902,7 @@
         <v>14</v>
       </c>
       <c r="E163">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F163">
         <v>1365</v>
@@ -11937,7 +11937,7 @@
         <v>14</v>
       </c>
       <c r="E164">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F164">
         <v>1365</v>
@@ -11972,7 +11972,7 @@
         <v>14</v>
       </c>
       <c r="E165">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F165">
         <v>1365</v>
@@ -12007,7 +12007,7 @@
         <v>14</v>
       </c>
       <c r="E166">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F166">
         <v>1365</v>
@@ -12042,7 +12042,7 @@
         <v>14</v>
       </c>
       <c r="E167">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F167">
         <v>1365</v>
@@ -12077,7 +12077,7 @@
         <v>14</v>
       </c>
       <c r="E168">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F168">
         <v>1365</v>
@@ -12112,7 +12112,7 @@
         <v>14</v>
       </c>
       <c r="E169">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F169">
         <v>1365</v>
@@ -12147,7 +12147,7 @@
         <v>14</v>
       </c>
       <c r="E170">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F170">
         <v>1365</v>
@@ -12182,7 +12182,7 @@
         <v>14</v>
       </c>
       <c r="E171">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F171">
         <v>1365</v>
@@ -12217,7 +12217,7 @@
         <v>14</v>
       </c>
       <c r="E172">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F172">
         <v>1365</v>
@@ -12252,7 +12252,7 @@
         <v>14</v>
       </c>
       <c r="E173">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F173">
         <v>1365</v>
@@ -12287,7 +12287,7 @@
         <v>14</v>
       </c>
       <c r="E174">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F174">
         <v>1365</v>
@@ -12322,7 +12322,7 @@
         <v>14</v>
       </c>
       <c r="E175">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F175">
         <v>1365</v>
@@ -12357,7 +12357,7 @@
         <v>14</v>
       </c>
       <c r="E176">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F176">
         <v>1365</v>
@@ -12392,7 +12392,7 @@
         <v>14</v>
       </c>
       <c r="E177">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F177">
         <v>1365</v>
@@ -12427,7 +12427,7 @@
         <v>14</v>
       </c>
       <c r="E178">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F178">
         <v>1365</v>
@@ -12462,7 +12462,7 @@
         <v>14</v>
       </c>
       <c r="E179">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F179">
         <v>1365</v>
@@ -12497,7 +12497,7 @@
         <v>14</v>
       </c>
       <c r="E180">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F180">
         <v>1365</v>
@@ -12532,7 +12532,7 @@
         <v>14</v>
       </c>
       <c r="E181">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F181">
         <v>1365</v>
@@ -12567,7 +12567,7 @@
         <v>14</v>
       </c>
       <c r="E182">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F182">
         <v>1365</v>
@@ -12602,7 +12602,7 @@
         <v>14</v>
       </c>
       <c r="E183">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F183">
         <v>1365</v>
@@ -12637,7 +12637,7 @@
         <v>14</v>
       </c>
       <c r="E184">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F184">
         <v>1365</v>
@@ -12672,7 +12672,7 @@
         <v>14</v>
       </c>
       <c r="E185">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F185">
         <v>1365</v>
@@ -12707,7 +12707,7 @@
         <v>14</v>
       </c>
       <c r="E186">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F186">
         <v>1365</v>
@@ -12742,7 +12742,7 @@
         <v>14</v>
       </c>
       <c r="E187">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F187">
         <v>1365</v>
@@ -12777,7 +12777,7 @@
         <v>14</v>
       </c>
       <c r="E188">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F188">
         <v>1365</v>
@@ -12812,7 +12812,7 @@
         <v>14</v>
       </c>
       <c r="E189">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F189">
         <v>1365</v>
@@ -12847,7 +12847,7 @@
         <v>14</v>
       </c>
       <c r="E190">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F190">
         <v>1365</v>
@@ -12882,7 +12882,7 @@
         <v>14</v>
       </c>
       <c r="E191">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F191">
         <v>1365</v>
@@ -12917,7 +12917,7 @@
         <v>14</v>
       </c>
       <c r="E192">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F192">
         <v>1365</v>
@@ -12952,7 +12952,7 @@
         <v>14</v>
       </c>
       <c r="E193">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F193">
         <v>1365</v>
@@ -12987,7 +12987,7 @@
         <v>14</v>
       </c>
       <c r="E194">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F194">
         <v>1365</v>
@@ -13022,7 +13022,7 @@
         <v>14</v>
       </c>
       <c r="E195">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F195">
         <v>1365</v>
@@ -13057,7 +13057,7 @@
         <v>14</v>
       </c>
       <c r="E196">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F196">
         <v>1365</v>
@@ -13092,7 +13092,7 @@
         <v>14</v>
       </c>
       <c r="E197">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F197">
         <v>1365</v>
@@ -13127,7 +13127,7 @@
         <v>14</v>
       </c>
       <c r="E198">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F198">
         <v>1365</v>
@@ -13162,7 +13162,7 @@
         <v>14</v>
       </c>
       <c r="E199">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F199">
         <v>1365</v>
@@ -13197,7 +13197,7 @@
         <v>14</v>
       </c>
       <c r="E200">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F200">
         <v>1365</v>
@@ -13232,7 +13232,7 @@
         <v>14</v>
       </c>
       <c r="E201">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F201">
         <v>1365</v>
@@ -13267,7 +13267,7 @@
         <v>14</v>
       </c>
       <c r="E202">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F202">
         <v>1365</v>
@@ -13302,7 +13302,7 @@
         <v>14</v>
       </c>
       <c r="E203">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F203">
         <v>1365</v>
@@ -13337,7 +13337,7 @@
         <v>14</v>
       </c>
       <c r="E204">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F204">
         <v>1365</v>
@@ -13372,7 +13372,7 @@
         <v>14</v>
       </c>
       <c r="E205">
-        <v>0.44000250000000002</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="F205">
         <v>1365</v>
@@ -13407,7 +13407,7 @@
         <v>14</v>
       </c>
       <c r="E206">
-        <v>0.24276000000000003</v>
+        <v>0.25132800000000005</v>
       </c>
       <c r="F206">
         <v>1365</v>
@@ -13442,7 +13442,7 @@
         <v>14</v>
       </c>
       <c r="E207">
-        <v>0.24276000000000003</v>
+        <v>0.25132800000000005</v>
       </c>
       <c r="F207">
         <v>1365</v>
@@ -13477,7 +13477,7 @@
         <v>14</v>
       </c>
       <c r="E208">
-        <v>0.27310499999999999</v>
+        <v>0.28274400000000005</v>
       </c>
       <c r="F208">
         <v>1365</v>
@@ -13512,7 +13512,7 @@
         <v>14</v>
       </c>
       <c r="E209">
-        <v>0.27310499999999999</v>
+        <v>0.28274400000000005</v>
       </c>
       <c r="F209">
         <v>1365</v>
@@ -13547,7 +13547,7 @@
         <v>14</v>
       </c>
       <c r="E210">
-        <v>0.27310499999999999</v>
+        <v>0.28274400000000005</v>
       </c>
       <c r="F210">
         <v>1365</v>
@@ -13582,7 +13582,7 @@
         <v>14</v>
       </c>
       <c r="E211">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F211">
         <v>1365</v>
@@ -13617,7 +13617,7 @@
         <v>14</v>
       </c>
       <c r="E212">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F212">
         <v>1365</v>
@@ -13652,7 +13652,7 @@
         <v>14</v>
       </c>
       <c r="E213">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F213">
         <v>1365</v>
@@ -13687,7 +13687,7 @@
         <v>14</v>
       </c>
       <c r="E214">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F214">
         <v>1365</v>
@@ -13722,7 +13722,7 @@
         <v>14</v>
       </c>
       <c r="E215">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F215">
         <v>1365</v>
@@ -13757,7 +13757,7 @@
         <v>14</v>
       </c>
       <c r="E216">
-        <v>0.26551874999999997</v>
+        <v>0.27489000000000002</v>
       </c>
       <c r="F216">
         <v>1365</v>
@@ -13792,7 +13792,7 @@
         <v>14</v>
       </c>
       <c r="E217">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F217">
         <v>1365</v>
@@ -13827,7 +13827,7 @@
         <v>14</v>
       </c>
       <c r="E218">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F218">
         <v>1365</v>
@@ -13862,7 +13862,7 @@
         <v>14</v>
       </c>
       <c r="E219">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F219">
         <v>1365</v>
@@ -13897,7 +13897,7 @@
         <v>14</v>
       </c>
       <c r="E220">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F220">
         <v>1365</v>
@@ -13932,7 +13932,7 @@
         <v>14</v>
       </c>
       <c r="E221">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F221">
         <v>1365</v>
@@ -13967,7 +13967,7 @@
         <v>14</v>
       </c>
       <c r="E222">
-        <v>0.26551874999999997</v>
+        <v>0.27489000000000002</v>
       </c>
       <c r="F222">
         <v>1365</v>
@@ -14002,7 +14002,7 @@
         <v>14</v>
       </c>
       <c r="E223">
-        <v>0.26551874999999997</v>
+        <v>0.27489000000000002</v>
       </c>
       <c r="F223">
         <v>1365</v>
@@ -14037,7 +14037,7 @@
         <v>14</v>
       </c>
       <c r="E224">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F224">
         <v>1365</v>
@@ -14072,7 +14072,7 @@
         <v>14</v>
       </c>
       <c r="E225">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F225">
         <v>1365</v>
@@ -14107,7 +14107,7 @@
         <v>14</v>
       </c>
       <c r="E226">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F226">
         <v>1365</v>
@@ -14142,7 +14142,7 @@
         <v>14</v>
       </c>
       <c r="E227">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F227">
         <v>1365</v>
@@ -14177,7 +14177,7 @@
         <v>14</v>
       </c>
       <c r="E228">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F228">
         <v>1365</v>
@@ -14212,7 +14212,7 @@
         <v>14</v>
       </c>
       <c r="E229">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F229">
         <v>1365</v>
@@ -14247,7 +14247,7 @@
         <v>14</v>
       </c>
       <c r="E230">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F230">
         <v>1365</v>
@@ -14282,7 +14282,7 @@
         <v>14</v>
       </c>
       <c r="E231">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F231">
         <v>1365</v>
@@ -14317,7 +14317,7 @@
         <v>14</v>
       </c>
       <c r="E232">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F232">
         <v>1365</v>
@@ -14352,7 +14352,7 @@
         <v>14</v>
       </c>
       <c r="E233">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F233">
         <v>1365</v>
@@ -14387,7 +14387,7 @@
         <v>14</v>
       </c>
       <c r="E234">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F234">
         <v>1365</v>
@@ -14422,7 +14422,7 @@
         <v>14</v>
       </c>
       <c r="E235">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F235">
         <v>1365</v>
@@ -14457,7 +14457,7 @@
         <v>14</v>
       </c>
       <c r="E236">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F236">
         <v>1365</v>
@@ -14492,7 +14492,7 @@
         <v>14</v>
       </c>
       <c r="E237">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F237">
         <v>1365</v>
@@ -14527,7 +14527,7 @@
         <v>14</v>
       </c>
       <c r="E238">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F238">
         <v>1365</v>
@@ -14562,7 +14562,7 @@
         <v>14</v>
       </c>
       <c r="E239">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F239">
         <v>1365</v>
@@ -14597,7 +14597,7 @@
         <v>14</v>
       </c>
       <c r="E240">
-        <v>0.27689812499999999</v>
+        <v>0.28667100000000001</v>
       </c>
       <c r="F240">
         <v>1365</v>
@@ -14632,7 +14632,7 @@
         <v>14</v>
       </c>
       <c r="E241">
-        <v>0.2275875</v>
+        <v>0.23562000000000002</v>
       </c>
       <c r="F241">
         <v>1365</v>
@@ -14667,7 +14667,7 @@
         <v>14</v>
       </c>
       <c r="E242">
-        <v>0.2275875</v>
+        <v>0.23562000000000002</v>
       </c>
       <c r="F242">
         <v>1365</v>
@@ -14702,7 +14702,7 @@
         <v>14</v>
       </c>
       <c r="E243">
-        <v>0.2275875</v>
+        <v>0.23562000000000002</v>
       </c>
       <c r="F243">
         <v>1365</v>
@@ -14737,7 +14737,7 @@
         <v>14</v>
       </c>
       <c r="E244">
-        <v>0.24276000000000003</v>
+        <v>0.25132800000000005</v>
       </c>
       <c r="F244">
         <v>1365</v>
@@ -14772,7 +14772,7 @@
         <v>14</v>
       </c>
       <c r="E245">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F245">
         <v>1365</v>
@@ -14807,7 +14807,7 @@
         <v>14</v>
       </c>
       <c r="E246">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F246">
         <v>1365</v>
@@ -14842,7 +14842,7 @@
         <v>14</v>
       </c>
       <c r="E247">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F247">
         <v>1365</v>
@@ -14877,7 +14877,7 @@
         <v>14</v>
       </c>
       <c r="E248">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F248">
         <v>1365</v>
@@ -14912,7 +14912,7 @@
         <v>14</v>
       </c>
       <c r="E249">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F249">
         <v>1365</v>
@@ -14947,7 +14947,7 @@
         <v>14</v>
       </c>
       <c r="E250">
-        <v>0.24276000000000003</v>
+        <v>0.25132800000000005</v>
       </c>
       <c r="F250">
         <v>1365</v>
@@ -14982,7 +14982,7 @@
         <v>14</v>
       </c>
       <c r="E251">
-        <v>0.24276000000000003</v>
+        <v>0.25132800000000005</v>
       </c>
       <c r="F251">
         <v>1365</v>
@@ -15017,7 +15017,7 @@
         <v>14</v>
       </c>
       <c r="E252">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F252">
         <v>1365</v>
@@ -15052,7 +15052,7 @@
         <v>14</v>
       </c>
       <c r="E253">
-        <v>0.25034624999999999</v>
+        <v>0.25918200000000002</v>
       </c>
       <c r="F253">
         <v>1365</v>
@@ -15087,7 +15087,7 @@
         <v>14</v>
       </c>
       <c r="E254">
-        <v>0.24276000000000003</v>
+        <v>0.25132800000000011</v>
       </c>
       <c r="F254">
         <v>1365</v>
@@ -15122,7 +15122,7 @@
         <v>14</v>
       </c>
       <c r="E255">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F255">
         <v>1365</v>
@@ -15157,7 +15157,7 @@
         <v>14</v>
       </c>
       <c r="E256">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F256">
         <v>1365</v>
@@ -15192,7 +15192,7 @@
         <v>14</v>
       </c>
       <c r="E257">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F257">
         <v>1365</v>
@@ -15227,7 +15227,7 @@
         <v>14</v>
       </c>
       <c r="E258">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F258">
         <v>1365</v>
@@ -15262,7 +15262,7 @@
         <v>14</v>
       </c>
       <c r="E259">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F259">
         <v>1365</v>
@@ -15297,7 +15297,7 @@
         <v>14</v>
       </c>
       <c r="E260">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F260">
         <v>1365</v>
@@ -15332,7 +15332,7 @@
         <v>14</v>
       </c>
       <c r="E261">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F261">
         <v>1365</v>
@@ -15367,7 +15367,7 @@
         <v>14</v>
       </c>
       <c r="E262">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F262">
         <v>1365</v>
@@ -15402,7 +15402,7 @@
         <v>14</v>
       </c>
       <c r="E263">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F263">
         <v>1365</v>
@@ -15437,7 +15437,7 @@
         <v>14</v>
       </c>
       <c r="E264">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F264">
         <v>1365</v>
@@ -15472,7 +15472,7 @@
         <v>14</v>
       </c>
       <c r="E265">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F265">
         <v>1365</v>
@@ -15507,7 +15507,7 @@
         <v>14</v>
       </c>
       <c r="E266">
-        <v>0.25793250000000006</v>
+        <v>0.26703600000000005</v>
       </c>
       <c r="F266">
         <v>1365</v>
@@ -15537,7 +15537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C63898D-D74E-4D56-A3CD-CD0457031BB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF30874D-D643-4E7E-AF92-BED16D323B10}">
   <dimension ref="B9:T586"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15622,7 +15622,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G11">
-        <v>0.19941000000000003</v>
+        <v>0.20644799999999999</v>
       </c>
       <c r="H11">
         <v>5670</v>
@@ -15675,7 +15675,7 @@
         <v>0.04</v>
       </c>
       <c r="G12">
-        <v>0.22108500000000003</v>
+        <v>0.22888800000000004</v>
       </c>
       <c r="H12">
         <v>5670</v>
@@ -15728,7 +15728,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="G13">
-        <v>0.24276</v>
+        <v>0.251328</v>
       </c>
       <c r="H13">
         <v>5670</v>
@@ -15781,7 +15781,7 @@
         <v>0.1663</v>
       </c>
       <c r="G14">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H14">
         <v>5670</v>
@@ -15834,7 +15834,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G15">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H15">
         <v>5670</v>
@@ -15887,7 +15887,7 @@
         <v>0.11652999999999999</v>
       </c>
       <c r="G16">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H16">
         <v>5670</v>
@@ -15940,7 +15940,7 @@
         <v>0.04</v>
       </c>
       <c r="G17">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H17">
         <v>5670</v>
@@ -15993,7 +15993,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G18">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H18">
         <v>5670</v>
@@ -16046,7 +16046,7 @@
         <v>0.09</v>
       </c>
       <c r="G19">
-        <v>0.2601</v>
+        <v>0.26927999999999996</v>
       </c>
       <c r="H19">
         <v>5670</v>
@@ -16099,7 +16099,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
       <c r="G20">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H20">
         <v>5670</v>
@@ -16152,7 +16152,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G21">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H21">
         <v>5670</v>
@@ -16205,7 +16205,7 @@
         <v>1.5011700000000001</v>
       </c>
       <c r="G22">
-        <v>0.30345</v>
+        <v>0.31415999999999999</v>
       </c>
       <c r="H22">
         <v>4200</v>
@@ -16258,7 +16258,7 @@
         <v>0.112</v>
       </c>
       <c r="G23">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H23">
         <v>4829.9999999999991</v>
@@ -16311,7 +16311,7 @@
         <v>0.05</v>
       </c>
       <c r="G24">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H24">
         <v>5670</v>
@@ -16364,7 +16364,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G25">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H25">
         <v>4829.9999999999991</v>
@@ -16417,7 +16417,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G26">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H26">
         <v>4829.9999999999991</v>
@@ -16470,7 +16470,7 @@
         <v>0.05</v>
       </c>
       <c r="G27">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H27">
         <v>5670</v>
@@ -16523,7 +16523,7 @@
         <v>0.05</v>
       </c>
       <c r="G28">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H28">
         <v>5670</v>
@@ -16576,7 +16576,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="G29">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H29">
         <v>4829.9999999999991</v>
@@ -16629,7 +16629,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G30">
-        <v>0.26876999999999995</v>
+        <v>0.278256</v>
       </c>
       <c r="H30">
         <v>4829.9999999999991</v>
@@ -16682,7 +16682,7 @@
         <v>0.05</v>
       </c>
       <c r="G31">
-        <v>0.221085</v>
+        <v>0.22888800000000001</v>
       </c>
       <c r="H31">
         <v>5670</v>
@@ -16735,7 +16735,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G32">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H32">
         <v>4829.9999999999991</v>
@@ -16788,7 +16788,7 @@
         <v>0.05</v>
       </c>
       <c r="G33">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H33">
         <v>5670</v>
@@ -16841,7 +16841,7 @@
         <v>0.05</v>
       </c>
       <c r="G34">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H34">
         <v>5670</v>
@@ -16894,7 +16894,7 @@
         <v>0.05</v>
       </c>
       <c r="G35">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H35">
         <v>5670</v>
@@ -16947,7 +16947,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G36">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H36">
         <v>4829.9999999999991</v>
@@ -17000,7 +17000,7 @@
         <v>0.112</v>
       </c>
       <c r="G37">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H37">
         <v>4829.9999999999991</v>
@@ -17053,7 +17053,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G38">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H38">
         <v>4829.9999999999991</v>
@@ -17106,7 +17106,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G39">
-        <v>0.26876999999999995</v>
+        <v>0.278256</v>
       </c>
       <c r="H39">
         <v>4829.9999999999991</v>
@@ -17159,7 +17159,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G40">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H40">
         <v>4829.9999999999991</v>
@@ -17212,7 +17212,7 @@
         <v>0.05</v>
       </c>
       <c r="G41">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H41">
         <v>5670</v>
@@ -17265,7 +17265,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G42">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H42">
         <v>4829.9999999999991</v>
@@ -17318,7 +17318,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G43">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H43">
         <v>4829.9999999999991</v>
@@ -17371,7 +17371,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G44">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H44">
         <v>4829.9999999999991</v>
@@ -17424,7 +17424,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G45">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H45">
         <v>4829.9999999999991</v>
@@ -17477,7 +17477,7 @@
         <v>0.05</v>
       </c>
       <c r="G46">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H46">
         <v>5670</v>
@@ -17530,7 +17530,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G47">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H47">
         <v>4829.9999999999991</v>
@@ -17583,7 +17583,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G48">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H48">
         <v>4829.9999999999991</v>
@@ -17636,7 +17636,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G49">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H49">
         <v>4829.9999999999991</v>
@@ -17689,7 +17689,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G50">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H50">
         <v>4829.9999999999991</v>
@@ -17742,7 +17742,7 @@
         <v>0.2</v>
       </c>
       <c r="G51">
-        <v>0.221085</v>
+        <v>0.22888800000000001</v>
       </c>
       <c r="H51">
         <v>4829.9999999999991</v>
@@ -17795,7 +17795,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="G52">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H52">
         <v>4829.9999999999991</v>
@@ -17848,7 +17848,7 @@
         <v>0.112</v>
       </c>
       <c r="G53">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H53">
         <v>4829.9999999999991</v>
@@ -17901,7 +17901,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="G54">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H54">
         <v>4829.9999999999991</v>
@@ -17954,7 +17954,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G55">
-        <v>0.26876999999999995</v>
+        <v>0.278256</v>
       </c>
       <c r="H55">
         <v>4829.9999999999991</v>
@@ -18007,7 +18007,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G56">
-        <v>0.26876999999999995</v>
+        <v>0.278256</v>
       </c>
       <c r="H56">
         <v>4829.9999999999991</v>
@@ -18060,7 +18060,7 @@
         <v>0.05</v>
       </c>
       <c r="G57">
-        <v>0.19940999999999998</v>
+        <v>0.20644799999999999</v>
       </c>
       <c r="H57">
         <v>5670</v>
@@ -18113,7 +18113,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G58">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H58">
         <v>4829.9999999999991</v>
@@ -18166,7 +18166,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G59">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H59">
         <v>4829.9999999999991</v>
@@ -18219,7 +18219,7 @@
         <v>0.05</v>
       </c>
       <c r="G60">
-        <v>0.24276</v>
+        <v>0.251328</v>
       </c>
       <c r="H60">
         <v>5670</v>
@@ -18272,7 +18272,7 @@
         <v>0.05</v>
       </c>
       <c r="G61">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H61">
         <v>5670</v>
@@ -18325,7 +18325,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G62">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H62">
         <v>4829.9999999999991</v>
@@ -18378,7 +18378,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="G63">
-        <v>0.26876999999999995</v>
+        <v>0.278256</v>
       </c>
       <c r="H63">
         <v>4829.9999999999991</v>
@@ -18431,7 +18431,7 @@
         <v>0.05</v>
       </c>
       <c r="G64">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H64">
         <v>5670</v>
@@ -18484,7 +18484,7 @@
         <v>0.05</v>
       </c>
       <c r="G65">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H65">
         <v>5670</v>
@@ -18537,7 +18537,7 @@
         <v>0.08</v>
       </c>
       <c r="G66">
-        <v>0.26876999999999995</v>
+        <v>0.278256</v>
       </c>
       <c r="H66">
         <v>4829.9999999999991</v>
@@ -18590,7 +18590,7 @@
         <v>0.05</v>
       </c>
       <c r="G67">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H67">
         <v>5670</v>
@@ -18643,7 +18643,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G68">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H68">
         <v>4829.9999999999991</v>
@@ -18696,7 +18696,7 @@
         <v>0.05</v>
       </c>
       <c r="G69">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H69">
         <v>5670</v>
@@ -18749,7 +18749,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="G70">
-        <v>0.26876999999999995</v>
+        <v>0.278256</v>
       </c>
       <c r="H70">
         <v>4829.9999999999991</v>
@@ -18802,7 +18802,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G71">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H71">
         <v>4829.9999999999991</v>
@@ -18855,7 +18855,7 @@
         <v>0.05</v>
       </c>
       <c r="G72">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H72">
         <v>5670</v>
@@ -18908,7 +18908,7 @@
         <v>0.05</v>
       </c>
       <c r="G73">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H73">
         <v>5670</v>
@@ -18961,7 +18961,7 @@
         <v>0.05</v>
       </c>
       <c r="G74">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H74">
         <v>5670</v>
@@ -19014,7 +19014,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G75">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H75">
         <v>4829.9999999999991</v>
@@ -19067,7 +19067,7 @@
         <v>0.112</v>
       </c>
       <c r="G76">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H76">
         <v>4829.9999999999991</v>
@@ -19120,7 +19120,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G77">
-        <v>0.26876999999999995</v>
+        <v>0.278256</v>
       </c>
       <c r="H77">
         <v>4829.9999999999991</v>
@@ -19173,7 +19173,7 @@
         <v>0.05</v>
       </c>
       <c r="G78">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H78">
         <v>5670</v>
@@ -19226,7 +19226,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="G79">
-        <v>0.26876999999999995</v>
+        <v>0.278256</v>
       </c>
       <c r="H79">
         <v>4829.9999999999991</v>
@@ -19279,7 +19279,7 @@
         <v>0.14899999999999999</v>
       </c>
       <c r="G80">
-        <v>0.29911499999999996</v>
+        <v>0.309672</v>
       </c>
       <c r="H80">
         <v>3174</v>
@@ -19332,7 +19332,7 @@
         <v>0.05</v>
       </c>
       <c r="G81">
-        <v>0.29044500000000001</v>
+        <v>0.30069600000000002</v>
       </c>
       <c r="H81">
         <v>3726</v>
@@ -19385,7 +19385,7 @@
         <v>3.85E-2</v>
       </c>
       <c r="G82">
-        <v>0.29911499999999996</v>
+        <v>0.309672</v>
       </c>
       <c r="H82">
         <v>3726</v>
@@ -19438,7 +19438,7 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="G83">
-        <v>0.3468</v>
+        <v>0.35904000000000003</v>
       </c>
       <c r="H83">
         <v>5796</v>
@@ -19491,7 +19491,7 @@
         <v>0.54300000000000004</v>
       </c>
       <c r="G84">
-        <v>0.37714499999999995</v>
+        <v>0.39045599999999997</v>
       </c>
       <c r="H84">
         <v>5040</v>
@@ -19544,7 +19544,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G85">
-        <v>0.37714499999999995</v>
+        <v>0.39045599999999997</v>
       </c>
       <c r="H85">
         <v>5040</v>
@@ -19597,7 +19597,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G86">
-        <v>0.24276</v>
+        <v>0.251328</v>
       </c>
       <c r="H86">
         <v>2760</v>
@@ -19650,7 +19650,7 @@
         <v>0.03</v>
       </c>
       <c r="G87">
-        <v>0.23409000000000002</v>
+        <v>0.24235200000000004</v>
       </c>
       <c r="H87">
         <v>3240</v>
@@ -19703,7 +19703,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G88">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H88">
         <v>2760</v>
@@ -19756,7 +19756,7 @@
         <v>0.25</v>
       </c>
       <c r="G89">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H89">
         <v>2760</v>
@@ -19809,7 +19809,7 @@
         <v>0.25</v>
       </c>
       <c r="G90">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H90">
         <v>2760</v>
@@ -19862,7 +19862,7 @@
         <v>0.5</v>
       </c>
       <c r="G91">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H91">
         <v>2760</v>
@@ -19915,7 +19915,7 @@
         <v>0.25</v>
       </c>
       <c r="G92">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H92">
         <v>2760</v>
@@ -19968,7 +19968,7 @@
         <v>0.25</v>
       </c>
       <c r="G93">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H93">
         <v>2760</v>
@@ -20021,7 +20021,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="G94">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H94">
         <v>2760</v>
@@ -20074,7 +20074,7 @@
         <v>0.189</v>
       </c>
       <c r="G95">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H95">
         <v>2760</v>
@@ -20127,7 +20127,7 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="G96">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H96">
         <v>2760</v>
@@ -20180,7 +20180,7 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="G97">
-        <v>0.29021684210526316</v>
+        <v>0.30045978947368429</v>
       </c>
       <c r="H97">
         <v>2494.7368421052633</v>
@@ -20233,7 +20233,7 @@
         <v>0.35</v>
       </c>
       <c r="G98">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H98">
         <v>2400</v>
@@ -20286,7 +20286,7 @@
         <v>0.35</v>
       </c>
       <c r="G99">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H99">
         <v>2400</v>
@@ -20339,7 +20339,7 @@
         <v>0.27</v>
       </c>
       <c r="G100">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H100">
         <v>2760</v>
@@ -20392,7 +20392,7 @@
         <v>0.21299999999999999</v>
       </c>
       <c r="G101">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H101">
         <v>2760</v>
@@ -20445,7 +20445,7 @@
         <v>0.44600000000000001</v>
       </c>
       <c r="G102">
-        <v>0.28527410313901341</v>
+        <v>0.29534260089686099</v>
       </c>
       <c r="H102">
         <v>2806.2780269058294</v>
@@ -20498,7 +20498,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G103">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H103">
         <v>3240</v>
@@ -20551,7 +20551,7 @@
         <v>0.28699999999999998</v>
       </c>
       <c r="G104">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H104">
         <v>2760</v>
@@ -20604,7 +20604,7 @@
         <v>0.14899999999999999</v>
       </c>
       <c r="G105">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H105">
         <v>2760</v>
@@ -20657,7 +20657,7 @@
         <v>0.10579999999999999</v>
       </c>
       <c r="G106">
-        <v>0.29150211720226843</v>
+        <v>0.30179042722117211</v>
       </c>
       <c r="H106">
         <v>2941.4744801512288</v>
@@ -20710,7 +20710,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="G107">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H107">
         <v>2760</v>
@@ -20763,7 +20763,7 @@
         <v>0.1226</v>
       </c>
       <c r="G108">
-        <v>0.29141383360522027</v>
+        <v>0.30169902773246332</v>
       </c>
       <c r="H108">
         <v>2946.3621533442088</v>
@@ -20816,7 +20816,7 @@
         <v>0.156</v>
       </c>
       <c r="G109">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H109">
         <v>2760</v>
@@ -20869,7 +20869,7 @@
         <v>0.156</v>
       </c>
       <c r="G110">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H110">
         <v>2760</v>
@@ -20922,7 +20922,7 @@
         <v>0.19850000000000001</v>
       </c>
       <c r="G111">
-        <v>0.29261795969773302</v>
+        <v>0.30294565239294713</v>
       </c>
       <c r="H111">
         <v>2879.6977329974811</v>
@@ -20975,7 +20975,7 @@
         <v>0.10249999999999999</v>
       </c>
       <c r="G112">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H112">
         <v>2760</v>
@@ -21028,7 +21028,7 @@
         <v>0.11</v>
       </c>
       <c r="G113">
-        <v>0.2947800000000001</v>
+        <v>0.30518400000000012</v>
       </c>
       <c r="H113">
         <v>2760</v>
@@ -21081,7 +21081,7 @@
         <v>0.65300000000000002</v>
       </c>
       <c r="G114">
-        <v>0.29477999999999999</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H114">
         <v>2760</v>
@@ -21134,7 +21134,7 @@
         <v>0.29799999999999999</v>
       </c>
       <c r="G115">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H115">
         <v>2760</v>
@@ -21187,7 +21187,7 @@
         <v>0.14499999999999999</v>
       </c>
       <c r="G116">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H116">
         <v>2760</v>
@@ -21240,7 +21240,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G117">
-        <v>0.30518400000000001</v>
+        <v>0.31595519999999999</v>
       </c>
       <c r="H117">
         <v>2544</v>
@@ -21293,7 +21293,7 @@
         <v>0.438</v>
       </c>
       <c r="G118">
-        <v>0.29477999999999999</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H118">
         <v>2760</v>
@@ -21346,7 +21346,7 @@
         <v>0.46029999999999999</v>
       </c>
       <c r="G119">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H119">
         <v>2760</v>
@@ -21399,7 +21399,7 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="G120">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H120">
         <v>2760</v>
@@ -21452,7 +21452,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G121">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H121">
         <v>3240</v>
@@ -21505,7 +21505,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="G122">
-        <v>0.29180317596566524</v>
+        <v>0.30210211158798289</v>
       </c>
       <c r="H122">
         <v>2924.8068669527897</v>
@@ -21558,7 +21558,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="G123">
-        <v>0.29405034653465345</v>
+        <v>0.30442859405940598</v>
       </c>
       <c r="H123">
         <v>2800.3960396039606</v>
@@ -21611,7 +21611,7 @@
         <v>0.11</v>
       </c>
       <c r="G124">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H124">
         <v>2760</v>
@@ -21664,7 +21664,7 @@
         <v>7.3799999999999991E-2</v>
       </c>
       <c r="G125">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H125">
         <v>3240</v>
@@ -21717,7 +21717,7 @@
         <v>0.03</v>
       </c>
       <c r="G126">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H126">
         <v>3240</v>
@@ -21770,7 +21770,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="G127">
-        <v>0.29477999999999999</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H127">
         <v>2760</v>
@@ -21823,7 +21823,7 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="G128">
-        <v>0.29415056206088996</v>
+        <v>0.30453234660421552</v>
       </c>
       <c r="H128">
         <v>2794.8477751756441</v>
@@ -21876,7 +21876,7 @@
         <v>0.112</v>
       </c>
       <c r="G129">
-        <v>0.29477999999999999</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H129">
         <v>2760</v>
@@ -21929,7 +21929,7 @@
         <v>0.112</v>
       </c>
       <c r="G130">
-        <v>0.29477999999999999</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H130">
         <v>2760</v>
@@ -21982,7 +21982,7 @@
         <v>0.112</v>
       </c>
       <c r="G131">
-        <v>0.29477999999999999</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H131">
         <v>2760</v>
@@ -22035,7 +22035,7 @@
         <v>0.3</v>
       </c>
       <c r="G132">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H132">
         <v>2760</v>
@@ -22088,7 +22088,7 @@
         <v>0.64199999999998891</v>
       </c>
       <c r="G133">
-        <v>0.31211999999999995</v>
+        <v>0.32313599999999998</v>
       </c>
       <c r="H133">
         <v>2400</v>
@@ -22141,7 +22141,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="G134">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H134">
         <v>2760</v>
@@ -22194,7 +22194,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="G135">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H135">
         <v>2760</v>
@@ -22247,7 +22247,7 @@
         <v>0.25900000000000001</v>
       </c>
       <c r="G136">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H136">
         <v>2760</v>
@@ -22300,7 +22300,7 @@
         <v>0.112</v>
       </c>
       <c r="G137">
-        <v>0.29477999999999999</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H137">
         <v>2760</v>
@@ -22353,7 +22353,7 @@
         <v>0.7</v>
       </c>
       <c r="G138">
-        <v>0.33813000000000004</v>
+        <v>0.35006400000000004</v>
       </c>
       <c r="H138">
         <v>2640</v>
@@ -22406,7 +22406,7 @@
         <v>0.7</v>
       </c>
       <c r="G139">
-        <v>0.33813000000000004</v>
+        <v>0.35006400000000004</v>
       </c>
       <c r="H139">
         <v>2640</v>
@@ -22459,7 +22459,7 @@
         <v>0.5</v>
       </c>
       <c r="G140">
-        <v>0.32079000000000002</v>
+        <v>0.33211200000000002</v>
       </c>
       <c r="H140">
         <v>2640</v>
@@ -22512,7 +22512,7 @@
         <v>0.5</v>
       </c>
       <c r="G141">
-        <v>0.32079000000000002</v>
+        <v>0.33211200000000002</v>
       </c>
       <c r="H141">
         <v>2640</v>
@@ -22565,7 +22565,7 @@
         <v>0.7</v>
       </c>
       <c r="G142">
-        <v>0.32079000000000002</v>
+        <v>0.33211200000000002</v>
       </c>
       <c r="H142">
         <v>2640</v>
@@ -22618,7 +22618,7 @@
         <v>1</v>
       </c>
       <c r="G143">
-        <v>0.32079000000000002</v>
+        <v>0.33211200000000002</v>
       </c>
       <c r="H143">
         <v>2640</v>
@@ -22671,7 +22671,7 @@
         <v>0.6</v>
       </c>
       <c r="G144">
-        <v>0.32079000000000002</v>
+        <v>0.33211200000000002</v>
       </c>
       <c r="H144">
         <v>2640</v>
@@ -22724,7 +22724,7 @@
         <v>0.6</v>
       </c>
       <c r="G145">
-        <v>0.32079000000000002</v>
+        <v>0.33211200000000002</v>
       </c>
       <c r="H145">
         <v>2640</v>
@@ -22777,7 +22777,7 @@
         <v>0.6</v>
       </c>
       <c r="G146">
-        <v>0.33813000000000004</v>
+        <v>0.35006400000000004</v>
       </c>
       <c r="H146">
         <v>2640</v>
@@ -22830,7 +22830,7 @@
         <v>0.7</v>
       </c>
       <c r="G147">
-        <v>0.33813000000000004</v>
+        <v>0.35006400000000004</v>
       </c>
       <c r="H147">
         <v>2640</v>
@@ -22883,7 +22883,7 @@
         <v>0.5</v>
       </c>
       <c r="G148">
-        <v>0.32079000000000002</v>
+        <v>0.33211200000000002</v>
       </c>
       <c r="H148">
         <v>2640</v>
@@ -22936,7 +22936,7 @@
         <v>0.5</v>
       </c>
       <c r="G149">
-        <v>0.32079000000000002</v>
+        <v>0.33211200000000002</v>
       </c>
       <c r="H149">
         <v>2640</v>
@@ -22989,7 +22989,7 @@
         <v>1</v>
       </c>
       <c r="G150">
-        <v>0.33813000000000004</v>
+        <v>0.35006400000000004</v>
       </c>
       <c r="H150">
         <v>2640</v>
@@ -23042,7 +23042,7 @@
         <v>1</v>
       </c>
       <c r="G151">
-        <v>0.33813000000000004</v>
+        <v>0.35006400000000004</v>
       </c>
       <c r="H151">
         <v>2640</v>
@@ -23095,7 +23095,7 @@
         <v>0.7</v>
       </c>
       <c r="G152">
-        <v>0.34246500000000002</v>
+        <v>0.35455200000000003</v>
       </c>
       <c r="H152">
         <v>2640</v>
@@ -23148,7 +23148,7 @@
         <v>0.7</v>
       </c>
       <c r="G153">
-        <v>0.34246500000000002</v>
+        <v>0.35455200000000003</v>
       </c>
       <c r="H153">
         <v>2640</v>
@@ -23201,7 +23201,7 @@
         <v>0.52200000000000002</v>
       </c>
       <c r="G154">
-        <v>0.34246500000000002</v>
+        <v>0.35455200000000003</v>
       </c>
       <c r="H154">
         <v>2640</v>
@@ -23254,7 +23254,7 @@
         <v>0.7</v>
       </c>
       <c r="G155">
-        <v>0.32079000000000002</v>
+        <v>0.33211200000000002</v>
       </c>
       <c r="H155">
         <v>2640</v>
@@ -23307,7 +23307,7 @@
         <v>0.6</v>
       </c>
       <c r="G156">
-        <v>0.32079000000000002</v>
+        <v>0.33211200000000002</v>
       </c>
       <c r="H156">
         <v>2640</v>
@@ -23360,7 +23360,7 @@
         <v>0.5</v>
       </c>
       <c r="G157">
-        <v>0.33813000000000004</v>
+        <v>0.35006400000000004</v>
       </c>
       <c r="H157">
         <v>2640</v>
@@ -23413,7 +23413,7 @@
         <v>0.36</v>
       </c>
       <c r="G158">
-        <v>0.34246500000000002</v>
+        <v>0.35455200000000003</v>
       </c>
       <c r="H158">
         <v>2640</v>
@@ -23466,7 +23466,7 @@
         <v>1</v>
       </c>
       <c r="G159">
-        <v>0.35546999999999995</v>
+        <v>0.36801599999999995</v>
       </c>
       <c r="H159">
         <v>2880</v>
@@ -23519,7 +23519,7 @@
         <v>1</v>
       </c>
       <c r="G160">
-        <v>0.35546999999999995</v>
+        <v>0.36801599999999995</v>
       </c>
       <c r="H160">
         <v>2880</v>
@@ -23572,7 +23572,7 @@
         <v>0.7</v>
       </c>
       <c r="G161">
-        <v>0.35546999999999995</v>
+        <v>0.3680159999999999</v>
       </c>
       <c r="H161">
         <v>2880</v>
@@ -23625,7 +23625,7 @@
         <v>1</v>
       </c>
       <c r="G162">
-        <v>0.36414000000000002</v>
+        <v>0.37699199999999999</v>
       </c>
       <c r="H162">
         <v>2880</v>
@@ -23678,7 +23678,7 @@
         <v>1</v>
       </c>
       <c r="G163">
-        <v>0.36414000000000002</v>
+        <v>0.37699199999999999</v>
       </c>
       <c r="H163">
         <v>2880</v>
@@ -23731,7 +23731,7 @@
         <v>0.6</v>
       </c>
       <c r="G164">
-        <v>0.36414000000000002</v>
+        <v>0.37699199999999999</v>
       </c>
       <c r="H164">
         <v>2880</v>
@@ -23784,7 +23784,7 @@
         <v>0.6</v>
       </c>
       <c r="G165">
-        <v>0.37714499999999995</v>
+        <v>0.39045599999999997</v>
       </c>
       <c r="H165">
         <v>2880</v>
@@ -23837,7 +23837,7 @@
         <v>0.65</v>
       </c>
       <c r="G166">
-        <v>0.38581500000000002</v>
+        <v>0.39943200000000001</v>
       </c>
       <c r="H166">
         <v>2880</v>
@@ -23890,7 +23890,7 @@
         <v>1</v>
       </c>
       <c r="G167">
-        <v>0.36414000000000002</v>
+        <v>0.37699199999999999</v>
       </c>
       <c r="H167">
         <v>2880</v>
@@ -23943,7 +23943,7 @@
         <v>1</v>
       </c>
       <c r="G168">
-        <v>0.37714499999999995</v>
+        <v>0.39045599999999997</v>
       </c>
       <c r="H168">
         <v>2880</v>
@@ -23996,7 +23996,7 @@
         <v>0.6</v>
       </c>
       <c r="G169">
-        <v>0.36414000000000002</v>
+        <v>0.37699199999999999</v>
       </c>
       <c r="H169">
         <v>2880</v>
@@ -24049,7 +24049,7 @@
         <v>0.6</v>
       </c>
       <c r="G170">
-        <v>0.36414000000000002</v>
+        <v>0.37699199999999999</v>
       </c>
       <c r="H170">
         <v>2880</v>
@@ -24102,7 +24102,7 @@
         <v>1.05</v>
       </c>
       <c r="G171">
-        <v>0.35546999999999995</v>
+        <v>0.36801599999999995</v>
       </c>
       <c r="H171">
         <v>2880</v>
@@ -24155,7 +24155,7 @@
         <v>1.05</v>
       </c>
       <c r="G172">
-        <v>0.35546999999999995</v>
+        <v>0.36801599999999995</v>
       </c>
       <c r="H172">
         <v>2880</v>
@@ -24208,7 +24208,7 @@
         <v>0.65</v>
       </c>
       <c r="G173">
-        <v>0.38581500000000002</v>
+        <v>0.39943200000000001</v>
       </c>
       <c r="H173">
         <v>2880</v>
@@ -24261,7 +24261,7 @@
         <v>0.65</v>
       </c>
       <c r="G174">
-        <v>0.38581500000000002</v>
+        <v>0.39943200000000001</v>
       </c>
       <c r="H174">
         <v>2880</v>
@@ -24314,7 +24314,7 @@
         <v>0.9</v>
       </c>
       <c r="G175">
-        <v>0.36414000000000002</v>
+        <v>0.37699199999999999</v>
       </c>
       <c r="H175">
         <v>2880</v>
@@ -24367,7 +24367,7 @@
         <v>0.9</v>
       </c>
       <c r="G176">
-        <v>0.36414000000000002</v>
+        <v>0.37699199999999999</v>
       </c>
       <c r="H176">
         <v>2880</v>
@@ -24420,7 +24420,7 @@
         <v>1</v>
       </c>
       <c r="G177">
-        <v>0.37714499999999995</v>
+        <v>0.39045599999999997</v>
       </c>
       <c r="H177">
         <v>2880</v>
@@ -24473,7 +24473,7 @@
         <v>1</v>
       </c>
       <c r="G178">
-        <v>0.35546999999999995</v>
+        <v>0.36801599999999995</v>
       </c>
       <c r="H178">
         <v>2880</v>
@@ -24526,7 +24526,7 @@
         <v>1</v>
       </c>
       <c r="G179">
-        <v>0.35546999999999995</v>
+        <v>0.36801599999999995</v>
       </c>
       <c r="H179">
         <v>2880</v>
@@ -24579,7 +24579,7 @@
         <v>1</v>
       </c>
       <c r="G180">
-        <v>0.38581500000000002</v>
+        <v>0.39943200000000001</v>
       </c>
       <c r="H180">
         <v>2880</v>
@@ -24632,7 +24632,7 @@
         <v>0.5</v>
       </c>
       <c r="G181">
-        <v>0.35546999999999995</v>
+        <v>0.36801599999999995</v>
       </c>
       <c r="H181">
         <v>2880</v>
@@ -24685,7 +24685,7 @@
         <v>0.7</v>
       </c>
       <c r="G182">
-        <v>0.35546999999999995</v>
+        <v>0.3680159999999999</v>
       </c>
       <c r="H182">
         <v>2880</v>
@@ -24738,7 +24738,7 @@
         <v>0.6</v>
       </c>
       <c r="G183">
-        <v>0.35546999999999995</v>
+        <v>0.36801599999999995</v>
       </c>
       <c r="H183">
         <v>2880</v>
@@ -24791,7 +24791,7 @@
         <v>0.6</v>
       </c>
       <c r="G184">
-        <v>0.37714499999999995</v>
+        <v>0.39045599999999997</v>
       </c>
       <c r="H184">
         <v>2880</v>
@@ -24844,7 +24844,7 @@
         <v>0.7</v>
       </c>
       <c r="G185">
-        <v>0.36414000000000002</v>
+        <v>0.37699200000000005</v>
       </c>
       <c r="H185">
         <v>2880</v>
@@ -24897,7 +24897,7 @@
         <v>0.5</v>
       </c>
       <c r="G186">
-        <v>0.38581500000000002</v>
+        <v>0.39943200000000001</v>
       </c>
       <c r="H186">
         <v>2880</v>
@@ -24950,7 +24950,7 @@
         <v>0.7</v>
       </c>
       <c r="G187">
-        <v>0.35546999999999995</v>
+        <v>0.3680159999999999</v>
       </c>
       <c r="H187">
         <v>2880</v>
@@ -25003,7 +25003,7 @@
         <v>0.64500000000000002</v>
       </c>
       <c r="G188">
-        <v>0.37714499999999995</v>
+        <v>0.39045599999999997</v>
       </c>
       <c r="H188">
         <v>2880</v>
@@ -25056,7 +25056,7 @@
         <v>0.6</v>
       </c>
       <c r="G189">
-        <v>0.37714499999999995</v>
+        <v>0.39045599999999997</v>
       </c>
       <c r="H189">
         <v>2880</v>
@@ -25109,7 +25109,7 @@
         <v>1.07</v>
       </c>
       <c r="G190">
-        <v>0.38581500000000002</v>
+        <v>0.39943200000000001</v>
       </c>
       <c r="H190">
         <v>2880</v>
@@ -25162,7 +25162,7 @@
         <v>0.7</v>
       </c>
       <c r="G191">
-        <v>0.36414000000000002</v>
+        <v>0.37699200000000005</v>
       </c>
       <c r="H191">
         <v>2880</v>
@@ -25215,7 +25215,7 @@
         <v>0.7</v>
       </c>
       <c r="G192">
-        <v>0.35546999999999995</v>
+        <v>0.3680159999999999</v>
       </c>
       <c r="H192">
         <v>2880</v>
@@ -25268,7 +25268,7 @@
         <v>0.65</v>
       </c>
       <c r="G193">
-        <v>0.38581500000000002</v>
+        <v>0.39943200000000001</v>
       </c>
       <c r="H193">
         <v>2880</v>
@@ -25321,7 +25321,7 @@
         <v>0.65</v>
       </c>
       <c r="G194">
-        <v>0.38581500000000002</v>
+        <v>0.39943200000000001</v>
       </c>
       <c r="H194">
         <v>2880</v>
@@ -25374,7 +25374,7 @@
         <v>0.14799999999999999</v>
       </c>
       <c r="G195">
-        <v>0.31211999999999995</v>
+        <v>0.32313599999999998</v>
       </c>
       <c r="H195">
         <v>1380</v>
@@ -25427,7 +25427,7 @@
         <v>0.38580000000000003</v>
       </c>
       <c r="G196">
-        <v>0.37280999999999997</v>
+        <v>0.38596799999999992</v>
       </c>
       <c r="H196">
         <v>1380</v>
@@ -25480,7 +25480,7 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="G197">
-        <v>0.37280999999999997</v>
+        <v>0.38596799999999998</v>
       </c>
       <c r="H197">
         <v>1380</v>
@@ -25533,7 +25533,7 @@
         <v>1</v>
       </c>
       <c r="G198">
-        <v>0.37280999999999992</v>
+        <v>0.38596799999999998</v>
       </c>
       <c r="H198">
         <v>1380</v>
@@ -25586,7 +25586,7 @@
         <v>0.16200000000000001</v>
       </c>
       <c r="G199">
-        <v>0.37280999999999997</v>
+        <v>0.38596799999999998</v>
       </c>
       <c r="H199">
         <v>1380</v>
@@ -25639,7 +25639,7 @@
         <v>1.5489999999999999</v>
       </c>
       <c r="G200">
-        <v>0.37280999999999997</v>
+        <v>0.38596799999999992</v>
       </c>
       <c r="H200">
         <v>1380</v>
@@ -25692,7 +25692,7 @@
         <v>0.6</v>
       </c>
       <c r="G201">
-        <v>0.43349999999999994</v>
+        <v>0.44880000000000003</v>
       </c>
       <c r="H201">
         <v>1380</v>
@@ -25745,7 +25745,7 @@
         <v>0.78600000000000003</v>
       </c>
       <c r="G202">
-        <v>0.4335</v>
+        <v>0.44880000000000009</v>
       </c>
       <c r="H202">
         <v>1380</v>
@@ -25798,7 +25798,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="G203">
-        <v>0.43349999999999994</v>
+        <v>0.44880000000000003</v>
       </c>
       <c r="H203">
         <v>1380</v>
@@ -25851,7 +25851,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="G204">
-        <v>0.43349999999999994</v>
+        <v>0.44880000000000003</v>
       </c>
       <c r="H204">
         <v>1380</v>
@@ -25904,7 +25904,7 @@
         <v>3.2469999999999999</v>
       </c>
       <c r="G205">
-        <v>0.43853324607329847</v>
+        <v>0.45401089005235606</v>
       </c>
       <c r="H205">
         <v>1338.2014166923313</v>
@@ -25957,7 +25957,7 @@
         <v>3.2090000000000001</v>
       </c>
       <c r="G206">
-        <v>0.44368569647865386</v>
+        <v>0.45934519164848869</v>
       </c>
       <c r="H206">
         <v>1295.4129012153319</v>
@@ -26010,7 +26010,7 @@
         <v>3.3069999999999999</v>
       </c>
       <c r="G207">
-        <v>0.4408014665860297</v>
+        <v>0.45635916540671317</v>
       </c>
       <c r="H207">
         <v>1319.364983368612</v>
@@ -26063,7 +26063,7 @@
         <v>1.589</v>
       </c>
       <c r="G208">
-        <v>0.45314254247954694</v>
+        <v>0.46913580868470744</v>
       </c>
       <c r="H208">
         <v>1216.8785399622404</v>
@@ -26116,7 +26116,7 @@
         <v>1.08</v>
       </c>
       <c r="G209">
-        <v>0.45517500000000005</v>
+        <v>0.4712400000000001</v>
       </c>
       <c r="H209">
         <v>1200</v>
@@ -26169,7 +26169,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="G210">
-        <v>0.47251500000000002</v>
+        <v>0.48919200000000002</v>
       </c>
       <c r="H210">
         <v>1200</v>
@@ -26222,7 +26222,7 @@
         <v>0.91849999999999998</v>
       </c>
       <c r="G211">
-        <v>0.46919944474686992</v>
+        <v>0.48575942514970072</v>
       </c>
       <c r="H211">
         <v>1227.5340228633643</v>
@@ -26275,7 +26275,7 @@
         <v>1.8614000000000002</v>
       </c>
       <c r="G212">
-        <v>0.46809709143655309</v>
+        <v>0.48461816525196094</v>
       </c>
       <c r="H212">
         <v>1236.6885140217041</v>
@@ -26328,7 +26328,7 @@
         <v>0.46</v>
       </c>
       <c r="G213">
-        <v>0.44895521739130434</v>
+        <v>0.46480069565217386</v>
       </c>
       <c r="H213">
         <v>1406.0869565217392</v>
@@ -26381,7 +26381,7 @@
         <v>0.1047</v>
       </c>
       <c r="G214">
-        <v>0.45083999999999996</v>
+        <v>0.466752</v>
       </c>
       <c r="H214">
         <v>1380</v>
@@ -26434,7 +26434,7 @@
         <v>0.24</v>
       </c>
       <c r="G215">
-        <v>0.45083999999999996</v>
+        <v>0.466752</v>
       </c>
       <c r="H215">
         <v>1380</v>
@@ -26487,7 +26487,7 @@
         <v>2.5474000000000001</v>
       </c>
       <c r="G216">
-        <v>0.47166413244877131</v>
+        <v>0.48831110182931614</v>
       </c>
       <c r="H216">
         <v>1207.0660281070896</v>
@@ -26540,7 +26540,7 @@
         <v>2.5939999999999999</v>
       </c>
       <c r="G217">
-        <v>0.46086698535080944</v>
+        <v>0.47713287895142642</v>
       </c>
       <c r="H217">
         <v>1296.7309175019275</v>
@@ -26593,7 +26593,7 @@
         <v>2.4981999999999998</v>
       </c>
       <c r="G218">
-        <v>0.46890568129052912</v>
+        <v>0.48545529357137146</v>
       </c>
       <c r="H218">
         <v>1229.9735809783044</v>
@@ -26646,7 +26646,7 @@
         <v>0.26189999999999997</v>
       </c>
       <c r="G219">
-        <v>0.48552000000000006</v>
+        <v>0.50265599999999999</v>
       </c>
       <c r="H219">
         <v>1380.0000000000002</v>
@@ -26699,7 +26699,7 @@
         <v>0.36330000000000001</v>
       </c>
       <c r="G220">
-        <v>0.48552000000000001</v>
+        <v>0.50265599999999999</v>
       </c>
       <c r="H220">
         <v>1380</v>
@@ -26752,7 +26752,7 @@
         <v>1.224</v>
       </c>
       <c r="G221">
-        <v>0.49930416666666672</v>
+        <v>0.51692666666666665</v>
       </c>
       <c r="H221">
         <v>1236.9117647058824</v>
@@ -26805,7 +26805,7 @@
         <v>3.149</v>
       </c>
       <c r="G222">
-        <v>0.50049495395363597</v>
+        <v>0.51815948174023496</v>
       </c>
       <c r="H222">
         <v>1224.5506510003177</v>
@@ -26858,7 +26858,7 @@
         <v>1.0771999999999999</v>
       </c>
       <c r="G223">
-        <v>0.49335133122911246</v>
+        <v>0.51076373115484597</v>
       </c>
       <c r="H223">
         <v>1298.7059041960638</v>
@@ -26911,7 +26911,7 @@
         <v>0.69610000000000005</v>
       </c>
       <c r="G224">
-        <v>0.49566094813963507</v>
+        <v>0.51315486395632814</v>
       </c>
       <c r="H224">
         <v>1274.7306421491164</v>
@@ -26964,7 +26964,7 @@
         <v>0.42469999999999997</v>
       </c>
       <c r="G225">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H225">
         <v>1200</v>
@@ -27017,7 +27017,7 @@
         <v>0.33700000000000002</v>
       </c>
       <c r="G226">
-        <v>0.48552000000000001</v>
+        <v>0.50265599999999999</v>
       </c>
       <c r="H226">
         <v>1380</v>
@@ -27070,7 +27070,7 @@
         <v>0.2</v>
       </c>
       <c r="G227">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H227">
         <v>1380</v>
@@ -27123,7 +27123,7 @@
         <v>0.28560000000003072</v>
       </c>
       <c r="G228">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H228">
         <v>1380</v>
@@ -27176,7 +27176,7 @@
         <v>0.56599999999999995</v>
       </c>
       <c r="G229">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H229">
         <v>1200</v>
@@ -27229,7 +27229,7 @@
         <v>0.65</v>
       </c>
       <c r="G230">
-        <v>0.5202</v>
+        <v>0.53856000000000004</v>
       </c>
       <c r="H230">
         <v>1200</v>
@@ -27282,7 +27282,7 @@
         <v>0.65</v>
       </c>
       <c r="G231">
-        <v>0.5202</v>
+        <v>0.53856000000000004</v>
       </c>
       <c r="H231">
         <v>1200</v>
@@ -27335,7 +27335,7 @@
         <v>0.65</v>
       </c>
       <c r="G232">
-        <v>0.5202</v>
+        <v>0.53856000000000004</v>
       </c>
       <c r="H232">
         <v>1200</v>
@@ -27388,7 +27388,7 @@
         <v>0.5</v>
       </c>
       <c r="G233">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H233">
         <v>1200</v>
@@ -27441,7 +27441,7 @@
         <v>0.5</v>
       </c>
       <c r="G234">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H234">
         <v>1200</v>
@@ -27494,7 +27494,7 @@
         <v>0.5</v>
       </c>
       <c r="G235">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H235">
         <v>1200</v>
@@ -27547,7 +27547,7 @@
         <v>0.85399999999999998</v>
       </c>
       <c r="G236">
-        <v>0.45517500000000005</v>
+        <v>0.4712400000000001</v>
       </c>
       <c r="H236">
         <v>1200</v>
@@ -27600,7 +27600,7 @@
         <v>0.85399999999999998</v>
       </c>
       <c r="G237">
-        <v>0.45517500000000005</v>
+        <v>0.4712400000000001</v>
       </c>
       <c r="H237">
         <v>1200</v>
@@ -27653,7 +27653,7 @@
         <v>0.85399999999999998</v>
       </c>
       <c r="G238">
-        <v>0.45517500000000005</v>
+        <v>0.4712400000000001</v>
       </c>
       <c r="H238">
         <v>1200</v>
@@ -27706,7 +27706,7 @@
         <v>0.85399999999999998</v>
       </c>
       <c r="G239">
-        <v>0.45517500000000005</v>
+        <v>0.4712400000000001</v>
       </c>
       <c r="H239">
         <v>1200</v>
@@ -27759,7 +27759,7 @@
         <v>0.59</v>
       </c>
       <c r="G240">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H240">
         <v>1200</v>
@@ -27812,7 +27812,7 @@
         <v>0.59</v>
       </c>
       <c r="G241">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H241">
         <v>1200</v>
@@ -27865,7 +27865,7 @@
         <v>0.50700000000000001</v>
       </c>
       <c r="G242">
-        <v>0.47251500000000002</v>
+        <v>0.48919200000000007</v>
       </c>
       <c r="H242">
         <v>1200</v>
@@ -27918,7 +27918,7 @@
         <v>0.50700000000000001</v>
       </c>
       <c r="G243">
-        <v>0.47251500000000002</v>
+        <v>0.48919200000000007</v>
       </c>
       <c r="H243">
         <v>1200</v>
@@ -27971,7 +27971,7 @@
         <v>0.50700000000000001</v>
       </c>
       <c r="G244">
-        <v>0.47251500000000002</v>
+        <v>0.48919200000000007</v>
       </c>
       <c r="H244">
         <v>1200</v>
@@ -28024,7 +28024,7 @@
         <v>0.78</v>
       </c>
       <c r="G245">
-        <v>0.5202</v>
+        <v>0.53856000000000004</v>
       </c>
       <c r="H245">
         <v>1200</v>
@@ -28077,7 +28077,7 @@
         <v>0.78</v>
       </c>
       <c r="G246">
-        <v>0.5202</v>
+        <v>0.53856000000000004</v>
       </c>
       <c r="H246">
         <v>1200</v>
@@ -28130,7 +28130,7 @@
         <v>0.78</v>
       </c>
       <c r="G247">
-        <v>0.5202</v>
+        <v>0.53856000000000004</v>
       </c>
       <c r="H247">
         <v>1200</v>
@@ -28183,7 +28183,7 @@
         <v>0.60499999999999998</v>
       </c>
       <c r="G248">
-        <v>0.39015</v>
+        <v>0.40392</v>
       </c>
       <c r="H248">
         <v>1200</v>
@@ -28236,7 +28236,7 @@
         <v>0.60499999999999998</v>
       </c>
       <c r="G249">
-        <v>0.39015</v>
+        <v>0.40392</v>
       </c>
       <c r="H249">
         <v>1200</v>
@@ -28289,7 +28289,7 @@
         <v>0.85</v>
       </c>
       <c r="G250">
-        <v>0.45517500000000005</v>
+        <v>0.4712400000000001</v>
       </c>
       <c r="H250">
         <v>1200</v>
@@ -28342,7 +28342,7 @@
         <v>0.85</v>
       </c>
       <c r="G251">
-        <v>0.47251500000000007</v>
+        <v>0.48919200000000007</v>
       </c>
       <c r="H251">
         <v>1200</v>
@@ -28395,7 +28395,7 @@
         <v>0.72899999999999998</v>
       </c>
       <c r="G252">
-        <v>0.45517500000000005</v>
+        <v>0.4712400000000001</v>
       </c>
       <c r="H252">
         <v>1200</v>
@@ -28448,7 +28448,7 @@
         <v>0.71299999999999997</v>
       </c>
       <c r="G253">
-        <v>0.45517500000000005</v>
+        <v>0.4712400000000001</v>
       </c>
       <c r="H253">
         <v>1200</v>
@@ -28501,7 +28501,7 @@
         <v>0.62260000000000004</v>
       </c>
       <c r="G254">
-        <v>0.5202</v>
+        <v>0.53856000000000004</v>
       </c>
       <c r="H254">
         <v>1200</v>
@@ -28554,7 +28554,7 @@
         <v>0.62260000000000004</v>
       </c>
       <c r="G255">
-        <v>0.5202</v>
+        <v>0.53856000000000004</v>
       </c>
       <c r="H255">
         <v>1200</v>
@@ -28607,7 +28607,7 @@
         <v>0.56940000000000002</v>
       </c>
       <c r="G256">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H256">
         <v>1200</v>
@@ -28660,7 +28660,7 @@
         <v>0.57199999999999995</v>
       </c>
       <c r="G257">
-        <v>0.5202</v>
+        <v>0.53856000000000004</v>
       </c>
       <c r="H257">
         <v>1200</v>
@@ -28713,7 +28713,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="G258">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H258">
         <v>1200</v>
@@ -28766,7 +28766,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="G259">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H259">
         <v>1200</v>
@@ -28819,7 +28819,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="G260">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H260">
         <v>1200</v>
@@ -28872,7 +28872,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="G261">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H261">
         <v>1200</v>
@@ -28925,7 +28925,7 @@
         <v>0.5</v>
       </c>
       <c r="G262">
-        <v>0.47251500000000002</v>
+        <v>0.48919200000000007</v>
       </c>
       <c r="H262">
         <v>1200</v>
@@ -28978,7 +28978,7 @@
         <v>0.5</v>
       </c>
       <c r="G263">
-        <v>0.47251500000000002</v>
+        <v>0.48919200000000007</v>
       </c>
       <c r="H263">
         <v>1200</v>
@@ -29031,7 +29031,7 @@
         <v>0.5</v>
       </c>
       <c r="G264">
-        <v>0.47251500000000002</v>
+        <v>0.48919200000000007</v>
       </c>
       <c r="H264">
         <v>1200</v>
@@ -29084,7 +29084,7 @@
         <v>0.5</v>
       </c>
       <c r="G265">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H265">
         <v>1200</v>
@@ -29137,7 +29137,7 @@
         <v>0.71</v>
       </c>
       <c r="G266">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H266">
         <v>1200</v>
@@ -29190,7 +29190,7 @@
         <v>0.71</v>
       </c>
       <c r="G267">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H267">
         <v>1200</v>
@@ -29243,7 +29243,7 @@
         <v>0.62409999999999999</v>
       </c>
       <c r="G268">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H268">
         <v>1200</v>
@@ -29296,7 +29296,7 @@
         <v>0.62409999999999999</v>
       </c>
       <c r="G269">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H269">
         <v>1200</v>
@@ -29349,7 +29349,7 @@
         <v>1.1879999999999999</v>
       </c>
       <c r="G270">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H270">
         <v>1200</v>
@@ -29402,7 +29402,7 @@
         <v>1.1879999999999999</v>
       </c>
       <c r="G271">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H271">
         <v>1200</v>
@@ -29455,7 +29455,7 @@
         <v>0.5</v>
       </c>
       <c r="G272">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H272">
         <v>1200</v>
@@ -29508,7 +29508,7 @@
         <v>0.52300000000000002</v>
       </c>
       <c r="G273">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H273">
         <v>1200</v>
@@ -29561,7 +29561,7 @@
         <v>0.52300000000000002</v>
       </c>
       <c r="G274">
-        <v>0.50285999999999997</v>
+        <v>0.52060800000000007</v>
       </c>
       <c r="H274">
         <v>1200</v>
@@ -29614,7 +29614,7 @@
         <v>0.41599999999999998</v>
       </c>
       <c r="G275">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H275">
         <v>960</v>
@@ -29667,7 +29667,7 @@
         <v>0.15</v>
       </c>
       <c r="G276">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H276">
         <v>1103.9999999999998</v>
@@ -29720,7 +29720,7 @@
         <v>0.10920000000000001</v>
       </c>
       <c r="G277">
-        <v>0.30778499999999998</v>
+        <v>0.31864799999999999</v>
       </c>
       <c r="H277">
         <v>1518</v>
@@ -29773,7 +29773,7 @@
         <v>0.10920000000000001</v>
       </c>
       <c r="G278">
-        <v>0.30778499999999998</v>
+        <v>0.31864799999999999</v>
       </c>
       <c r="H278">
         <v>1518</v>
@@ -29826,7 +29826,7 @@
         <v>0.10920000000000001</v>
       </c>
       <c r="G279">
-        <v>0.31211999999999995</v>
+        <v>0.32313600000000003</v>
       </c>
       <c r="H279">
         <v>1518</v>
@@ -29879,7 +29879,7 @@
         <v>1.7190000000000001</v>
       </c>
       <c r="G280">
-        <v>0.27422216404886568</v>
+        <v>0.28390059336823736</v>
       </c>
       <c r="H280">
         <v>1480.0837696335079</v>
@@ -29932,7 +29932,7 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="G281">
-        <v>0.26876999999999995</v>
+        <v>0.278256</v>
       </c>
       <c r="H281">
         <v>1656</v>
@@ -29985,7 +29985,7 @@
         <v>0.66800000000000004</v>
       </c>
       <c r="G282">
-        <v>0.26876999999999995</v>
+        <v>0.278256</v>
       </c>
       <c r="H282">
         <v>1656</v>
@@ -30038,7 +30038,7 @@
         <v>0.70499999999999996</v>
       </c>
       <c r="G283">
-        <v>0.27983808510638297</v>
+        <v>0.28971472340425536</v>
       </c>
       <c r="H283">
         <v>1518.127659574468</v>
@@ -30091,7 +30091,7 @@
         <v>0.375</v>
       </c>
       <c r="G284">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H284">
         <v>1440</v>
@@ -30144,7 +30144,7 @@
         <v>0.13800000000000001</v>
       </c>
       <c r="G285">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H285">
         <v>1656</v>
@@ -30197,7 +30197,7 @@
         <v>0.14899999999999999</v>
       </c>
       <c r="G286">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H286">
         <v>1656</v>
@@ -30250,7 +30250,7 @@
         <v>0.1</v>
       </c>
       <c r="G287">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H287">
         <v>1656</v>
@@ -30303,7 +30303,7 @@
         <v>0.34</v>
       </c>
       <c r="G288">
-        <v>0.31211999999999995</v>
+        <v>0.32313599999999998</v>
       </c>
       <c r="H288">
         <v>1440</v>
@@ -30356,7 +30356,7 @@
         <v>0.46</v>
       </c>
       <c r="G289">
-        <v>0.30797347826086957</v>
+        <v>0.31884313043478257</v>
       </c>
       <c r="H289">
         <v>1491.6521739130435</v>
@@ -30409,7 +30409,7 @@
         <v>0.35</v>
       </c>
       <c r="G290">
-        <v>0.31645499999999999</v>
+        <v>0.32762400000000003</v>
       </c>
       <c r="H290">
         <v>1440</v>
@@ -30462,7 +30462,7 @@
         <v>0.85599999999999998</v>
       </c>
       <c r="G291">
-        <v>0.31329490654205605</v>
+        <v>0.32435237383177573</v>
       </c>
       <c r="H291">
         <v>1479.3644859813085</v>
@@ -30515,7 +30515,7 @@
         <v>0.156</v>
       </c>
       <c r="G292">
-        <v>0.29911499999999996</v>
+        <v>0.309672</v>
       </c>
       <c r="H292">
         <v>1656</v>
@@ -30568,7 +30568,7 @@
         <v>0.6</v>
       </c>
       <c r="G293">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H293">
         <v>1440</v>
@@ -30621,7 +30621,7 @@
         <v>0.6</v>
       </c>
       <c r="G294">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H294">
         <v>1440</v>
@@ -30674,7 +30674,7 @@
         <v>0.6</v>
       </c>
       <c r="G295">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H295">
         <v>1440</v>
@@ -30727,7 +30727,7 @@
         <v>0.6</v>
       </c>
       <c r="G296">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H296">
         <v>1440</v>
@@ -30780,7 +30780,7 @@
         <v>1</v>
       </c>
       <c r="G297">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H297">
         <v>1440</v>
@@ -30833,7 +30833,7 @@
         <v>1</v>
       </c>
       <c r="G298">
-        <v>0.30345</v>
+        <v>0.31415999999999999</v>
       </c>
       <c r="H298">
         <v>1440</v>
@@ -30886,7 +30886,7 @@
         <v>0.7</v>
       </c>
       <c r="G299">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H299">
         <v>1440</v>
@@ -30939,7 +30939,7 @@
         <v>0.7</v>
       </c>
       <c r="G300">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H300">
         <v>1440</v>
@@ -30992,7 +30992,7 @@
         <v>0.6</v>
       </c>
       <c r="G301">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H301">
         <v>1440</v>
@@ -31045,7 +31045,7 @@
         <v>0.6</v>
       </c>
       <c r="G302">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H302">
         <v>1440</v>
@@ -31098,7 +31098,7 @@
         <v>0.6</v>
       </c>
       <c r="G303">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H303">
         <v>1440</v>
@@ -31151,7 +31151,7 @@
         <v>0.6</v>
       </c>
       <c r="G304">
-        <v>0.30345</v>
+        <v>0.31415999999999999</v>
       </c>
       <c r="H304">
         <v>1440</v>
@@ -31204,7 +31204,7 @@
         <v>0.6</v>
       </c>
       <c r="G305">
-        <v>0.30345</v>
+        <v>0.31415999999999999</v>
       </c>
       <c r="H305">
         <v>1440</v>
@@ -31257,7 +31257,7 @@
         <v>0.6</v>
       </c>
       <c r="G306">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H306">
         <v>1440</v>
@@ -31310,7 +31310,7 @@
         <v>1</v>
       </c>
       <c r="G307">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H307">
         <v>1440</v>
@@ -31363,7 +31363,7 @@
         <v>1</v>
       </c>
       <c r="G308">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H308">
         <v>1440</v>
@@ -31416,7 +31416,7 @@
         <v>1</v>
       </c>
       <c r="G309">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H309">
         <v>1440</v>
@@ -39096,7 +39096,7 @@
         <v>0.14799999999999999</v>
       </c>
       <c r="G507">
-        <v>0.19074000000000002</v>
+        <v>0.19747200000000001</v>
       </c>
       <c r="H507">
         <v>1242</v>
@@ -39128,7 +39128,7 @@
         <v>0.106</v>
       </c>
       <c r="G508">
-        <v>0.24276</v>
+        <v>0.251328</v>
       </c>
       <c r="H508">
         <v>1242</v>
@@ -39160,7 +39160,7 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="G509">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H509">
         <v>1242</v>
@@ -39192,7 +39192,7 @@
         <v>0.45</v>
       </c>
       <c r="G510">
-        <v>0.26876999999999995</v>
+        <v>0.278256</v>
       </c>
       <c r="H510">
         <v>1560</v>
@@ -39224,7 +39224,7 @@
         <v>0.25</v>
       </c>
       <c r="G511">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H511">
         <v>1793.9999999999998</v>
@@ -39256,7 +39256,7 @@
         <v>0.35</v>
       </c>
       <c r="G512">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H512">
         <v>1560</v>
@@ -39288,7 +39288,7 @@
         <v>0.25</v>
       </c>
       <c r="G513">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H513">
         <v>1793.9999999999998</v>
@@ -39320,7 +39320,7 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="G514">
-        <v>0.2601</v>
+        <v>0.26928000000000002</v>
       </c>
       <c r="H514">
         <v>1793.9999999999998</v>
@@ -39352,7 +39352,7 @@
         <v>0.45</v>
       </c>
       <c r="G515">
-        <v>0.27744000000000002</v>
+        <v>0.2872320000000001</v>
       </c>
       <c r="H515">
         <v>1560</v>
@@ -39384,7 +39384,7 @@
         <v>0.72499999999999998</v>
       </c>
       <c r="G516">
-        <v>0.26847103448275861</v>
+        <v>0.27794648275862072</v>
       </c>
       <c r="H516">
         <v>1681.0344827586207</v>
@@ -39416,7 +39416,7 @@
         <v>0.35</v>
       </c>
       <c r="G517">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H517">
         <v>1560</v>
@@ -39448,7 +39448,7 @@
         <v>0.125</v>
       </c>
       <c r="G518">
-        <v>0.26877000000000001</v>
+        <v>0.278256</v>
       </c>
       <c r="H518">
         <v>1793.9999999999998</v>
@@ -39480,7 +39480,7 @@
         <v>0.35</v>
       </c>
       <c r="G519">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H519">
         <v>1560</v>
@@ -39512,7 +39512,7 @@
         <v>0.35</v>
       </c>
       <c r="G520">
-        <v>0.29478000000000004</v>
+        <v>0.30518400000000007</v>
       </c>
       <c r="H520">
         <v>1560</v>
@@ -39544,7 +39544,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="G521">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000008</v>
       </c>
       <c r="H521">
         <v>1793.9999999999998</v>
@@ -39576,7 +39576,7 @@
         <v>0.5</v>
       </c>
       <c r="G522">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H522">
         <v>1560</v>
@@ -39608,7 +39608,7 @@
         <v>0.7</v>
       </c>
       <c r="G523">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H523">
         <v>1560</v>
@@ -39640,7 +39640,7 @@
         <v>0.7</v>
       </c>
       <c r="G524">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H524">
         <v>1560</v>
@@ -39672,7 +39672,7 @@
         <v>0.6</v>
       </c>
       <c r="G525">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H525">
         <v>1560</v>
@@ -39704,7 +39704,7 @@
         <v>0.6</v>
       </c>
       <c r="G526">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H526">
         <v>1560</v>
@@ -39736,7 +39736,7 @@
         <v>0.5</v>
       </c>
       <c r="G527">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H527">
         <v>1560</v>
@@ -39768,7 +39768,7 @@
         <v>0.5</v>
       </c>
       <c r="G528">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H528">
         <v>1560</v>
@@ -39800,7 +39800,7 @@
         <v>0.6</v>
       </c>
       <c r="G529">
-        <v>0.27744000000000002</v>
+        <v>0.28723200000000004</v>
       </c>
       <c r="H529">
         <v>1560</v>
@@ -39832,7 +39832,7 @@
         <v>0.6</v>
       </c>
       <c r="G530">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H530">
         <v>1560</v>
@@ -39864,7 +39864,7 @@
         <v>0.6</v>
       </c>
       <c r="G531">
-        <v>0.28610999999999998</v>
+        <v>0.29620800000000003</v>
       </c>
       <c r="H531">
         <v>1560</v>
@@ -39896,7 +39896,7 @@
         <v>0.45</v>
       </c>
       <c r="G532">
-        <v>0.27744000000000002</v>
+        <v>0.2872320000000001</v>
       </c>
       <c r="H532">
         <v>1560</v>
@@ -40803,7 +40803,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L561">
-        <v>0.39895126255821034</v>
+        <v>0.39895126255821028</v>
       </c>
     </row>
     <row r="562" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59E83A22-B569-4EB9-9698-1BDAF258DDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A77F0A2-AD65-447F-8C38-BB01DC6F6860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{506E9D17-4763-471F-B781-A7200E9E9C64}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5F6FCF46-84A5-4AD4-9FEE-1D8ED8C718FC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3479,7 +3479,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A7EB98-106B-4F22-84F6-5C2894A214CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE1E71A-F022-4E7E-A42A-C9A384825E46}">
   <dimension ref="B9:T266"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15537,7 +15537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF30874D-D643-4E7E-AF92-BED16D323B10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D71BDA59-805C-4104-AE76-049E0426C251}">
   <dimension ref="B9:T586"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39943,7 +39943,7 @@
         <v>33</v>
       </c>
       <c r="L533">
-        <v>0.19194755490778873</v>
+        <v>0.1919475549077887</v>
       </c>
     </row>
     <row r="534" spans="2:12" x14ac:dyDescent="0.45">
@@ -40803,7 +40803,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L561">
-        <v>0.39895126255821028</v>
+        <v>0.39895126255821034</v>
       </c>
     </row>
     <row r="562" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A77F0A2-AD65-447F-8C38-BB01DC6F6860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{668FC214-1BC9-4DE3-BFC6-5BC8A6296FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5F6FCF46-84A5-4AD4-9FEE-1D8ED8C718FC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7C7BF036-602F-45DC-A28D-72005B8D911A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3479,7 +3479,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE1E71A-F022-4E7E-A42A-C9A384825E46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A08CCB4-7312-4E8A-A75E-DBA4115DE3D9}">
   <dimension ref="B9:T266"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15537,7 +15537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D71BDA59-805C-4104-AE76-049E0426C251}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FFA02C7-BD04-494F-84C1-B49DC5A7E4F1}">
   <dimension ref="B9:T586"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40596,7 +40596,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L552">
-        <v>0.38298883693604863</v>
+        <v>0.38298883693604857</v>
       </c>
     </row>
     <row r="553" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F197482-4948-4AEB-9C21-7975A8BA4879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93AA1553-C849-4B11-800D-77AEF7A5DB01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6C3E4061-F810-4B57-BBFF-7B4BDA20580B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2664A485-CC1B-4A16-BC98-7687FDACBC0B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3809,7 +3809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAA97785-4CB9-4466-A686-5C9ECA285861}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF637764-9C6B-4826-8DB4-98D3875D9F3B}">
   <dimension ref="B9:T266"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15888,7 +15888,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D32A76A3-E0FE-4D62-8445-72EF0C066CB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18BBF084-60D6-4FD9-98BB-0EF4588C39E5}">
   <dimension ref="B9:T987"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -55707,7 +55707,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L987">
-        <v>0.30748532685371854</v>
+        <v>0.30748532685371849</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8528AC45-1B0D-4592-9537-B211CCB0A9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6844F528-41DC-4EC7-B772-80DD3041AB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DFA8283B-271D-47E8-910E-4BE50E1EFBAC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0642808D-3AF6-4AB7-9D50-87C617C2B603}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1592,22 +1592,22 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant -- construction</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>Aggregated Plant -- operating</t>
-  </si>
-  <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant -- construction</t>
   </si>
   <si>
     <t>Sendai-ko power station_1 -- construction</t>
@@ -4552,7 +4552,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A6F653D-F7D8-4F20-9541-F22B5690EC3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D5B0909-7BBB-4B7A-869F-C59D937ABFF9}">
   <dimension ref="B9:T168"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13474,7 +13474,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4623797B-1F6A-41D3-89A3-5133F386607C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FC4811-9BA6-4D66-BAC2-6A952C14C220}">
   <dimension ref="B9:T130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19959,7 +19959,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD956CD6-05FB-4299-A03E-96A0FD3ED2E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72501FC1-E49C-4D68-A764-3B631B26163F}">
   <dimension ref="B9:T996"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23192,7 +23192,7 @@
         <v>72</v>
       </c>
       <c r="P70" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q70" t="s">
         <v>518</v>
@@ -23245,7 +23245,7 @@
         <v>74</v>
       </c>
       <c r="P71" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q71" t="s">
         <v>518</v>
@@ -23457,7 +23457,7 @@
         <v>78</v>
       </c>
       <c r="P75" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q75" t="s">
         <v>518</v>
@@ -26466,7 +26466,7 @@
         <v>135</v>
       </c>
       <c r="P132" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q132" t="s">
         <v>518</v>
@@ -26519,7 +26519,7 @@
         <v>137</v>
       </c>
       <c r="P133" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q133" t="s">
         <v>518</v>
@@ -29010,7 +29010,7 @@
         <v>184</v>
       </c>
       <c r="P180" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q180" t="s">
         <v>518</v>
@@ -29063,7 +29063,7 @@
         <v>185</v>
       </c>
       <c r="P181" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q181" t="s">
         <v>518</v>
@@ -29116,7 +29116,7 @@
         <v>186</v>
       </c>
       <c r="P182" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q182" t="s">
         <v>518</v>
@@ -30270,7 +30270,7 @@
         <v>209</v>
       </c>
       <c r="P204" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q204" t="s">
         <v>518</v>
@@ -34086,7 +34086,7 @@
         <v>281</v>
       </c>
       <c r="P276" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q276" t="s">
         <v>518</v>
@@ -35941,7 +35941,7 @@
         <v>316</v>
       </c>
       <c r="P311" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q311" t="s">
         <v>518</v>
@@ -38208,7 +38208,7 @@
         <v>361</v>
       </c>
       <c r="P354" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q354" t="s">
         <v>518</v>
@@ -38261,7 +38261,7 @@
         <v>362</v>
       </c>
       <c r="P355" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q355" t="s">
         <v>518</v>
@@ -38950,7 +38950,7 @@
         <v>379</v>
       </c>
       <c r="P368" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q368" t="s">
         <v>518</v>
@@ -39003,7 +39003,7 @@
         <v>380</v>
       </c>
       <c r="P369" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q369" t="s">
         <v>518</v>
@@ -39056,7 +39056,7 @@
         <v>382</v>
       </c>
       <c r="P370" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q370" t="s">
         <v>518</v>
@@ -39109,7 +39109,7 @@
         <v>384</v>
       </c>
       <c r="P371" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q371" t="s">
         <v>518</v>
@@ -39162,7 +39162,7 @@
         <v>386</v>
       </c>
       <c r="P372" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q372" t="s">
         <v>518</v>
@@ -39321,7 +39321,7 @@
         <v>390</v>
       </c>
       <c r="P375" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Q375" t="s">
         <v>518</v>
@@ -39374,7 +39374,7 @@
         <v>390</v>
       </c>
       <c r="P376" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q376" t="s">
         <v>518</v>
@@ -39427,7 +39427,7 @@
         <v>391</v>
       </c>
       <c r="P377" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Q377" t="s">
         <v>518</v>
@@ -39480,7 +39480,7 @@
         <v>391</v>
       </c>
       <c r="P378" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q378" t="s">
         <v>518</v>
@@ -39533,7 +39533,7 @@
         <v>392</v>
       </c>
       <c r="P379" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q379" t="s">
         <v>518</v>
@@ -39586,7 +39586,7 @@
         <v>394</v>
       </c>
       <c r="P380" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q380" t="s">
         <v>518</v>
@@ -39639,7 +39639,7 @@
         <v>396</v>
       </c>
       <c r="P381" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q381" t="s">
         <v>518</v>
@@ -39692,7 +39692,7 @@
         <v>398</v>
       </c>
       <c r="P382" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q382" t="s">
         <v>518</v>
@@ -39745,7 +39745,7 @@
         <v>400</v>
       </c>
       <c r="P383" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q383" t="s">
         <v>518</v>
@@ -39798,7 +39798,7 @@
         <v>402</v>
       </c>
       <c r="P384" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q384" t="s">
         <v>518</v>
@@ -39851,7 +39851,7 @@
         <v>404</v>
       </c>
       <c r="P385" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q385" t="s">
         <v>518</v>
@@ -39904,7 +39904,7 @@
         <v>406</v>
       </c>
       <c r="P386" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q386" t="s">
         <v>518</v>
@@ -39957,7 +39957,7 @@
         <v>408</v>
       </c>
       <c r="P387" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q387" t="s">
         <v>518</v>
@@ -40010,7 +40010,7 @@
         <v>410</v>
       </c>
       <c r="P388" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q388" t="s">
         <v>518</v>
@@ -40063,7 +40063,7 @@
         <v>412</v>
       </c>
       <c r="P389" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q389" t="s">
         <v>518</v>
@@ -40116,7 +40116,7 @@
         <v>414</v>
       </c>
       <c r="P390" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q390" t="s">
         <v>518</v>
@@ -40169,7 +40169,7 @@
         <v>416</v>
       </c>
       <c r="P391" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Q391" t="s">
         <v>518</v>
@@ -40222,7 +40222,7 @@
         <v>416</v>
       </c>
       <c r="P392" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q392" t="s">
         <v>518</v>
@@ -40275,7 +40275,7 @@
         <v>418</v>
       </c>
       <c r="P393" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Q393" t="s">
         <v>518</v>
@@ -40328,7 +40328,7 @@
         <v>418</v>
       </c>
       <c r="P394" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q394" t="s">
         <v>518</v>
@@ -40381,7 +40381,7 @@
         <v>420</v>
       </c>
       <c r="P395" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q395" t="s">
         <v>518</v>
@@ -40434,7 +40434,7 @@
         <v>421</v>
       </c>
       <c r="P396" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q396" t="s">
         <v>518</v>
@@ -40487,7 +40487,7 @@
         <v>421</v>
       </c>
       <c r="P397" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Q397" t="s">
         <v>518</v>
@@ -40540,7 +40540,7 @@
         <v>423</v>
       </c>
       <c r="P398" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q398" t="s">
         <v>518</v>
@@ -40593,7 +40593,7 @@
         <v>425</v>
       </c>
       <c r="P399" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q399" t="s">
         <v>518</v>
@@ -40752,7 +40752,7 @@
         <v>429</v>
       </c>
       <c r="P402" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q402" t="s">
         <v>518</v>
@@ -40805,7 +40805,7 @@
         <v>431</v>
       </c>
       <c r="P403" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q403" t="s">
         <v>518</v>
@@ -40858,7 +40858,7 @@
         <v>433</v>
       </c>
       <c r="P404" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q404" t="s">
         <v>518</v>
@@ -40911,7 +40911,7 @@
         <v>435</v>
       </c>
       <c r="P405" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q405" t="s">
         <v>518</v>
@@ -41123,7 +41123,7 @@
         <v>440</v>
       </c>
       <c r="P409" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q409" t="s">
         <v>518</v>
@@ -41176,7 +41176,7 @@
         <v>443</v>
       </c>
       <c r="P410" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q410" t="s">
         <v>518</v>
@@ -41229,7 +41229,7 @@
         <v>445</v>
       </c>
       <c r="P411" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q411" t="s">
         <v>518</v>
@@ -41282,7 +41282,7 @@
         <v>447</v>
       </c>
       <c r="P412" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Q412" t="s">
         <v>518</v>
@@ -41335,7 +41335,7 @@
         <v>449</v>
       </c>
       <c r="P413" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q413" t="s">
         <v>518</v>
@@ -41388,7 +41388,7 @@
         <v>451</v>
       </c>
       <c r="P414" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q414" t="s">
         <v>518</v>
@@ -41441,7 +41441,7 @@
         <v>453</v>
       </c>
       <c r="P415" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q415" t="s">
         <v>518</v>
@@ -41759,7 +41759,7 @@
         <v>465</v>
       </c>
       <c r="P421" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q421" t="s">
         <v>518</v>
@@ -41812,7 +41812,7 @@
         <v>467</v>
       </c>
       <c r="P422" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q422" t="s">
         <v>518</v>
@@ -41865,7 +41865,7 @@
         <v>468</v>
       </c>
       <c r="P423" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q423" t="s">
         <v>518</v>
@@ -41918,7 +41918,7 @@
         <v>470</v>
       </c>
       <c r="P424" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q424" t="s">
         <v>518</v>
@@ -41971,7 +41971,7 @@
         <v>472</v>
       </c>
       <c r="P425" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q425" t="s">
         <v>518</v>
@@ -42021,7 +42021,7 @@
         <v>474</v>
       </c>
       <c r="P426" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q426" t="s">
         <v>518</v>
@@ -42071,7 +42071,7 @@
         <v>474</v>
       </c>
       <c r="P427" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Q427" t="s">
         <v>518</v>
@@ -42121,7 +42121,7 @@
         <v>476</v>
       </c>
       <c r="P428" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q428" t="s">
         <v>518</v>
@@ -42171,7 +42171,7 @@
         <v>478</v>
       </c>
       <c r="P429" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q429" t="s">
         <v>518</v>
@@ -42221,7 +42221,7 @@
         <v>478</v>
       </c>
       <c r="P430" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Q430" t="s">
         <v>518</v>
@@ -42271,7 +42271,7 @@
         <v>480</v>
       </c>
       <c r="P431" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q431" t="s">
         <v>518</v>
@@ -42321,7 +42321,7 @@
         <v>482</v>
       </c>
       <c r="P432" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q432" t="s">
         <v>518</v>
@@ -42371,7 +42371,7 @@
         <v>484</v>
       </c>
       <c r="P433" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q433" t="s">
         <v>518</v>
@@ -42421,7 +42421,7 @@
         <v>486</v>
       </c>
       <c r="P434" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q434" t="s">
         <v>518</v>
@@ -42471,7 +42471,7 @@
         <v>488</v>
       </c>
       <c r="P435" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q435" t="s">
         <v>518</v>
@@ -42521,7 +42521,7 @@
         <v>490</v>
       </c>
       <c r="P436" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q436" t="s">
         <v>518</v>
@@ -42571,7 +42571,7 @@
         <v>492</v>
       </c>
       <c r="P437" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q437" t="s">
         <v>518</v>
@@ -42621,7 +42621,7 @@
         <v>492</v>
       </c>
       <c r="P438" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Q438" t="s">
         <v>518</v>
@@ -42771,7 +42771,7 @@
         <v>496</v>
       </c>
       <c r="P441" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q441" t="s">
         <v>518</v>
@@ -42821,7 +42821,7 @@
         <v>496</v>
       </c>
       <c r="P442" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Q442" t="s">
         <v>518</v>
@@ -42871,7 +42871,7 @@
         <v>498</v>
       </c>
       <c r="P443" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q443" t="s">
         <v>518</v>
@@ -42921,7 +42921,7 @@
         <v>500</v>
       </c>
       <c r="P444" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q444" t="s">
         <v>518</v>
@@ -42971,7 +42971,7 @@
         <v>502</v>
       </c>
       <c r="P445" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q445" t="s">
         <v>518</v>
@@ -43021,7 +43021,7 @@
         <v>503</v>
       </c>
       <c r="P446" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q446" t="s">
         <v>518</v>
@@ -43071,7 +43071,7 @@
         <v>505</v>
       </c>
       <c r="P447" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Q447" t="s">
         <v>518</v>
@@ -43121,7 +43121,7 @@
         <v>505</v>
       </c>
       <c r="P448" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q448" t="s">
         <v>518</v>
@@ -43171,7 +43171,7 @@
         <v>507</v>
       </c>
       <c r="P449" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Q449" t="s">
         <v>518</v>
@@ -61947,7 +61947,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F09553A-EF19-4B2F-AEB4-14C71FEB731A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDBCDFB-E02D-4F36-8BBC-1C8931D91A85}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
